--- a/docs/balance/final status.xlsx
+++ b/docs/balance/final status.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_版本与口径" sheetId="1" r:id="Rc77e7b895931489e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_棋子基础" sheetId="2" r:id="R3813da0535534520"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_棋子技能" sheetId="3" r:id="Rbe5498b7547042b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_宠物与商城" sheetId="4" r:id="R5478ddca75cb4516"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_羁绊" sheetId="5" r:id="R693beae0369c4825"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_野怪" sheetId="6" r:id="R0a2aa50d82904c28"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_Boss" sheetId="7" r:id="R28ee6b2848364c28"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_佣兵" sheetId="8" r:id="R0083492c362e4e7c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_法阵友军" sheetId="9" r:id="R898e5e33d38a4a57"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_宝藏与套装" sheetId="10" r:id="R5635d0c7a93b4d68"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_宝藏联动" sheetId="11" r:id="R404fd7bf1399459f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_金币规则" sheetId="12" r:id="R6631ee625a644dcd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_萝卜规则" sheetId="13" r:id="Rd7f7ab2fe03c4524"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_回合与商店" sheetId="14" r:id="R790ad9756a3042d4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_界面映射" sheetId="15" r:id="Rb74e9d730c594b0a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_冲突与验证" sheetId="16" r:id="Rc2d99fefb9454534"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="90_运行配置" sheetId="17" r:id="R85e91f8bcef34650"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="91_来源清单" sheetId="18" r:id="Rdbcb52a0e48c418e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="92_代码参数" sheetId="19" r:id="R80f2eefdfbbf4dde"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="93_商城目录" sheetId="20" r:id="Rf8c697e7726b4a2f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_版本与口径" sheetId="1" r:id="Rbc9f94533e1f4de3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_棋子基础" sheetId="2" r:id="R8c12b76d00474b0e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_棋子技能" sheetId="3" r:id="Rdec20b56cd0b49f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_宠物与商城" sheetId="4" r:id="Rf5fdc2bc53c84dc7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_羁绊" sheetId="5" r:id="Rc1e798b18c3b4964"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_野怪" sheetId="6" r:id="R40effd7421f94fe3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_Boss" sheetId="7" r:id="R859b5958df554f38"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_佣兵" sheetId="8" r:id="Rc421c76db5004995"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_法阵友军" sheetId="9" r:id="R468702f519b34c0d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_宝藏与套装" sheetId="10" r:id="Rb0bd05e7ce684546"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_宝藏联动" sheetId="11" r:id="Re82476d1f1bd4a09"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_金币规则" sheetId="12" r:id="Rc0db4d14e2014fa3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_萝卜规则" sheetId="13" r:id="R95cb57068bf14711"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_回合与商店" sheetId="14" r:id="R6e76ca46b3e34806"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_界面映射" sheetId="15" r:id="Rc5550d3bb1664009"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_冲突与验证" sheetId="16" r:id="R9855aaa9e6894675"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="90_运行配置" sheetId="17" r:id="R136561bd0a1c4796"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="91_来源清单" sheetId="18" r:id="Ra374f73a99054af8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="92_代码参数" sheetId="19" r:id="R92c8508dc14d4631"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="93_商城目录" sheetId="20" r:id="R7cc36b6846f446d6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4691,7 +4691,7 @@
     </x:row>
     <x:row r="2" ht="42" customHeight="1">
       <x:c r="A2" s="4" t="str">
-        <x:v>高级字段：完整收录当前 Godot/商城运行 JSON。路径以 $ 为根，值按 JSON 语法编辑；普通数值优先在前面的业务页修改。导出工具会检查并生成运行文件。</x:v>
+        <x:v>历史配置快照，仅供查阅，不再参与运行前同步。基础数值以 01/03/05/06/08 业务页为准；其余复杂字段以项目中的 JSON / GDScript 为准。</x:v>
       </x:c>
       <x:c r="B2" s="4"/>
       <x:c r="C2" s="4"/>
@@ -52028,7 +52028,7 @@
     </x:row>
     <x:row r="2" ht="32" customHeight="1">
       <x:c r="A2" s="4" t="str">
-        <x:v>40 名棋子。1–4★ HP / 攻击 / 防御为新表中的本机战斗运行值；战斗内其他加成仍按对应规则动态结算。</x:v>
+        <x:v>编辑 1★ HP / 攻击 / 防御（G、K、O 列）；2–4★由公式按游戏星级倍率计算。运行前执行 tools/run_with_final.py，同步 JSON 和游戏显示。</x:v>
       </x:c>
       <x:c r="B2" s="4"/>
       <x:c r="C2" s="4"/>
@@ -52171,36 +52171,45 @@
         <x:v>580</x:v>
       </x:c>
       <x:c r="H4" s="11" t="n">
+        <x:f>ROUND(G4*1.5,0)</x:f>
         <x:v>870</x:v>
       </x:c>
       <x:c r="I4" s="11" t="n">
+        <x:f>ROUND(G4*3,0)</x:f>
         <x:v>1740</x:v>
       </x:c>
       <x:c r="J4" s="11" t="n">
+        <x:f>ROUND(G4*(3*1.15),0)</x:f>
         <x:v>2001</x:v>
       </x:c>
       <x:c r="K4" s="11" t="n">
         <x:v>37</x:v>
       </x:c>
       <x:c r="L4" s="11" t="n">
+        <x:f>ROUND(K4*1.5,0)</x:f>
         <x:v>56</x:v>
       </x:c>
       <x:c r="M4" s="11" t="n">
+        <x:f>ROUND(K4*3,0)</x:f>
         <x:v>111</x:v>
       </x:c>
       <x:c r="N4" s="11" t="n">
+        <x:f>ROUND(K4*(3*1.15),0)</x:f>
         <x:v>128</x:v>
       </x:c>
       <x:c r="O4" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="P4" s="11" t="n">
+        <x:f>ROUND(O4*1.5,0)</x:f>
         <x:v>6</x:v>
       </x:c>
       <x:c r="Q4" s="11" t="n">
+        <x:f>ROUND(O4*3,0)</x:f>
         <x:v>12</x:v>
       </x:c>
       <x:c r="R4" s="11" t="n">
+        <x:f>ROUND(O4*(3*1.15),0)</x:f>
         <x:v>14</x:v>
       </x:c>
       <x:c r="S4" s="11" t="n">
@@ -52258,36 +52267,45 @@
         <x:v>520</x:v>
       </x:c>
       <x:c r="H5" s="15" t="n">
+        <x:f>ROUND(G5*1.5,0)</x:f>
         <x:v>780</x:v>
       </x:c>
       <x:c r="I5" s="15" t="n">
+        <x:f>ROUND(G5*3,0)</x:f>
         <x:v>1560</x:v>
       </x:c>
       <x:c r="J5" s="15" t="n">
+        <x:f>ROUND(G5*(3*1.15),0)</x:f>
         <x:v>1794</x:v>
       </x:c>
       <x:c r="K5" s="15" t="n">
         <x:v>48</x:v>
       </x:c>
       <x:c r="L5" s="15" t="n">
+        <x:f>ROUND(K5*1.5,0)</x:f>
         <x:v>72</x:v>
       </x:c>
       <x:c r="M5" s="15" t="n">
+        <x:f>ROUND(K5*3,0)</x:f>
         <x:v>144</x:v>
       </x:c>
       <x:c r="N5" s="15" t="n">
+        <x:f>ROUND(K5*(3*1.15),0)</x:f>
         <x:v>166</x:v>
       </x:c>
       <x:c r="O5" s="15" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="P5" s="15" t="n">
+        <x:f>ROUND(O5*1.5,0)</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="Q5" s="15" t="n">
+        <x:f>ROUND(O5*3,0)</x:f>
         <x:v>9</x:v>
       </x:c>
       <x:c r="R5" s="15" t="n">
+        <x:f>ROUND(O5*(3*1.15),0)</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="S5" s="15" t="n">
@@ -52345,36 +52363,45 @@
         <x:v>840</x:v>
       </x:c>
       <x:c r="H6" s="11" t="n">
+        <x:f>ROUND(G6*1.5,0)</x:f>
         <x:v>1260</x:v>
       </x:c>
       <x:c r="I6" s="11" t="n">
+        <x:f>ROUND(G6*3,0)</x:f>
         <x:v>2520</x:v>
       </x:c>
       <x:c r="J6" s="11" t="n">
+        <x:f>ROUND(G6*(3*1.15),0)</x:f>
         <x:v>2898</x:v>
       </x:c>
       <x:c r="K6" s="11" t="n">
         <x:v>55</x:v>
       </x:c>
       <x:c r="L6" s="11" t="n">
+        <x:f>ROUND(K6*1.5,0)</x:f>
         <x:v>83</x:v>
       </x:c>
       <x:c r="M6" s="11" t="n">
+        <x:f>ROUND(K6*3,0)</x:f>
         <x:v>165</x:v>
       </x:c>
       <x:c r="N6" s="11" t="n">
+        <x:f>ROUND(K6*(3*1.15),0)</x:f>
         <x:v>190</x:v>
       </x:c>
       <x:c r="O6" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="P6" s="11" t="n">
+        <x:f>ROUND(O6*1.5,0)</x:f>
         <x:v>11</x:v>
       </x:c>
       <x:c r="Q6" s="11" t="n">
+        <x:f>ROUND(O6*3,0)</x:f>
         <x:v>21</x:v>
       </x:c>
       <x:c r="R6" s="11" t="n">
+        <x:f>ROUND(O6*(3*1.15),0)</x:f>
         <x:v>24</x:v>
       </x:c>
       <x:c r="S6" s="11" t="n">
@@ -52432,36 +52459,45 @@
         <x:v>920</x:v>
       </x:c>
       <x:c r="H7" s="15" t="n">
+        <x:f>ROUND(G7*1.5,0)</x:f>
         <x:v>1380</x:v>
       </x:c>
       <x:c r="I7" s="15" t="n">
+        <x:f>ROUND(G7*3,0)</x:f>
         <x:v>2760</x:v>
       </x:c>
       <x:c r="J7" s="15" t="n">
+        <x:f>ROUND(G7*(3*1.15),0)</x:f>
         <x:v>3174</x:v>
       </x:c>
       <x:c r="K7" s="15" t="n">
         <x:v>68</x:v>
       </x:c>
       <x:c r="L7" s="15" t="n">
+        <x:f>ROUND(K7*1.5,0)</x:f>
         <x:v>102</x:v>
       </x:c>
       <x:c r="M7" s="15" t="n">
+        <x:f>ROUND(K7*3,0)</x:f>
         <x:v>204</x:v>
       </x:c>
       <x:c r="N7" s="15" t="n">
+        <x:f>ROUND(K7*(3*1.15),0)</x:f>
         <x:v>235</x:v>
       </x:c>
       <x:c r="O7" s="15" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="P7" s="15" t="n">
+        <x:f>ROUND(O7*1.5,0)</x:f>
         <x:v>12</x:v>
       </x:c>
       <x:c r="Q7" s="15" t="n">
+        <x:f>ROUND(O7*3,0)</x:f>
         <x:v>24</x:v>
       </x:c>
       <x:c r="R7" s="15" t="n">
+        <x:f>ROUND(O7*(3*1.15),0)</x:f>
         <x:v>28</x:v>
       </x:c>
       <x:c r="S7" s="15" t="n">
@@ -52519,36 +52555,45 @@
         <x:v>780</x:v>
       </x:c>
       <x:c r="H8" s="11" t="n">
+        <x:f>ROUND(G8*1.5,0)</x:f>
         <x:v>1170</x:v>
       </x:c>
       <x:c r="I8" s="11" t="n">
+        <x:f>ROUND(G8*3,0)</x:f>
         <x:v>2340</x:v>
       </x:c>
       <x:c r="J8" s="11" t="n">
+        <x:f>ROUND(G8*(3*1.15),0)</x:f>
         <x:v>2691</x:v>
       </x:c>
       <x:c r="K8" s="11" t="n">
         <x:v>88</x:v>
       </x:c>
       <x:c r="L8" s="11" t="n">
+        <x:f>ROUND(K8*1.5,0)</x:f>
         <x:v>132</x:v>
       </x:c>
       <x:c r="M8" s="11" t="n">
+        <x:f>ROUND(K8*3,0)</x:f>
         <x:v>264</x:v>
       </x:c>
       <x:c r="N8" s="11" t="n">
+        <x:f>ROUND(K8*(3*1.15),0)</x:f>
         <x:v>304</x:v>
       </x:c>
       <x:c r="O8" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="P8" s="11" t="n">
+        <x:f>ROUND(O8*1.5,0)</x:f>
         <x:v>9</x:v>
       </x:c>
       <x:c r="Q8" s="11" t="n">
+        <x:f>ROUND(O8*3,0)</x:f>
         <x:v>18</x:v>
       </x:c>
       <x:c r="R8" s="11" t="n">
+        <x:f>ROUND(O8*(3*1.15),0)</x:f>
         <x:v>21</x:v>
       </x:c>
       <x:c r="S8" s="11" t="n">
@@ -52606,36 +52651,45 @@
         <x:v>860</x:v>
       </x:c>
       <x:c r="H9" s="15" t="n">
+        <x:f>ROUND(G9*1.5,0)</x:f>
         <x:v>1290</x:v>
       </x:c>
       <x:c r="I9" s="15" t="n">
+        <x:f>ROUND(G9*3,0)</x:f>
         <x:v>2580</x:v>
       </x:c>
       <x:c r="J9" s="15" t="n">
+        <x:f>ROUND(G9*(3*1.15),0)</x:f>
         <x:v>2967</x:v>
       </x:c>
       <x:c r="K9" s="15" t="n">
         <x:v>64</x:v>
       </x:c>
       <x:c r="L9" s="15" t="n">
+        <x:f>ROUND(K9*1.5,0)</x:f>
         <x:v>96</x:v>
       </x:c>
       <x:c r="M9" s="15" t="n">
+        <x:f>ROUND(K9*3,0)</x:f>
         <x:v>192</x:v>
       </x:c>
       <x:c r="N9" s="15" t="n">
+        <x:f>ROUND(K9*(3*1.15),0)</x:f>
         <x:v>221</x:v>
       </x:c>
       <x:c r="O9" s="15" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="P9" s="15" t="n">
+        <x:f>ROUND(O9*1.5,0)</x:f>
         <x:v>11</x:v>
       </x:c>
       <x:c r="Q9" s="15" t="n">
+        <x:f>ROUND(O9*3,0)</x:f>
         <x:v>21</x:v>
       </x:c>
       <x:c r="R9" s="15" t="n">
+        <x:f>ROUND(O9*(3*1.15),0)</x:f>
         <x:v>24</x:v>
       </x:c>
       <x:c r="S9" s="15" t="n">
@@ -52693,36 +52747,45 @@
         <x:v>1640</x:v>
       </x:c>
       <x:c r="H10" s="11" t="n">
+        <x:f>ROUND(G10*1.5,0)</x:f>
         <x:v>2460</x:v>
       </x:c>
       <x:c r="I10" s="11" t="n">
+        <x:f>ROUND(G10*3,0)</x:f>
         <x:v>4920</x:v>
       </x:c>
       <x:c r="J10" s="11" t="n">
+        <x:f>ROUND(G10*(3*1.15),0)</x:f>
         <x:v>5658</x:v>
       </x:c>
       <x:c r="K10" s="11" t="n">
         <x:v>97</x:v>
       </x:c>
       <x:c r="L10" s="11" t="n">
+        <x:f>ROUND(K10*1.5,0)</x:f>
         <x:v>146</x:v>
       </x:c>
       <x:c r="M10" s="11" t="n">
+        <x:f>ROUND(K10*3,0)</x:f>
         <x:v>291</x:v>
       </x:c>
       <x:c r="N10" s="11" t="n">
+        <x:f>ROUND(K10*(3*1.15),0)</x:f>
         <x:v>335</x:v>
       </x:c>
       <x:c r="O10" s="11" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="P10" s="11" t="n">
+        <x:f>ROUND(O10*1.5,0)</x:f>
         <x:v>24</x:v>
       </x:c>
       <x:c r="Q10" s="11" t="n">
+        <x:f>ROUND(O10*3,0)</x:f>
         <x:v>48</x:v>
       </x:c>
       <x:c r="R10" s="11" t="n">
+        <x:f>ROUND(O10*(3*1.15),0)</x:f>
         <x:v>55</x:v>
       </x:c>
       <x:c r="S10" s="11" t="n">
@@ -52782,36 +52845,45 @@
         <x:v>1800</x:v>
       </x:c>
       <x:c r="H11" s="15" t="n">
+        <x:f>ROUND(G11*1.5,0)</x:f>
         <x:v>2700</x:v>
       </x:c>
       <x:c r="I11" s="15" t="n">
+        <x:f>ROUND(G11*3,0)</x:f>
         <x:v>5400</x:v>
       </x:c>
       <x:c r="J11" s="15" t="n">
+        <x:f>ROUND(G11*(3*1.15),0)</x:f>
         <x:v>6210</x:v>
       </x:c>
       <x:c r="K11" s="15" t="n">
         <x:v>110</x:v>
       </x:c>
       <x:c r="L11" s="15" t="n">
+        <x:f>ROUND(K11*1.5,0)</x:f>
         <x:v>165</x:v>
       </x:c>
       <x:c r="M11" s="15" t="n">
+        <x:f>ROUND(K11*3,0)</x:f>
         <x:v>330</x:v>
       </x:c>
       <x:c r="N11" s="15" t="n">
+        <x:f>ROUND(K11*(3*1.15),0)</x:f>
         <x:v>379</x:v>
       </x:c>
       <x:c r="O11" s="15" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="P11" s="15" t="n">
+        <x:f>ROUND(O11*1.5,0)</x:f>
         <x:v>21</x:v>
       </x:c>
       <x:c r="Q11" s="15" t="n">
+        <x:f>ROUND(O11*3,0)</x:f>
         <x:v>42</x:v>
       </x:c>
       <x:c r="R11" s="15" t="n">
+        <x:f>ROUND(O11*(3*1.15),0)</x:f>
         <x:v>48</x:v>
       </x:c>
       <x:c r="S11" s="15" t="n">
@@ -52871,36 +52943,45 @@
         <x:v>640</x:v>
       </x:c>
       <x:c r="H12" s="11" t="n">
+        <x:f>ROUND(G12*1.5,0)</x:f>
         <x:v>960</x:v>
       </x:c>
       <x:c r="I12" s="11" t="n">
+        <x:f>ROUND(G12*3,0)</x:f>
         <x:v>1920</x:v>
       </x:c>
       <x:c r="J12" s="11" t="n">
+        <x:f>ROUND(G12*(3*1.15),0)</x:f>
         <x:v>2208</x:v>
       </x:c>
       <x:c r="K12" s="11" t="n">
         <x:v>31</x:v>
       </x:c>
       <x:c r="L12" s="11" t="n">
+        <x:f>ROUND(K12*1.5,0)</x:f>
         <x:v>47</x:v>
       </x:c>
       <x:c r="M12" s="11" t="n">
+        <x:f>ROUND(K12*3,0)</x:f>
         <x:v>93</x:v>
       </x:c>
       <x:c r="N12" s="11" t="n">
+        <x:f>ROUND(K12*(3*1.15),0)</x:f>
         <x:v>107</x:v>
       </x:c>
       <x:c r="O12" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="P12" s="11" t="n">
+        <x:f>ROUND(O12*1.5,0)</x:f>
         <x:v>6</x:v>
       </x:c>
       <x:c r="Q12" s="11" t="n">
+        <x:f>ROUND(O12*3,0)</x:f>
         <x:v>12</x:v>
       </x:c>
       <x:c r="R12" s="11" t="n">
+        <x:f>ROUND(O12*(3*1.15),0)</x:f>
         <x:v>14</x:v>
       </x:c>
       <x:c r="S12" s="11" t="n">
@@ -52958,36 +53039,45 @@
         <x:v>600</x:v>
       </x:c>
       <x:c r="H13" s="15" t="n">
+        <x:f>ROUND(G13*1.5,0)</x:f>
         <x:v>900</x:v>
       </x:c>
       <x:c r="I13" s="15" t="n">
+        <x:f>ROUND(G13*3,0)</x:f>
         <x:v>1800</x:v>
       </x:c>
       <x:c r="J13" s="15" t="n">
+        <x:f>ROUND(G13*(3*1.15),0)</x:f>
         <x:v>2070</x:v>
       </x:c>
       <x:c r="K13" s="15" t="n">
         <x:v>26</x:v>
       </x:c>
       <x:c r="L13" s="15" t="n">
+        <x:f>ROUND(K13*1.5,0)</x:f>
         <x:v>39</x:v>
       </x:c>
       <x:c r="M13" s="15" t="n">
+        <x:f>ROUND(K13*3,0)</x:f>
         <x:v>78</x:v>
       </x:c>
       <x:c r="N13" s="15" t="n">
+        <x:f>ROUND(K13*(3*1.15),0)</x:f>
         <x:v>90</x:v>
       </x:c>
       <x:c r="O13" s="15" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="P13" s="15" t="n">
+        <x:f>ROUND(O13*1.5,0)</x:f>
         <x:v>6</x:v>
       </x:c>
       <x:c r="Q13" s="15" t="n">
+        <x:f>ROUND(O13*3,0)</x:f>
         <x:v>12</x:v>
       </x:c>
       <x:c r="R13" s="15" t="n">
+        <x:f>ROUND(O13*(3*1.15),0)</x:f>
         <x:v>14</x:v>
       </x:c>
       <x:c r="S13" s="15" t="n">
@@ -53045,36 +53135,45 @@
         <x:v>1080</x:v>
       </x:c>
       <x:c r="H14" s="11" t="n">
+        <x:f>ROUND(G14*1.5,0)</x:f>
         <x:v>1620</x:v>
       </x:c>
       <x:c r="I14" s="11" t="n">
+        <x:f>ROUND(G14*3,0)</x:f>
         <x:v>3240</x:v>
       </x:c>
       <x:c r="J14" s="11" t="n">
+        <x:f>ROUND(G14*(3*1.15),0)</x:f>
         <x:v>3726</x:v>
       </x:c>
       <x:c r="K14" s="11" t="n">
         <x:v>48</x:v>
       </x:c>
       <x:c r="L14" s="11" t="n">
+        <x:f>ROUND(K14*1.5,0)</x:f>
         <x:v>72</x:v>
       </x:c>
       <x:c r="M14" s="11" t="n">
+        <x:f>ROUND(K14*3,0)</x:f>
         <x:v>144</x:v>
       </x:c>
       <x:c r="N14" s="11" t="n">
+        <x:f>ROUND(K14*(3*1.15),0)</x:f>
         <x:v>166</x:v>
       </x:c>
       <x:c r="O14" s="11" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="P14" s="11" t="n">
+        <x:f>ROUND(O14*1.5,0)</x:f>
         <x:v>12</x:v>
       </x:c>
       <x:c r="Q14" s="11" t="n">
+        <x:f>ROUND(O14*3,0)</x:f>
         <x:v>24</x:v>
       </x:c>
       <x:c r="R14" s="11" t="n">
+        <x:f>ROUND(O14*(3*1.15),0)</x:f>
         <x:v>28</x:v>
       </x:c>
       <x:c r="S14" s="11" t="n">
@@ -53132,36 +53231,45 @@
         <x:v>1040</x:v>
       </x:c>
       <x:c r="H15" s="15" t="n">
+        <x:f>ROUND(G15*1.5,0)</x:f>
         <x:v>1560</x:v>
       </x:c>
       <x:c r="I15" s="15" t="n">
+        <x:f>ROUND(G15*3,0)</x:f>
         <x:v>3120</x:v>
       </x:c>
       <x:c r="J15" s="15" t="n">
+        <x:f>ROUND(G15*(3*1.15),0)</x:f>
         <x:v>3588</x:v>
       </x:c>
       <x:c r="K15" s="15" t="n">
         <x:v>79</x:v>
       </x:c>
       <x:c r="L15" s="15" t="n">
+        <x:f>ROUND(K15*1.5,0)</x:f>
         <x:v>119</x:v>
       </x:c>
       <x:c r="M15" s="15" t="n">
+        <x:f>ROUND(K15*3,0)</x:f>
         <x:v>237</x:v>
       </x:c>
       <x:c r="N15" s="15" t="n">
+        <x:f>ROUND(K15*(3*1.15),0)</x:f>
         <x:v>273</x:v>
       </x:c>
       <x:c r="O15" s="15" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="P15" s="15" t="n">
+        <x:f>ROUND(O15*1.5,0)</x:f>
         <x:v>15</x:v>
       </x:c>
       <x:c r="Q15" s="15" t="n">
+        <x:f>ROUND(O15*3,0)</x:f>
         <x:v>30</x:v>
       </x:c>
       <x:c r="R15" s="15" t="n">
+        <x:f>ROUND(O15*(3*1.15),0)</x:f>
         <x:v>35</x:v>
       </x:c>
       <x:c r="S15" s="15" t="n">
@@ -53219,36 +53327,45 @@
         <x:v>720</x:v>
       </x:c>
       <x:c r="H16" s="11" t="n">
+        <x:f>ROUND(G16*1.5,0)</x:f>
         <x:v>1080</x:v>
       </x:c>
       <x:c r="I16" s="11" t="n">
+        <x:f>ROUND(G16*3,0)</x:f>
         <x:v>2160</x:v>
       </x:c>
       <x:c r="J16" s="11" t="n">
+        <x:f>ROUND(G16*(3*1.15),0)</x:f>
         <x:v>2484</x:v>
       </x:c>
       <x:c r="K16" s="11" t="n">
         <x:v>77</x:v>
       </x:c>
       <x:c r="L16" s="11" t="n">
+        <x:f>ROUND(K16*1.5,0)</x:f>
         <x:v>116</x:v>
       </x:c>
       <x:c r="M16" s="11" t="n">
+        <x:f>ROUND(K16*3,0)</x:f>
         <x:v>231</x:v>
       </x:c>
       <x:c r="N16" s="11" t="n">
+        <x:f>ROUND(K16*(3*1.15),0)</x:f>
         <x:v>266</x:v>
       </x:c>
       <x:c r="O16" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="P16" s="11" t="n">
+        <x:f>ROUND(O16*1.5,0)</x:f>
         <x:v>6</x:v>
       </x:c>
       <x:c r="Q16" s="11" t="n">
+        <x:f>ROUND(O16*3,0)</x:f>
         <x:v>12</x:v>
       </x:c>
       <x:c r="R16" s="11" t="n">
+        <x:f>ROUND(O16*(3*1.15),0)</x:f>
         <x:v>14</x:v>
       </x:c>
       <x:c r="S16" s="11" t="n">
@@ -53306,36 +53423,45 @@
         <x:v>1520</x:v>
       </x:c>
       <x:c r="H17" s="15" t="n">
+        <x:f>ROUND(G17*1.5,0)</x:f>
         <x:v>2280</x:v>
       </x:c>
       <x:c r="I17" s="15" t="n">
+        <x:f>ROUND(G17*3,0)</x:f>
         <x:v>4560</x:v>
       </x:c>
       <x:c r="J17" s="15" t="n">
+        <x:f>ROUND(G17*(3*1.15),0)</x:f>
         <x:v>5244</x:v>
       </x:c>
       <x:c r="K17" s="15" t="n">
         <x:v>46</x:v>
       </x:c>
       <x:c r="L17" s="15" t="n">
+        <x:f>ROUND(K17*1.5,0)</x:f>
         <x:v>69</x:v>
       </x:c>
       <x:c r="M17" s="15" t="n">
+        <x:f>ROUND(K17*3,0)</x:f>
         <x:v>138</x:v>
       </x:c>
       <x:c r="N17" s="15" t="n">
+        <x:f>ROUND(K17*(3*1.15),0)</x:f>
         <x:v>159</x:v>
       </x:c>
       <x:c r="O17" s="15" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="P17" s="15" t="n">
+        <x:f>ROUND(O17*1.5,0)</x:f>
         <x:v>21</x:v>
       </x:c>
       <x:c r="Q17" s="15" t="n">
+        <x:f>ROUND(O17*3,0)</x:f>
         <x:v>42</x:v>
       </x:c>
       <x:c r="R17" s="15" t="n">
+        <x:f>ROUND(O17*(3*1.15),0)</x:f>
         <x:v>48</x:v>
       </x:c>
       <x:c r="S17" s="15" t="n">
@@ -53393,36 +53519,45 @@
         <x:v>1700</x:v>
       </x:c>
       <x:c r="H18" s="11" t="n">
+        <x:f>ROUND(G18*1.5,0)</x:f>
         <x:v>2550</x:v>
       </x:c>
       <x:c r="I18" s="11" t="n">
+        <x:f>ROUND(G18*3,0)</x:f>
         <x:v>5100</x:v>
       </x:c>
       <x:c r="J18" s="11" t="n">
+        <x:f>ROUND(G18*(3*1.15),0)</x:f>
         <x:v>5865</x:v>
       </x:c>
       <x:c r="K18" s="11" t="n">
         <x:v>73</x:v>
       </x:c>
       <x:c r="L18" s="11" t="n">
+        <x:f>ROUND(K18*1.5,0)</x:f>
         <x:v>110</x:v>
       </x:c>
       <x:c r="M18" s="11" t="n">
+        <x:f>ROUND(K18*3,0)</x:f>
         <x:v>219</x:v>
       </x:c>
       <x:c r="N18" s="11" t="n">
+        <x:f>ROUND(K18*(3*1.15),0)</x:f>
         <x:v>252</x:v>
       </x:c>
       <x:c r="O18" s="11" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="P18" s="11" t="n">
+        <x:f>ROUND(O18*1.5,0)</x:f>
         <x:v>23</x:v>
       </x:c>
       <x:c r="Q18" s="11" t="n">
+        <x:f>ROUND(O18*3,0)</x:f>
         <x:v>45</x:v>
       </x:c>
       <x:c r="R18" s="11" t="n">
+        <x:f>ROUND(O18*(3*1.15),0)</x:f>
         <x:v>52</x:v>
       </x:c>
       <x:c r="S18" s="11" t="n">
@@ -53482,36 +53617,45 @@
         <x:v>1800</x:v>
       </x:c>
       <x:c r="H19" s="15" t="n">
+        <x:f>ROUND(G19*1.5,0)</x:f>
         <x:v>2700</x:v>
       </x:c>
       <x:c r="I19" s="15" t="n">
+        <x:f>ROUND(G19*3,0)</x:f>
         <x:v>5400</x:v>
       </x:c>
       <x:c r="J19" s="15" t="n">
+        <x:f>ROUND(G19*(3*1.15),0)</x:f>
         <x:v>6210</x:v>
       </x:c>
       <x:c r="K19" s="15" t="n">
         <x:v>105</x:v>
       </x:c>
       <x:c r="L19" s="15" t="n">
+        <x:f>ROUND(K19*1.5,0)</x:f>
         <x:v>158</x:v>
       </x:c>
       <x:c r="M19" s="15" t="n">
+        <x:f>ROUND(K19*3,0)</x:f>
         <x:v>315</x:v>
       </x:c>
       <x:c r="N19" s="15" t="n">
+        <x:f>ROUND(K19*(3*1.15),0)</x:f>
         <x:v>362</x:v>
       </x:c>
       <x:c r="O19" s="15" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="P19" s="15" t="n">
+        <x:f>ROUND(O19*1.5,0)</x:f>
         <x:v>24</x:v>
       </x:c>
       <x:c r="Q19" s="15" t="n">
+        <x:f>ROUND(O19*3,0)</x:f>
         <x:v>48</x:v>
       </x:c>
       <x:c r="R19" s="15" t="n">
+        <x:f>ROUND(O19*(3*1.15),0)</x:f>
         <x:v>55</x:v>
       </x:c>
       <x:c r="S19" s="15" t="n">
@@ -53571,36 +53715,45 @@
         <x:v>560</x:v>
       </x:c>
       <x:c r="H20" s="11" t="n">
+        <x:f>ROUND(G20*1.5,0)</x:f>
         <x:v>840</x:v>
       </x:c>
       <x:c r="I20" s="11" t="n">
+        <x:f>ROUND(G20*3,0)</x:f>
         <x:v>1680</x:v>
       </x:c>
       <x:c r="J20" s="11" t="n">
+        <x:f>ROUND(G20*(3*1.15),0)</x:f>
         <x:v>1932</x:v>
       </x:c>
       <x:c r="K20" s="11" t="n">
         <x:v>29</x:v>
       </x:c>
       <x:c r="L20" s="11" t="n">
+        <x:f>ROUND(K20*1.5,0)</x:f>
         <x:v>44</x:v>
       </x:c>
       <x:c r="M20" s="11" t="n">
+        <x:f>ROUND(K20*3,0)</x:f>
         <x:v>87</x:v>
       </x:c>
       <x:c r="N20" s="11" t="n">
+        <x:f>ROUND(K20*(3*1.15),0)</x:f>
         <x:v>100</x:v>
       </x:c>
       <x:c r="O20" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="P20" s="11" t="n">
+        <x:f>ROUND(O20*1.5,0)</x:f>
         <x:v>6</x:v>
       </x:c>
       <x:c r="Q20" s="11" t="n">
+        <x:f>ROUND(O20*3,0)</x:f>
         <x:v>12</x:v>
       </x:c>
       <x:c r="R20" s="11" t="n">
+        <x:f>ROUND(O20*(3*1.15),0)</x:f>
         <x:v>14</x:v>
       </x:c>
       <x:c r="S20" s="11" t="n">
@@ -53658,36 +53811,45 @@
         <x:v>600</x:v>
       </x:c>
       <x:c r="H21" s="15" t="n">
+        <x:f>ROUND(G21*1.5,0)</x:f>
         <x:v>900</x:v>
       </x:c>
       <x:c r="I21" s="15" t="n">
+        <x:f>ROUND(G21*3,0)</x:f>
         <x:v>1800</x:v>
       </x:c>
       <x:c r="J21" s="15" t="n">
+        <x:f>ROUND(G21*(3*1.15),0)</x:f>
         <x:v>2070</x:v>
       </x:c>
       <x:c r="K21" s="15" t="n">
         <x:v>35</x:v>
       </x:c>
       <x:c r="L21" s="15" t="n">
+        <x:f>ROUND(K21*1.5,0)</x:f>
         <x:v>53</x:v>
       </x:c>
       <x:c r="M21" s="15" t="n">
+        <x:f>ROUND(K21*3,0)</x:f>
         <x:v>105</x:v>
       </x:c>
       <x:c r="N21" s="15" t="n">
+        <x:f>ROUND(K21*(3*1.15),0)</x:f>
         <x:v>121</x:v>
       </x:c>
       <x:c r="O21" s="15" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="P21" s="15" t="n">
+        <x:f>ROUND(O21*1.5,0)</x:f>
         <x:v>8</x:v>
       </x:c>
       <x:c r="Q21" s="15" t="n">
+        <x:f>ROUND(O21*3,0)</x:f>
         <x:v>15</x:v>
       </x:c>
       <x:c r="R21" s="15" t="n">
+        <x:f>ROUND(O21*(3*1.15),0)</x:f>
         <x:v>17</x:v>
       </x:c>
       <x:c r="S21" s="15" t="n">
@@ -53745,36 +53907,45 @@
         <x:v>760</x:v>
       </x:c>
       <x:c r="H22" s="11" t="n">
+        <x:f>ROUND(G22*1.5,0)</x:f>
         <x:v>1140</x:v>
       </x:c>
       <x:c r="I22" s="11" t="n">
+        <x:f>ROUND(G22*3,0)</x:f>
         <x:v>2280</x:v>
       </x:c>
       <x:c r="J22" s="11" t="n">
+        <x:f>ROUND(G22*(3*1.15),0)</x:f>
         <x:v>2622</x:v>
       </x:c>
       <x:c r="K22" s="11" t="n">
         <x:v>70</x:v>
       </x:c>
       <x:c r="L22" s="11" t="n">
+        <x:f>ROUND(K22*1.5,0)</x:f>
         <x:v>105</x:v>
       </x:c>
       <x:c r="M22" s="11" t="n">
+        <x:f>ROUND(K22*3,0)</x:f>
         <x:v>210</x:v>
       </x:c>
       <x:c r="N22" s="11" t="n">
+        <x:f>ROUND(K22*(3*1.15),0)</x:f>
         <x:v>241</x:v>
       </x:c>
       <x:c r="O22" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="P22" s="11" t="n">
+        <x:f>ROUND(O22*1.5,0)</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="Q22" s="11" t="n">
+        <x:f>ROUND(O22*3,0)</x:f>
         <x:v>9</x:v>
       </x:c>
       <x:c r="R22" s="11" t="n">
+        <x:f>ROUND(O22*(3*1.15),0)</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="S22" s="11" t="n">
@@ -53832,36 +54003,45 @@
         <x:v>1200</x:v>
       </x:c>
       <x:c r="H23" s="15" t="n">
+        <x:f>ROUND(G23*1.5,0)</x:f>
         <x:v>1800</x:v>
       </x:c>
       <x:c r="I23" s="15" t="n">
+        <x:f>ROUND(G23*3,0)</x:f>
         <x:v>3600</x:v>
       </x:c>
       <x:c r="J23" s="15" t="n">
+        <x:f>ROUND(G23*(3*1.15),0)</x:f>
         <x:v>4140</x:v>
       </x:c>
       <x:c r="K23" s="15" t="n">
         <x:v>48</x:v>
       </x:c>
       <x:c r="L23" s="15" t="n">
+        <x:f>ROUND(K23*1.5,0)</x:f>
         <x:v>72</x:v>
       </x:c>
       <x:c r="M23" s="15" t="n">
+        <x:f>ROUND(K23*3,0)</x:f>
         <x:v>144</x:v>
       </x:c>
       <x:c r="N23" s="15" t="n">
+        <x:f>ROUND(K23*(3*1.15),0)</x:f>
         <x:v>166</x:v>
       </x:c>
       <x:c r="O23" s="15" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="P23" s="15" t="n">
+        <x:f>ROUND(O23*1.5,0)</x:f>
         <x:v>9</x:v>
       </x:c>
       <x:c r="Q23" s="15" t="n">
+        <x:f>ROUND(O23*3,0)</x:f>
         <x:v>18</x:v>
       </x:c>
       <x:c r="R23" s="15" t="n">
+        <x:f>ROUND(O23*(3*1.15),0)</x:f>
         <x:v>21</x:v>
       </x:c>
       <x:c r="S23" s="15" t="n">
@@ -53919,36 +54099,45 @@
         <x:v>1640</x:v>
       </x:c>
       <x:c r="H24" s="11" t="n">
+        <x:f>ROUND(G24*1.5,0)</x:f>
         <x:v>2460</x:v>
       </x:c>
       <x:c r="I24" s="11" t="n">
+        <x:f>ROUND(G24*3,0)</x:f>
         <x:v>4920</x:v>
       </x:c>
       <x:c r="J24" s="11" t="n">
+        <x:f>ROUND(G24*(3*1.15),0)</x:f>
         <x:v>5658</x:v>
       </x:c>
       <x:c r="K24" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="L24" s="11" t="n">
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="M24" s="11" t="n">
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="N24" s="11" t="n">
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="O24" s="11" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="P24" s="11" t="n">
+        <x:f>ROUND(O24*1.5,0)</x:f>
         <x:v>27</x:v>
       </x:c>
       <x:c r="Q24" s="11" t="n">
+        <x:f>ROUND(O24*3,0)</x:f>
         <x:v>54</x:v>
       </x:c>
       <x:c r="R24" s="11" t="n">
+        <x:f>ROUND(O24*(3*1.15),0)</x:f>
         <x:v>62</x:v>
       </x:c>
       <x:c r="S24" s="11" t="n">
@@ -54006,36 +54195,45 @@
         <x:v>720</x:v>
       </x:c>
       <x:c r="H25" s="15" t="n">
+        <x:f>ROUND(G25*1.5,0)</x:f>
         <x:v>1080</x:v>
       </x:c>
       <x:c r="I25" s="15" t="n">
+        <x:f>ROUND(G25*3,0)</x:f>
         <x:v>2160</x:v>
       </x:c>
       <x:c r="J25" s="15" t="n">
+        <x:f>ROUND(G25*(3*1.15),0)</x:f>
         <x:v>2484</x:v>
       </x:c>
       <x:c r="K25" s="15" t="n">
         <x:v>72</x:v>
       </x:c>
       <x:c r="L25" s="15" t="n">
+        <x:f>ROUND(K25*1.5,0)</x:f>
         <x:v>108</x:v>
       </x:c>
       <x:c r="M25" s="15" t="n">
+        <x:f>ROUND(K25*3,0)</x:f>
         <x:v>216</x:v>
       </x:c>
       <x:c r="N25" s="15" t="n">
+        <x:f>ROUND(K25*(3*1.15),0)</x:f>
         <x:v>248</x:v>
       </x:c>
       <x:c r="O25" s="15" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="P25" s="15" t="n">
+        <x:f>ROUND(O25*1.5,0)</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="Q25" s="15" t="n">
+        <x:f>ROUND(O25*3,0)</x:f>
         <x:v>9</x:v>
       </x:c>
       <x:c r="R25" s="15" t="n">
+        <x:f>ROUND(O25*(3*1.15),0)</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="S25" s="15" t="n">
@@ -54093,36 +54291,45 @@
         <x:v>1120</x:v>
       </x:c>
       <x:c r="H26" s="11" t="n">
+        <x:f>ROUND(G26*1.5,0)</x:f>
         <x:v>1680</x:v>
       </x:c>
       <x:c r="I26" s="11" t="n">
+        <x:f>ROUND(G26*3,0)</x:f>
         <x:v>3360</x:v>
       </x:c>
       <x:c r="J26" s="11" t="n">
+        <x:f>ROUND(G26*(3*1.15),0)</x:f>
         <x:v>3864</x:v>
       </x:c>
       <x:c r="K26" s="11" t="n">
         <x:v>64</x:v>
       </x:c>
       <x:c r="L26" s="11" t="n">
+        <x:f>ROUND(K26*1.5,0)</x:f>
         <x:v>96</x:v>
       </x:c>
       <x:c r="M26" s="11" t="n">
+        <x:f>ROUND(K26*3,0)</x:f>
         <x:v>192</x:v>
       </x:c>
       <x:c r="N26" s="11" t="n">
+        <x:f>ROUND(K26*(3*1.15),0)</x:f>
         <x:v>221</x:v>
       </x:c>
       <x:c r="O26" s="11" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="P26" s="11" t="n">
+        <x:f>ROUND(O26*1.5,0)</x:f>
         <x:v>15</x:v>
       </x:c>
       <x:c r="Q26" s="11" t="n">
+        <x:f>ROUND(O26*3,0)</x:f>
         <x:v>30</x:v>
       </x:c>
       <x:c r="R26" s="11" t="n">
+        <x:f>ROUND(O26*(3*1.15),0)</x:f>
         <x:v>35</x:v>
       </x:c>
       <x:c r="S26" s="11" t="n">
@@ -54180,36 +54387,45 @@
         <x:v>720</x:v>
       </x:c>
       <x:c r="H27" s="15" t="n">
+        <x:f>ROUND(G27*1.5,0)</x:f>
         <x:v>1080</x:v>
       </x:c>
       <x:c r="I27" s="15" t="n">
+        <x:f>ROUND(G27*3,0)</x:f>
         <x:v>2160</x:v>
       </x:c>
       <x:c r="J27" s="15" t="n">
+        <x:f>ROUND(G27*(3*1.15),0)</x:f>
         <x:v>2484</x:v>
       </x:c>
       <x:c r="K27" s="15" t="n">
         <x:v>55</x:v>
       </x:c>
       <x:c r="L27" s="15" t="n">
+        <x:f>ROUND(K27*1.5,0)</x:f>
         <x:v>83</x:v>
       </x:c>
       <x:c r="M27" s="15" t="n">
+        <x:f>ROUND(K27*3,0)</x:f>
         <x:v>165</x:v>
       </x:c>
       <x:c r="N27" s="15" t="n">
+        <x:f>ROUND(K27*(3*1.15),0)</x:f>
         <x:v>190</x:v>
       </x:c>
       <x:c r="O27" s="15" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="P27" s="15" t="n">
+        <x:f>ROUND(O27*1.5,0)</x:f>
         <x:v>11</x:v>
       </x:c>
       <x:c r="Q27" s="15" t="n">
+        <x:f>ROUND(O27*3,0)</x:f>
         <x:v>21</x:v>
       </x:c>
       <x:c r="R27" s="15" t="n">
+        <x:f>ROUND(O27*(3*1.15),0)</x:f>
         <x:v>24</x:v>
       </x:c>
       <x:c r="S27" s="15" t="n">
@@ -54269,36 +54485,45 @@
         <x:v>660</x:v>
       </x:c>
       <x:c r="H28" s="11" t="n">
+        <x:f>ROUND(G28*1.5,0)</x:f>
         <x:v>990</x:v>
       </x:c>
       <x:c r="I28" s="11" t="n">
+        <x:f>ROUND(G28*3,0)</x:f>
         <x:v>1980</x:v>
       </x:c>
       <x:c r="J28" s="11" t="n">
+        <x:f>ROUND(G28*(3*1.15),0)</x:f>
         <x:v>2277</x:v>
       </x:c>
       <x:c r="K28" s="11" t="n">
         <x:v>33</x:v>
       </x:c>
       <x:c r="L28" s="11" t="n">
+        <x:f>ROUND(K28*1.5,0)</x:f>
         <x:v>50</x:v>
       </x:c>
       <x:c r="M28" s="11" t="n">
+        <x:f>ROUND(K28*3,0)</x:f>
         <x:v>99</x:v>
       </x:c>
       <x:c r="N28" s="11" t="n">
+        <x:f>ROUND(K28*(3*1.15),0)</x:f>
         <x:v>114</x:v>
       </x:c>
       <x:c r="O28" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="P28" s="11" t="n">
+        <x:f>ROUND(O28*1.5,0)</x:f>
         <x:v>8</x:v>
       </x:c>
       <x:c r="Q28" s="11" t="n">
+        <x:f>ROUND(O28*3,0)</x:f>
         <x:v>15</x:v>
       </x:c>
       <x:c r="R28" s="11" t="n">
+        <x:f>ROUND(O28*(3*1.15),0)</x:f>
         <x:v>17</x:v>
       </x:c>
       <x:c r="S28" s="11" t="n">
@@ -54356,36 +54581,45 @@
         <x:v>600</x:v>
       </x:c>
       <x:c r="H29" s="15" t="n">
+        <x:f>ROUND(G29*1.5,0)</x:f>
         <x:v>900</x:v>
       </x:c>
       <x:c r="I29" s="15" t="n">
+        <x:f>ROUND(G29*3,0)</x:f>
         <x:v>1800</x:v>
       </x:c>
       <x:c r="J29" s="15" t="n">
+        <x:f>ROUND(G29*(3*1.5),0)</x:f>
         <x:v>2700</x:v>
       </x:c>
       <x:c r="K29" s="15" t="n">
         <x:v>24</x:v>
       </x:c>
       <x:c r="L29" s="15" t="n">
+        <x:f>ROUND(K29*1.5,0)</x:f>
         <x:v>36</x:v>
       </x:c>
       <x:c r="M29" s="15" t="n">
+        <x:f>ROUND(K29*3,0)</x:f>
         <x:v>72</x:v>
       </x:c>
       <x:c r="N29" s="15" t="n">
+        <x:f>ROUND(K29*(3*1.5),0)</x:f>
         <x:v>108</x:v>
       </x:c>
       <x:c r="O29" s="15" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="P29" s="15" t="n">
+        <x:f>ROUND(O29*1.5,0)</x:f>
         <x:v>3</x:v>
       </x:c>
       <x:c r="Q29" s="15" t="n">
+        <x:f>ROUND(O29*3,0)</x:f>
         <x:v>6</x:v>
       </x:c>
       <x:c r="R29" s="15" t="n">
+        <x:f>ROUND(O29*(3*1.5),0)</x:f>
         <x:v>9</x:v>
       </x:c>
       <x:c r="S29" s="15" t="n">
@@ -54443,36 +54677,45 @@
         <x:v>600</x:v>
       </x:c>
       <x:c r="H30" s="11" t="n">
+        <x:f>ROUND(G30*1.5,0)</x:f>
         <x:v>900</x:v>
       </x:c>
       <x:c r="I30" s="11" t="n">
+        <x:f>ROUND(G30*3,0)</x:f>
         <x:v>1800</x:v>
       </x:c>
       <x:c r="J30" s="11" t="n">
+        <x:f>ROUND(G30*(3*1.15),0)</x:f>
         <x:v>2070</x:v>
       </x:c>
       <x:c r="K30" s="11" t="n">
         <x:v>145</x:v>
       </x:c>
       <x:c r="L30" s="11" t="n">
+        <x:f>ROUND(K30*1.5,0)</x:f>
         <x:v>218</x:v>
       </x:c>
       <x:c r="M30" s="11" t="n">
+        <x:f>ROUND(K30*3,0)</x:f>
         <x:v>435</x:v>
       </x:c>
       <x:c r="N30" s="11" t="n">
+        <x:f>ROUND(K30*(3*1.15),0)</x:f>
         <x:v>500</x:v>
       </x:c>
       <x:c r="O30" s="11" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="P30" s="11" t="n">
+        <x:f>ROUND(O30*1.5,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q30" s="11" t="n">
+        <x:f>ROUND(O30*3,0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="R30" s="11" t="n">
+        <x:f>ROUND(O30*(3*1.15),0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="S30" s="11" t="n">
@@ -54530,36 +54773,45 @@
         <x:v>760</x:v>
       </x:c>
       <x:c r="H31" s="15" t="n">
+        <x:f>ROUND(G31*1.5,0)</x:f>
         <x:v>1140</x:v>
       </x:c>
       <x:c r="I31" s="15" t="n">
+        <x:f>ROUND(G31*3,0)</x:f>
         <x:v>2280</x:v>
       </x:c>
       <x:c r="J31" s="15" t="n">
+        <x:f>ROUND(G31*(3*1.15),0)</x:f>
         <x:v>2622</x:v>
       </x:c>
       <x:c r="K31" s="15" t="n">
         <x:v>66</x:v>
       </x:c>
       <x:c r="L31" s="15" t="n">
+        <x:f>ROUND(K31*1.5,0)</x:f>
         <x:v>99</x:v>
       </x:c>
       <x:c r="M31" s="15" t="n">
+        <x:f>ROUND(K31*3,0)</x:f>
         <x:v>198</x:v>
       </x:c>
       <x:c r="N31" s="15" t="n">
+        <x:f>ROUND(K31*(3*1.15),0)</x:f>
         <x:v>228</x:v>
       </x:c>
       <x:c r="O31" s="15" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="P31" s="15" t="n">
+        <x:f>ROUND(O31*1.5,0)</x:f>
         <x:v>6</x:v>
       </x:c>
       <x:c r="Q31" s="15" t="n">
+        <x:f>ROUND(O31*3,0)</x:f>
         <x:v>12</x:v>
       </x:c>
       <x:c r="R31" s="15" t="n">
+        <x:f>ROUND(O31*(3*1.15),0)</x:f>
         <x:v>14</x:v>
       </x:c>
       <x:c r="S31" s="15" t="n">
@@ -54617,36 +54869,45 @@
         <x:v>840</x:v>
       </x:c>
       <x:c r="H32" s="11" t="n">
+        <x:f>ROUND(G32*1.5,0)</x:f>
         <x:v>1260</x:v>
       </x:c>
       <x:c r="I32" s="11" t="n">
+        <x:f>ROUND(G32*3,0)</x:f>
         <x:v>2520</x:v>
       </x:c>
       <x:c r="J32" s="11" t="n">
+        <x:f>ROUND(G32*(3*1.15),0)</x:f>
         <x:v>2898</x:v>
       </x:c>
       <x:c r="K32" s="11" t="n">
         <x:v>57</x:v>
       </x:c>
       <x:c r="L32" s="11" t="n">
+        <x:f>ROUND(K32*1.5,0)</x:f>
         <x:v>86</x:v>
       </x:c>
       <x:c r="M32" s="11" t="n">
+        <x:f>ROUND(K32*3,0)</x:f>
         <x:v>171</x:v>
       </x:c>
       <x:c r="N32" s="11" t="n">
+        <x:f>ROUND(K32*(3*1.15),0)</x:f>
         <x:v>197</x:v>
       </x:c>
       <x:c r="O32" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="P32" s="11" t="n">
+        <x:f>ROUND(O32*1.5,0)</x:f>
         <x:v>11</x:v>
       </x:c>
       <x:c r="Q32" s="11" t="n">
+        <x:f>ROUND(O32*3,0)</x:f>
         <x:v>21</x:v>
       </x:c>
       <x:c r="R32" s="11" t="n">
+        <x:f>ROUND(O32*(3*1.15),0)</x:f>
         <x:v>24</x:v>
       </x:c>
       <x:c r="S32" s="11" t="n">
@@ -54704,36 +54965,45 @@
         <x:v>800</x:v>
       </x:c>
       <x:c r="H33" s="15" t="n">
+        <x:f>ROUND(G33*1.5,0)</x:f>
         <x:v>1200</x:v>
       </x:c>
       <x:c r="I33" s="15" t="n">
+        <x:f>ROUND(G33*3,0)</x:f>
         <x:v>2400</x:v>
       </x:c>
       <x:c r="J33" s="15" t="n">
+        <x:f>ROUND(G33*(3*1.15),0)</x:f>
         <x:v>2760</x:v>
       </x:c>
       <x:c r="K33" s="15" t="n">
         <x:v>62</x:v>
       </x:c>
       <x:c r="L33" s="15" t="n">
+        <x:f>ROUND(K33*1.5,0)</x:f>
         <x:v>93</x:v>
       </x:c>
       <x:c r="M33" s="15" t="n">
+        <x:f>ROUND(K33*3,0)</x:f>
         <x:v>186</x:v>
       </x:c>
       <x:c r="N33" s="15" t="n">
+        <x:f>ROUND(K33*(3*1.15),0)</x:f>
         <x:v>214</x:v>
       </x:c>
       <x:c r="O33" s="15" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="P33" s="15" t="n">
+        <x:f>ROUND(O33*1.5,0)</x:f>
         <x:v>9</x:v>
       </x:c>
       <x:c r="Q33" s="15" t="n">
+        <x:f>ROUND(O33*3,0)</x:f>
         <x:v>18</x:v>
       </x:c>
       <x:c r="R33" s="15" t="n">
+        <x:f>ROUND(O33*(3*1.15),0)</x:f>
         <x:v>21</x:v>
       </x:c>
       <x:c r="S33" s="15" t="n">
@@ -54791,36 +55061,45 @@
         <x:v>1500</x:v>
       </x:c>
       <x:c r="H34" s="11" t="n">
+        <x:f>ROUND(G34*1.5,0)</x:f>
         <x:v>2250</x:v>
       </x:c>
       <x:c r="I34" s="11" t="n">
+        <x:f>ROUND(G34*3,0)</x:f>
         <x:v>4500</x:v>
       </x:c>
       <x:c r="J34" s="11" t="n">
+        <x:f>ROUND(G34*(3*1.15),0)</x:f>
         <x:v>5175</x:v>
       </x:c>
       <x:c r="K34" s="11" t="n">
         <x:v>50</x:v>
       </x:c>
       <x:c r="L34" s="11" t="n">
+        <x:f>ROUND(K34*1.5,0)</x:f>
         <x:v>75</x:v>
       </x:c>
       <x:c r="M34" s="11" t="n">
+        <x:f>ROUND(K34*3,0)</x:f>
         <x:v>150</x:v>
       </x:c>
       <x:c r="N34" s="11" t="n">
+        <x:f>ROUND(K34*(3*1.15),0)</x:f>
         <x:v>173</x:v>
       </x:c>
       <x:c r="O34" s="11" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="P34" s="11" t="n">
+        <x:f>ROUND(O34*1.5,0)</x:f>
         <x:v>32</x:v>
       </x:c>
       <x:c r="Q34" s="11" t="n">
+        <x:f>ROUND(O34*3,0)</x:f>
         <x:v>63</x:v>
       </x:c>
       <x:c r="R34" s="11" t="n">
+        <x:f>ROUND(O34*(3*1.15),0)</x:f>
         <x:v>72</x:v>
       </x:c>
       <x:c r="S34" s="11" t="n">
@@ -54878,36 +55157,45 @@
         <x:v>1600</x:v>
       </x:c>
       <x:c r="H35" s="15" t="n">
+        <x:f>ROUND(G35*1.5,0)</x:f>
         <x:v>2400</x:v>
       </x:c>
       <x:c r="I35" s="15" t="n">
+        <x:f>ROUND(G35*3,0)</x:f>
         <x:v>4800</x:v>
       </x:c>
       <x:c r="J35" s="15" t="n">
+        <x:f>ROUND(G35*(3*1.15),0)</x:f>
         <x:v>5520</x:v>
       </x:c>
       <x:c r="K35" s="15" t="n">
         <x:v>110</x:v>
       </x:c>
       <x:c r="L35" s="15" t="n">
+        <x:f>ROUND(K35*1.5,0)</x:f>
         <x:v>165</x:v>
       </x:c>
       <x:c r="M35" s="15" t="n">
+        <x:f>ROUND(K35*3,0)</x:f>
         <x:v>330</x:v>
       </x:c>
       <x:c r="N35" s="15" t="n">
+        <x:f>ROUND(K35*(3*1.15),0)</x:f>
         <x:v>379</x:v>
       </x:c>
       <x:c r="O35" s="15" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="P35" s="15" t="n">
+        <x:f>ROUND(O35*1.5,0)</x:f>
         <x:v>27</x:v>
       </x:c>
       <x:c r="Q35" s="15" t="n">
+        <x:f>ROUND(O35*3,0)</x:f>
         <x:v>54</x:v>
       </x:c>
       <x:c r="R35" s="15" t="n">
+        <x:f>ROUND(O35*(3*1.15),0)</x:f>
         <x:v>62</x:v>
       </x:c>
       <x:c r="S35" s="15" t="n">
@@ -54967,36 +55255,45 @@
         <x:v>650</x:v>
       </x:c>
       <x:c r="H36" s="11" t="n">
+        <x:f>ROUND(G36*1.5,0)</x:f>
         <x:v>975</x:v>
       </x:c>
       <x:c r="I36" s="11" t="n">
+        <x:f>ROUND(G36*3,0)</x:f>
         <x:v>1950</x:v>
       </x:c>
       <x:c r="J36" s="11" t="n">
+        <x:f>ROUND(G36*(3*1.15),0)</x:f>
         <x:v>2243</x:v>
       </x:c>
       <x:c r="K36" s="11" t="n">
         <x:v>31</x:v>
       </x:c>
       <x:c r="L36" s="11" t="n">
+        <x:f>ROUND(K36*1.5,0)</x:f>
         <x:v>47</x:v>
       </x:c>
       <x:c r="M36" s="11" t="n">
+        <x:f>ROUND(K36*3,0)</x:f>
         <x:v>93</x:v>
       </x:c>
       <x:c r="N36" s="11" t="n">
+        <x:f>ROUND(K36*(3*1.15),0)</x:f>
         <x:v>107</x:v>
       </x:c>
       <x:c r="O36" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="P36" s="11" t="n">
+        <x:f>ROUND(O36*1.5,0)</x:f>
         <x:v>11</x:v>
       </x:c>
       <x:c r="Q36" s="11" t="n">
+        <x:f>ROUND(O36*3,0)</x:f>
         <x:v>21</x:v>
       </x:c>
       <x:c r="R36" s="11" t="n">
+        <x:f>ROUND(O36*(3*1.15),0)</x:f>
         <x:v>24</x:v>
       </x:c>
       <x:c r="S36" s="11" t="n">
@@ -55054,36 +55351,45 @@
         <x:v>540</x:v>
       </x:c>
       <x:c r="H37" s="15" t="n">
+        <x:f>ROUND(G37*1.5,0)</x:f>
         <x:v>810</x:v>
       </x:c>
       <x:c r="I37" s="15" t="n">
+        <x:f>ROUND(G37*3,0)</x:f>
         <x:v>1620</x:v>
       </x:c>
       <x:c r="J37" s="15" t="n">
+        <x:f>ROUND(G37*(3*1.15),0)</x:f>
         <x:v>1863</x:v>
       </x:c>
       <x:c r="K37" s="15" t="n">
         <x:v>28</x:v>
       </x:c>
       <x:c r="L37" s="15" t="n">
+        <x:f>ROUND(K37*1.5,0)</x:f>
         <x:v>42</x:v>
       </x:c>
       <x:c r="M37" s="15" t="n">
+        <x:f>ROUND(K37*3,0)</x:f>
         <x:v>84</x:v>
       </x:c>
       <x:c r="N37" s="15" t="n">
+        <x:f>ROUND(K37*(3*1.15),0)</x:f>
         <x:v>97</x:v>
       </x:c>
       <x:c r="O37" s="15" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="P37" s="15" t="n">
+        <x:f>ROUND(O37*1.5,0)</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="Q37" s="15" t="n">
+        <x:f>ROUND(O37*3,0)</x:f>
         <x:v>9</x:v>
       </x:c>
       <x:c r="R37" s="15" t="n">
+        <x:f>ROUND(O37*(3*1.15),0)</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="S37" s="15" t="n">
@@ -55141,36 +55447,45 @@
         <x:v>980</x:v>
       </x:c>
       <x:c r="H38" s="11" t="n">
+        <x:f>ROUND(G38*1.5,0)</x:f>
         <x:v>1470</x:v>
       </x:c>
       <x:c r="I38" s="11" t="n">
+        <x:f>ROUND(G38*3,0)</x:f>
         <x:v>2940</x:v>
       </x:c>
       <x:c r="J38" s="11" t="n">
+        <x:f>ROUND(G38*(3*1.15),0)</x:f>
         <x:v>3381</x:v>
       </x:c>
       <x:c r="K38" s="11" t="n">
         <x:v>52</x:v>
       </x:c>
       <x:c r="L38" s="11" t="n">
+        <x:f>ROUND(K38*1.5,0)</x:f>
         <x:v>78</x:v>
       </x:c>
       <x:c r="M38" s="11" t="n">
+        <x:f>ROUND(K38*3,0)</x:f>
         <x:v>156</x:v>
       </x:c>
       <x:c r="N38" s="11" t="n">
+        <x:f>ROUND(K38*(3*1.15),0)</x:f>
         <x:v>179</x:v>
       </x:c>
       <x:c r="O38" s="11" t="n">
         <x:v>9</x:v>
       </x:c>
       <x:c r="P38" s="11" t="n">
+        <x:f>ROUND(O38*1.5,0)</x:f>
         <x:v>14</x:v>
       </x:c>
       <x:c r="Q38" s="11" t="n">
+        <x:f>ROUND(O38*3,0)</x:f>
         <x:v>27</x:v>
       </x:c>
       <x:c r="R38" s="11" t="n">
+        <x:f>ROUND(O38*(3*1.15),0)</x:f>
         <x:v>31</x:v>
       </x:c>
       <x:c r="S38" s="11" t="n">
@@ -55228,36 +55543,45 @@
         <x:v>760</x:v>
       </x:c>
       <x:c r="H39" s="15" t="n">
+        <x:f>ROUND(G39*1.5,0)</x:f>
         <x:v>1140</x:v>
       </x:c>
       <x:c r="I39" s="15" t="n">
+        <x:f>ROUND(G39*3,0)</x:f>
         <x:v>2280</x:v>
       </x:c>
       <x:c r="J39" s="15" t="n">
+        <x:f>ROUND(G39*(3*1.15),0)</x:f>
         <x:v>2622</x:v>
       </x:c>
       <x:c r="K39" s="15" t="n">
         <x:v>56</x:v>
       </x:c>
       <x:c r="L39" s="15" t="n">
+        <x:f>ROUND(K39*1.5,0)</x:f>
         <x:v>84</x:v>
       </x:c>
       <x:c r="M39" s="15" t="n">
+        <x:f>ROUND(K39*3,0)</x:f>
         <x:v>168</x:v>
       </x:c>
       <x:c r="N39" s="15" t="n">
+        <x:f>ROUND(K39*(3*1.15),0)</x:f>
         <x:v>193</x:v>
       </x:c>
       <x:c r="O39" s="15" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="P39" s="15" t="n">
+        <x:f>ROUND(O39*1.5,0)</x:f>
         <x:v>6</x:v>
       </x:c>
       <x:c r="Q39" s="15" t="n">
+        <x:f>ROUND(O39*3,0)</x:f>
         <x:v>12</x:v>
       </x:c>
       <x:c r="R39" s="15" t="n">
+        <x:f>ROUND(O39*(3*1.15),0)</x:f>
         <x:v>14</x:v>
       </x:c>
       <x:c r="S39" s="15" t="n">
@@ -55315,36 +55639,45 @@
         <x:v>1180</x:v>
       </x:c>
       <x:c r="H40" s="11" t="n">
+        <x:f>ROUND(G40*1.5,0)</x:f>
         <x:v>1770</x:v>
       </x:c>
       <x:c r="I40" s="11" t="n">
+        <x:f>ROUND(G40*3,0)</x:f>
         <x:v>3540</x:v>
       </x:c>
       <x:c r="J40" s="11" t="n">
+        <x:f>ROUND(G40*(3*1.15),0)</x:f>
         <x:v>4071</x:v>
       </x:c>
       <x:c r="K40" s="11" t="n">
         <x:v>54</x:v>
       </x:c>
       <x:c r="L40" s="11" t="n">
+        <x:f>ROUND(K40*1.5,0)</x:f>
         <x:v>81</x:v>
       </x:c>
       <x:c r="M40" s="11" t="n">
+        <x:f>ROUND(K40*3,0)</x:f>
         <x:v>162</x:v>
       </x:c>
       <x:c r="N40" s="11" t="n">
+        <x:f>ROUND(K40*(3*1.15),0)</x:f>
         <x:v>186</x:v>
       </x:c>
       <x:c r="O40" s="11" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="P40" s="11" t="n">
+        <x:f>ROUND(O40*1.5,0)</x:f>
         <x:v>18</x:v>
       </x:c>
       <x:c r="Q40" s="11" t="n">
+        <x:f>ROUND(O40*3,0)</x:f>
         <x:v>36</x:v>
       </x:c>
       <x:c r="R40" s="11" t="n">
+        <x:f>ROUND(O40*(3*1.15),0)</x:f>
         <x:v>41</x:v>
       </x:c>
       <x:c r="S40" s="11" t="n">
@@ -55402,36 +55735,45 @@
         <x:v>780</x:v>
       </x:c>
       <x:c r="H41" s="15" t="n">
+        <x:f>ROUND(G41*1.5,0)</x:f>
         <x:v>1170</x:v>
       </x:c>
       <x:c r="I41" s="15" t="n">
+        <x:f>ROUND(G41*3,0)</x:f>
         <x:v>2340</x:v>
       </x:c>
       <x:c r="J41" s="15" t="n">
+        <x:f>ROUND(G41*(3*1.15),0)</x:f>
         <x:v>2691</x:v>
       </x:c>
       <x:c r="K41" s="15" t="n">
         <x:v>68</x:v>
       </x:c>
       <x:c r="L41" s="15" t="n">
+        <x:f>ROUND(K41*1.5,0)</x:f>
         <x:v>102</x:v>
       </x:c>
       <x:c r="M41" s="15" t="n">
+        <x:f>ROUND(K41*3,0)</x:f>
         <x:v>204</x:v>
       </x:c>
       <x:c r="N41" s="15" t="n">
+        <x:f>ROUND(K41*(3*1.15),0)</x:f>
         <x:v>235</x:v>
       </x:c>
       <x:c r="O41" s="15" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="P41" s="15" t="n">
+        <x:f>ROUND(O41*1.5,0)</x:f>
         <x:v>6</x:v>
       </x:c>
       <x:c r="Q41" s="15" t="n">
+        <x:f>ROUND(O41*3,0)</x:f>
         <x:v>12</x:v>
       </x:c>
       <x:c r="R41" s="15" t="n">
+        <x:f>ROUND(O41*(3*1.15),0)</x:f>
         <x:v>14</x:v>
       </x:c>
       <x:c r="S41" s="15" t="n">
@@ -55489,36 +55831,45 @@
         <x:v>1500</x:v>
       </x:c>
       <x:c r="H42" s="11" t="n">
+        <x:f>ROUND(G42*1.5,0)</x:f>
         <x:v>2250</x:v>
       </x:c>
       <x:c r="I42" s="11" t="n">
+        <x:f>ROUND(G42*3,0)</x:f>
         <x:v>4500</x:v>
       </x:c>
       <x:c r="J42" s="11" t="n">
+        <x:f>ROUND(G42*(3*1.15),0)</x:f>
         <x:v>5175</x:v>
       </x:c>
       <x:c r="K42" s="11" t="n">
         <x:v>104</x:v>
       </x:c>
       <x:c r="L42" s="11" t="n">
+        <x:f>ROUND(K42*1.5,0)</x:f>
         <x:v>156</x:v>
       </x:c>
       <x:c r="M42" s="11" t="n">
+        <x:f>ROUND(K42*3,0)</x:f>
         <x:v>312</x:v>
       </x:c>
       <x:c r="N42" s="11" t="n">
+        <x:f>ROUND(K42*(3*1.15),0)</x:f>
         <x:v>359</x:v>
       </x:c>
       <x:c r="O42" s="11" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="P42" s="11" t="n">
+        <x:f>ROUND(O42*1.5,0)</x:f>
         <x:v>15</x:v>
       </x:c>
       <x:c r="Q42" s="11" t="n">
+        <x:f>ROUND(O42*3,0)</x:f>
         <x:v>30</x:v>
       </x:c>
       <x:c r="R42" s="11" t="n">
+        <x:f>ROUND(O42*(3*1.15),0)</x:f>
         <x:v>35</x:v>
       </x:c>
       <x:c r="S42" s="11" t="n">
@@ -55576,36 +55927,45 @@
         <x:v>1720</x:v>
       </x:c>
       <x:c r="H43" s="15" t="n">
+        <x:f>ROUND(G43*1.5,0)</x:f>
         <x:v>2580</x:v>
       </x:c>
       <x:c r="I43" s="15" t="n">
+        <x:f>ROUND(G43*3,0)</x:f>
         <x:v>5160</x:v>
       </x:c>
       <x:c r="J43" s="15" t="n">
+        <x:f>ROUND(G43*(3*1.15),0)</x:f>
         <x:v>5934</x:v>
       </x:c>
       <x:c r="K43" s="15" t="n">
         <x:v>82</x:v>
       </x:c>
       <x:c r="L43" s="15" t="n">
+        <x:f>ROUND(K43*1.5,0)</x:f>
         <x:v>123</x:v>
       </x:c>
       <x:c r="M43" s="15" t="n">
+        <x:f>ROUND(K43*3,0)</x:f>
         <x:v>246</x:v>
       </x:c>
       <x:c r="N43" s="15" t="n">
+        <x:f>ROUND(K43*(3*1.15),0)</x:f>
         <x:v>283</x:v>
       </x:c>
       <x:c r="O43" s="15" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="P43" s="15" t="n">
+        <x:f>ROUND(O43*1.5,0)</x:f>
         <x:v>24</x:v>
       </x:c>
       <x:c r="Q43" s="15" t="n">
+        <x:f>ROUND(O43*3,0)</x:f>
         <x:v>48</x:v>
       </x:c>
       <x:c r="R43" s="15" t="n">
+        <x:f>ROUND(O43*(3*1.15),0)</x:f>
         <x:v>55</x:v>
       </x:c>
       <x:c r="S43" s="15" t="n">
@@ -55679,7 +56039,7 @@
     </x:row>
     <x:row r="2" ht="36" customHeight="1">
       <x:c r="A2" s="4" t="str">
-        <x:v>名称、货币和价格必须与 90_运行配置的 data/shop.json 一致。新商品先在本页与机器页登记，再导出运行目录。</x:v>
+        <x:v>商城商品由 data/shop.json 管理；此页与 JSON 保持一致，发布检查会核对名称、货币、价格及上架状态。</x:v>
       </x:c>
       <x:c r="B2" s="4"/>
       <x:c r="C2" s="4"/>
@@ -58082,7 +58442,7 @@
     </x:row>
     <x:row r="2" ht="32" customHeight="1">
       <x:c r="A2" s="4" t="str">
-        <x:v>宠物效果与详细说明取指定新表；商品 ID、货币、价格和是否展示取 data/shop.json。服务端实际售卖目录及价格须上线前再核。</x:v>
+        <x:v>编辑 E 列效果百分比时，同步修改 F、N 列的说明百分比；工具会阻止文案与效果不一致。商品价格仍由 data/shop.json 管理。</x:v>
       </x:c>
       <x:c r="B2" s="4"/>
       <x:c r="C2" s="4"/>
@@ -58844,7 +59204,7 @@
     </x:row>
     <x:row r="2" ht="32" customHeight="1">
       <x:c r="A2" s="4" t="str">
-        <x:v>16 只野怪的基础值与战斗探针结论；回合成长另见回合页。</x:v>
+        <x:v>编辑 E–G 列基础 HP / 攻击 / 防御；回合成长和技能机制由 data/pve/pve_monsters.json 管理。运行前执行同步工具。</x:v>
       </x:c>
       <x:c r="B2" s="4"/>
       <x:c r="C2" s="4"/>
@@ -60000,7 +60360,7 @@
     </x:row>
     <x:row r="2" ht="32" customHeight="1">
       <x:c r="A2" s="4" t="str">
-        <x:v>9 种 Boss；R5/R10/R15/R20 数值沿用指定新表的本机运行结果。</x:v>
+        <x:v>编辑首场 HP / 攻击（D、E 列）和 R5 防御（O 列）；游戏 JSON 保存乘以 1.5 前的整数基础值。其余回合数值由公式按现有成长倍率推算。</x:v>
       </x:c>
       <x:c r="B2" s="4"/>
       <x:c r="C2" s="4"/>
@@ -60136,41 +60496,55 @@
       <x:c r="E4" s="11" t="n">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="F4" s="11"/>
+      <x:c r="F4" s="11" t="n">
+        <x:f>O4</x:f>
+        <x:v>15</x:v>
+      </x:c>
       <x:c r="G4" s="11" t="n">
+        <x:f>D4</x:f>
         <x:v>3300</x:v>
       </x:c>
       <x:c r="H4" s="11" t="n">
+        <x:f>ROUND(ROUND(D4/1.5,0)*1.5*1.45,0)</x:f>
         <x:v>4785</x:v>
       </x:c>
       <x:c r="I4" s="11" t="n">
+        <x:f>ROUND(ROUND(D4/1.5,0)*1.5*2.1025,0)</x:f>
         <x:v>6938</x:v>
       </x:c>
       <x:c r="J4" s="11" t="n">
+        <x:f>ROUND(ROUND(D4/1.5,0)*1.5*3.048625,0)</x:f>
         <x:v>10060</x:v>
       </x:c>
       <x:c r="K4" s="11" t="n">
+        <x:f>E4</x:f>
         <x:v>113</x:v>
       </x:c>
       <x:c r="L4" s="11" t="n">
+        <x:f>ROUND(ROUND(E4/1.5,0)*1.5*1.35,0)</x:f>
         <x:v>152</x:v>
       </x:c>
       <x:c r="M4" s="11" t="n">
+        <x:f>ROUND(ROUND(E4/1.5,0)*1.5*1.8225,0)</x:f>
         <x:v>205</x:v>
       </x:c>
       <x:c r="N4" s="11" t="n">
+        <x:f>ROUND(ROUND(E4/1.5,0)*1.5*2.460375,0)</x:f>
         <x:v>277</x:v>
       </x:c>
       <x:c r="O4" s="11" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="P4" s="11" t="n">
+        <x:f>ROUND(ROUND(O4/1.5,0)*1.5*1.3,0)</x:f>
         <x:v>20</x:v>
       </x:c>
       <x:c r="Q4" s="11" t="n">
+        <x:f>ROUND(ROUND(O4/1.5,0)*1.5*1.69,0)</x:f>
         <x:v>25</x:v>
       </x:c>
       <x:c r="R4" s="11" t="n">
+        <x:f>ROUND(ROUND(O4/1.5,0)*1.5*2.197,0)</x:f>
         <x:v>33</x:v>
       </x:c>
       <x:c r="S4" s="11" t="n">
@@ -60225,41 +60599,55 @@
       <x:c r="E5" s="15" t="n">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="F5" s="15"/>
+      <x:c r="F5" s="15" t="n">
+        <x:f>O5</x:f>
+        <x:v>23</x:v>
+      </x:c>
       <x:c r="G5" s="15" t="n">
+        <x:f>D5</x:f>
         <x:v>3750</x:v>
       </x:c>
       <x:c r="H5" s="15" t="n">
+        <x:f>ROUND(ROUND(D5/1.5,0)*1.5*1.45,0)</x:f>
         <x:v>5438</x:v>
       </x:c>
       <x:c r="I5" s="15" t="n">
+        <x:f>ROUND(ROUND(D5/1.5,0)*1.5*2.1025,0)</x:f>
         <x:v>7884</x:v>
       </x:c>
       <x:c r="J5" s="15" t="n">
+        <x:f>ROUND(ROUND(D5/1.5,0)*1.5*3.048625,0)</x:f>
         <x:v>11432</x:v>
       </x:c>
       <x:c r="K5" s="15" t="n">
+        <x:f>E5</x:f>
         <x:v>92</x:v>
       </x:c>
       <x:c r="L5" s="15" t="n">
+        <x:f>ROUND(ROUND(E5/1.5,0)*1.5*1.35,0)</x:f>
         <x:v>124</x:v>
       </x:c>
       <x:c r="M5" s="15" t="n">
+        <x:f>ROUND(ROUND(E5/1.5,0)*1.5*1.8225,0)</x:f>
         <x:v>167</x:v>
       </x:c>
       <x:c r="N5" s="15" t="n">
+        <x:f>ROUND(ROUND(E5/1.5,0)*1.5*2.460375,0)</x:f>
         <x:v>225</x:v>
       </x:c>
       <x:c r="O5" s="15" t="n">
         <x:v>23</x:v>
       </x:c>
       <x:c r="P5" s="15" t="n">
+        <x:f>ROUND(ROUND(O5/1.5,0)*1.5*1.3,0)</x:f>
         <x:v>29</x:v>
       </x:c>
       <x:c r="Q5" s="15" t="n">
+        <x:f>ROUND(ROUND(O5/1.5,0)*1.5*1.69,0)</x:f>
         <x:v>38</x:v>
       </x:c>
       <x:c r="R5" s="15" t="n">
+        <x:f>ROUND(ROUND(O5/1.5,0)*1.5*2.197,0)</x:f>
         <x:v>49</x:v>
       </x:c>
       <x:c r="S5" s="15" t="n">
@@ -60315,41 +60703,55 @@
       <x:c r="E6" s="11" t="n">
         <x:v>116</x:v>
       </x:c>
-      <x:c r="F6" s="11"/>
+      <x:c r="F6" s="11" t="n">
+        <x:f>O6</x:f>
+        <x:v>12</x:v>
+      </x:c>
       <x:c r="G6" s="11" t="n">
+        <x:f>D6</x:f>
         <x:v>2700</x:v>
       </x:c>
       <x:c r="H6" s="11" t="n">
+        <x:f>ROUND(ROUND(D6/1.5,0)*1.5*1.45,0)</x:f>
         <x:v>3915</x:v>
       </x:c>
       <x:c r="I6" s="11" t="n">
+        <x:f>ROUND(ROUND(D6/1.5,0)*1.5*2.1025,0)</x:f>
         <x:v>5677</x:v>
       </x:c>
       <x:c r="J6" s="11" t="n">
+        <x:f>ROUND(ROUND(D6/1.5,0)*1.5*3.048625,0)</x:f>
         <x:v>8231</x:v>
       </x:c>
       <x:c r="K6" s="11" t="n">
+        <x:f>E6</x:f>
         <x:v>116</x:v>
       </x:c>
       <x:c r="L6" s="11" t="n">
+        <x:f>ROUND(ROUND(E6/1.5,0)*1.5*1.35,0)</x:f>
         <x:v>156</x:v>
       </x:c>
       <x:c r="M6" s="11" t="n">
+        <x:f>ROUND(ROUND(E6/1.5,0)*1.5*1.8225,0)</x:f>
         <x:v>210</x:v>
       </x:c>
       <x:c r="N6" s="11" t="n">
+        <x:f>ROUND(ROUND(E6/1.5,0)*1.5*2.460375,0)</x:f>
         <x:v>284</x:v>
       </x:c>
       <x:c r="O6" s="11" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="P6" s="11" t="n">
+        <x:f>ROUND(ROUND(O6/1.5,0)*1.5*1.3,0)</x:f>
         <x:v>16</x:v>
       </x:c>
       <x:c r="Q6" s="11" t="n">
+        <x:f>ROUND(ROUND(O6/1.5,0)*1.5*1.69,0)</x:f>
         <x:v>20</x:v>
       </x:c>
       <x:c r="R6" s="11" t="n">
+        <x:f>ROUND(ROUND(O6/1.5,0)*1.5*2.197,0)</x:f>
         <x:v>26</x:v>
       </x:c>
       <x:c r="S6" s="11" t="n">
@@ -60406,41 +60808,55 @@
       <x:c r="E7" s="15" t="n">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="F7" s="15"/>
+      <x:c r="F7" s="15" t="n">
+        <x:f>O7</x:f>
+        <x:v>15</x:v>
+      </x:c>
       <x:c r="G7" s="15" t="n">
+        <x:f>D7</x:f>
         <x:v>3000</x:v>
       </x:c>
       <x:c r="H7" s="15" t="n">
+        <x:f>ROUND(ROUND(D7/1.5,0)*1.5*1.45,0)</x:f>
         <x:v>4350</x:v>
       </x:c>
       <x:c r="I7" s="15" t="n">
+        <x:f>ROUND(ROUND(D7/1.5,0)*1.5*2.1025,0)</x:f>
         <x:v>6308</x:v>
       </x:c>
       <x:c r="J7" s="15" t="n">
+        <x:f>ROUND(ROUND(D7/1.5,0)*1.5*3.048625,0)</x:f>
         <x:v>9146</x:v>
       </x:c>
       <x:c r="K7" s="15" t="n">
+        <x:f>E7</x:f>
         <x:v>75</x:v>
       </x:c>
       <x:c r="L7" s="15" t="n">
+        <x:f>ROUND(ROUND(E7/1.5,0)*1.5*1.35,0)</x:f>
         <x:v>101</x:v>
       </x:c>
       <x:c r="M7" s="15" t="n">
+        <x:f>ROUND(ROUND(E7/1.5,0)*1.5*1.8225,0)</x:f>
         <x:v>137</x:v>
       </x:c>
       <x:c r="N7" s="15" t="n">
+        <x:f>ROUND(ROUND(E7/1.5,0)*1.5*2.460375,0)</x:f>
         <x:v>185</x:v>
       </x:c>
       <x:c r="O7" s="15" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="P7" s="15" t="n">
+        <x:f>ROUND(ROUND(O7/1.5,0)*1.5*1.3,0)</x:f>
         <x:v>20</x:v>
       </x:c>
       <x:c r="Q7" s="15" t="n">
+        <x:f>ROUND(ROUND(O7/1.5,0)*1.5*1.69,0)</x:f>
         <x:v>25</x:v>
       </x:c>
       <x:c r="R7" s="15" t="n">
+        <x:f>ROUND(ROUND(O7/1.5,0)*1.5*2.197,0)</x:f>
         <x:v>33</x:v>
       </x:c>
       <x:c r="S7" s="15" t="n">
@@ -60496,41 +60912,55 @@
       <x:c r="E8" s="11" t="n">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="F8" s="11"/>
+      <x:c r="F8" s="11" t="n">
+        <x:f>O8</x:f>
+        <x:v>8</x:v>
+      </x:c>
       <x:c r="G8" s="11" t="n">
+        <x:f>D8</x:f>
         <x:v>2850</x:v>
       </x:c>
       <x:c r="H8" s="11" t="n">
+        <x:f>ROUND(ROUND(D8/1.5,0)*1.5*1.45,0)</x:f>
         <x:v>4133</x:v>
       </x:c>
       <x:c r="I8" s="11" t="n">
+        <x:f>ROUND(ROUND(D8/1.5,0)*1.5*2.1025,0)</x:f>
         <x:v>5992</x:v>
       </x:c>
       <x:c r="J8" s="11" t="n">
+        <x:f>ROUND(ROUND(D8/1.5,0)*1.5*3.048625,0)</x:f>
         <x:v>8689</x:v>
       </x:c>
       <x:c r="K8" s="11" t="n">
+        <x:f>E8</x:f>
         <x:v>83</x:v>
       </x:c>
       <x:c r="L8" s="11" t="n">
+        <x:f>ROUND(ROUND(E8/1.5,0)*1.5*1.35,0)</x:f>
         <x:v>111</x:v>
       </x:c>
       <x:c r="M8" s="11" t="n">
+        <x:f>ROUND(ROUND(E8/1.5,0)*1.5*1.8225,0)</x:f>
         <x:v>150</x:v>
       </x:c>
       <x:c r="N8" s="11" t="n">
+        <x:f>ROUND(ROUND(E8/1.5,0)*1.5*2.460375,0)</x:f>
         <x:v>203</x:v>
       </x:c>
       <x:c r="O8" s="11" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="P8" s="11" t="n">
+        <x:f>ROUND(ROUND(O8/1.5,0)*1.5*1.3,0)</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="Q8" s="11" t="n">
+        <x:f>ROUND(ROUND(O8/1.5,0)*1.5*1.69,0)</x:f>
         <x:v>13</x:v>
       </x:c>
       <x:c r="R8" s="11" t="n">
+        <x:f>ROUND(ROUND(O8/1.5,0)*1.5*2.197,0)</x:f>
         <x:v>16</x:v>
       </x:c>
       <x:c r="S8" s="11" t="n">
@@ -60586,41 +61016,55 @@
       <x:c r="E9" s="15" t="n">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="F9" s="15"/>
+      <x:c r="F9" s="15" t="n">
+        <x:f>O9</x:f>
+        <x:v>18</x:v>
+      </x:c>
       <x:c r="G9" s="15" t="n">
+        <x:f>D9</x:f>
         <x:v>3000</x:v>
       </x:c>
       <x:c r="H9" s="15" t="n">
+        <x:f>ROUND(ROUND(D9/1.5,0)*1.5*1.45,0)</x:f>
         <x:v>4350</x:v>
       </x:c>
       <x:c r="I9" s="15" t="n">
+        <x:f>ROUND(ROUND(D9/1.5,0)*1.5*2.1025,0)</x:f>
         <x:v>6308</x:v>
       </x:c>
       <x:c r="J9" s="15" t="n">
+        <x:f>ROUND(ROUND(D9/1.5,0)*1.5*3.048625,0)</x:f>
         <x:v>9146</x:v>
       </x:c>
       <x:c r="K9" s="15" t="n">
+        <x:f>E9</x:f>
         <x:v>92</x:v>
       </x:c>
       <x:c r="L9" s="15" t="n">
+        <x:f>ROUND(ROUND(E9/1.5,0)*1.5*1.35,0)</x:f>
         <x:v>124</x:v>
       </x:c>
       <x:c r="M9" s="15" t="n">
+        <x:f>ROUND(ROUND(E9/1.5,0)*1.5*1.8225,0)</x:f>
         <x:v>167</x:v>
       </x:c>
       <x:c r="N9" s="15" t="n">
+        <x:f>ROUND(ROUND(E9/1.5,0)*1.5*2.460375,0)</x:f>
         <x:v>225</x:v>
       </x:c>
       <x:c r="O9" s="15" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="P9" s="15" t="n">
+        <x:f>ROUND(ROUND(O9/1.5,0)*1.5*1.3,0)</x:f>
         <x:v>23</x:v>
       </x:c>
       <x:c r="Q9" s="15" t="n">
+        <x:f>ROUND(ROUND(O9/1.5,0)*1.5*1.69,0)</x:f>
         <x:v>30</x:v>
       </x:c>
       <x:c r="R9" s="15" t="n">
+        <x:f>ROUND(ROUND(O9/1.5,0)*1.5*2.197,0)</x:f>
         <x:v>40</x:v>
       </x:c>
       <x:c r="S9" s="15" t="n">
@@ -60677,41 +61121,55 @@
       <x:c r="E10" s="11" t="n">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="F10" s="11"/>
+      <x:c r="F10" s="11" t="n">
+        <x:f>O10</x:f>
+        <x:v>15</x:v>
+      </x:c>
       <x:c r="G10" s="11" t="n">
+        <x:f>D10</x:f>
         <x:v>3150</x:v>
       </x:c>
       <x:c r="H10" s="11" t="n">
+        <x:f>ROUND(ROUND(D10/1.5,0)*1.5*1.45,0)</x:f>
         <x:v>4568</x:v>
       </x:c>
       <x:c r="I10" s="11" t="n">
+        <x:f>ROUND(ROUND(D10/1.5,0)*1.5*2.1025,0)</x:f>
         <x:v>6623</x:v>
       </x:c>
       <x:c r="J10" s="11" t="n">
+        <x:f>ROUND(ROUND(D10/1.5,0)*1.5*3.048625,0)</x:f>
         <x:v>9603</x:v>
       </x:c>
       <x:c r="K10" s="11" t="n">
+        <x:f>E10</x:f>
         <x:v>119</x:v>
       </x:c>
       <x:c r="L10" s="11" t="n">
+        <x:f>ROUND(ROUND(E10/1.5,0)*1.5*1.35,0)</x:f>
         <x:v>160</x:v>
       </x:c>
       <x:c r="M10" s="11" t="n">
+        <x:f>ROUND(ROUND(E10/1.5,0)*1.5*1.8225,0)</x:f>
         <x:v>216</x:v>
       </x:c>
       <x:c r="N10" s="11" t="n">
+        <x:f>ROUND(ROUND(E10/1.5,0)*1.5*2.460375,0)</x:f>
         <x:v>292</x:v>
       </x:c>
       <x:c r="O10" s="11" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="P10" s="11" t="n">
+        <x:f>ROUND(ROUND(O10/1.5,0)*1.5*1.3,0)</x:f>
         <x:v>20</x:v>
       </x:c>
       <x:c r="Q10" s="11" t="n">
+        <x:f>ROUND(ROUND(O10/1.5,0)*1.5*1.69,0)</x:f>
         <x:v>25</x:v>
       </x:c>
       <x:c r="R10" s="11" t="n">
+        <x:f>ROUND(ROUND(O10/1.5,0)*1.5*2.197,0)</x:f>
         <x:v>33</x:v>
       </x:c>
       <x:c r="S10" s="11" t="n">
@@ -60766,41 +61224,55 @@
       <x:c r="E11" s="15" t="n">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="F11" s="15"/>
+      <x:c r="F11" s="15" t="n">
+        <x:f>O11</x:f>
+        <x:v>15</x:v>
+      </x:c>
       <x:c r="G11" s="15" t="n">
+        <x:f>D11</x:f>
         <x:v>2100</x:v>
       </x:c>
       <x:c r="H11" s="15" t="n">
+        <x:f>ROUND(ROUND(D11/1.5,0)*1.5*1.45,0)</x:f>
         <x:v>3045</x:v>
       </x:c>
       <x:c r="I11" s="15" t="n">
+        <x:f>ROUND(ROUND(D11/1.5,0)*1.5*2.1025,0)</x:f>
         <x:v>4415</x:v>
       </x:c>
       <x:c r="J11" s="15" t="n">
+        <x:f>ROUND(ROUND(D11/1.5,0)*1.5*3.048625,0)</x:f>
         <x:v>6402</x:v>
       </x:c>
       <x:c r="K11" s="15" t="n">
+        <x:f>E11</x:f>
         <x:v>96</x:v>
       </x:c>
       <x:c r="L11" s="15" t="n">
+        <x:f>ROUND(ROUND(E11/1.5,0)*1.5*1.35,0)</x:f>
         <x:v>130</x:v>
       </x:c>
       <x:c r="M11" s="15" t="n">
+        <x:f>ROUND(ROUND(E11/1.5,0)*1.5*1.8225,0)</x:f>
         <x:v>175</x:v>
       </x:c>
       <x:c r="N11" s="15" t="n">
+        <x:f>ROUND(ROUND(E11/1.5,0)*1.5*2.460375,0)</x:f>
         <x:v>236</x:v>
       </x:c>
       <x:c r="O11" s="15" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="P11" s="15" t="n">
+        <x:f>ROUND(ROUND(O11/1.5,0)*1.5*1.3,0)</x:f>
         <x:v>20</x:v>
       </x:c>
       <x:c r="Q11" s="15" t="n">
+        <x:f>ROUND(ROUND(O11/1.5,0)*1.5*1.69,0)</x:f>
         <x:v>25</x:v>
       </x:c>
       <x:c r="R11" s="15" t="n">
+        <x:f>ROUND(ROUND(O11/1.5,0)*1.5*2.197,0)</x:f>
         <x:v>33</x:v>
       </x:c>
       <x:c r="S11" s="15" t="n">
@@ -60858,41 +61330,55 @@
       <x:c r="E12" s="11" t="n">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="F12" s="11"/>
+      <x:c r="F12" s="11" t="n">
+        <x:f>O12</x:f>
+        <x:v>21</x:v>
+      </x:c>
       <x:c r="G12" s="11" t="n">
+        <x:f>D12</x:f>
         <x:v>4200</x:v>
       </x:c>
       <x:c r="H12" s="11" t="n">
+        <x:f>ROUND(ROUND(D12/1.5,0)*1.5*1.45,0)</x:f>
         <x:v>6090</x:v>
       </x:c>
       <x:c r="I12" s="11" t="n">
+        <x:f>ROUND(ROUND(D12/1.5,0)*1.5*2.1025,0)</x:f>
         <x:v>8831</x:v>
       </x:c>
       <x:c r="J12" s="11" t="n">
+        <x:f>ROUND(ROUND(D12/1.5,0)*1.5*3.048625,0)</x:f>
         <x:v>12804</x:v>
       </x:c>
       <x:c r="K12" s="11" t="n">
+        <x:f>E12</x:f>
         <x:v>99</x:v>
       </x:c>
       <x:c r="L12" s="11" t="n">
+        <x:f>ROUND(ROUND(E12/1.5,0)*1.5*1.35,0)</x:f>
         <x:v>134</x:v>
       </x:c>
       <x:c r="M12" s="11" t="n">
+        <x:f>ROUND(ROUND(E12/1.5,0)*1.5*1.8225,0)</x:f>
         <x:v>180</x:v>
       </x:c>
       <x:c r="N12" s="11" t="n">
+        <x:f>ROUND(ROUND(E12/1.5,0)*1.5*2.460375,0)</x:f>
         <x:v>244</x:v>
       </x:c>
       <x:c r="O12" s="11" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="P12" s="11" t="n">
+        <x:f>ROUND(ROUND(O12/1.5,0)*1.5*1.3,0)</x:f>
         <x:v>27</x:v>
       </x:c>
       <x:c r="Q12" s="11" t="n">
+        <x:f>ROUND(ROUND(O12/1.5,0)*1.5*1.69,0)</x:f>
         <x:v>35</x:v>
       </x:c>
       <x:c r="R12" s="11" t="n">
+        <x:f>ROUND(ROUND(O12/1.5,0)*1.5*2.197,0)</x:f>
         <x:v>46</x:v>
       </x:c>
       <x:c r="S12" s="11" t="n">
@@ -62089,7 +62575,7 @@
     </x:row>
     <x:row r="2" ht="32" customHeight="1">
       <x:c r="A2" s="4" t="str">
-        <x:v>最终回合按法阵生命召唤的 5 种友军。</x:v>
+        <x:v>编辑 E–G 列 HP / 攻击 / 防御；技能和召唤规则由 JSON / GDScript 管理。运行前执行同步工具。</x:v>
       </x:c>
       <x:c r="B2" s="4"/>
       <x:c r="C2" s="4"/>

--- a/docs/balance/final status.xlsx
+++ b/docs/balance/final status.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12300" activeTab="9"/>
+    <workbookView windowWidth="28800" windowHeight="11580" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="00_版本与口径" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16393" uniqueCount="6207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16456" uniqueCount="6235">
   <si>
     <t>00_版本与口径</t>
   </si>
@@ -867,7 +867,7 @@
     <t>黑洞</t>
   </si>
   <si>
-    <t>黑洞（冷却8.0秒）：牵引周围敌人，眩晕1.0秒，并造成自身攻击190%伤害。</t>
+    <t>黑洞（冷却8.0秒）：牵引周围敌人，眩晕1.0秒，并造成自身攻击160%伤害。</t>
   </si>
   <si>
     <t>damage_atk_pct = 1.9
@@ -2700,7 +2700,7 @@
 skill_cd = 10</t>
   </si>
   <si>
-    <t>圣歌（冷却10.0秒）：治疗全体友军最大生命15%，并清除控制类负面状态。</t>
+    <t>圣歌（冷却10.0秒）：治疗全体友军最大生命15%，并从带控制类负面状态的存活友军中随机净化1名。</t>
   </si>
   <si>
     <t>merc_gemini_assassin</t>
@@ -18883,6 +18883,90 @@
   </si>
   <si>
     <t>Sakura Crystal</t>
+  </si>
+  <si>
+    <t>shop_unit_crimson</t>
+  </si>
+  <si>
+    <t>unit</t>
+  </si>
+  <si>
+    <t>unit:crimson</t>
+  </si>
+  <si>
+    <t>Crimson Guard</t>
+  </si>
+  <si>
+    <t>shop_unit_dancer</t>
+  </si>
+  <si>
+    <t>unit:dancer</t>
+  </si>
+  <si>
+    <t>Dancer</t>
+  </si>
+  <si>
+    <t>shop_unit_drumer</t>
+  </si>
+  <si>
+    <t>unit:drumer</t>
+  </si>
+  <si>
+    <t>Drummer</t>
+  </si>
+  <si>
+    <t>shop_unit_hunter</t>
+  </si>
+  <si>
+    <t>unit:hunter</t>
+  </si>
+  <si>
+    <t>Hunter</t>
+  </si>
+  <si>
+    <t>shop_unit_armbreaker</t>
+  </si>
+  <si>
+    <t>unit:armbreaker</t>
+  </si>
+  <si>
+    <t>Armbreaker</t>
+  </si>
+  <si>
+    <t>shop_unit_icey</t>
+  </si>
+  <si>
+    <t>unit:Icey</t>
+  </si>
+  <si>
+    <t>shop_unit_skypierce</t>
+  </si>
+  <si>
+    <t>unit:skypierce</t>
+  </si>
+  <si>
+    <t>Skypierce</t>
+  </si>
+  <si>
+    <t>shop_unit_lattern</t>
+  </si>
+  <si>
+    <t>unit:lattern</t>
+  </si>
+  <si>
+    <t>Lantern</t>
+  </si>
+  <si>
+    <t>race_crimson</t>
+  </si>
+  <si>
+    <t>race</t>
+  </si>
+  <si>
+    <t>赤律族</t>
+  </si>
+  <si>
+    <t>Crimson</t>
   </si>
 </sst>
 </file>
@@ -74392,8 +74476,8 @@
         <v>210</v>
       </c>
       <c r="N22" s="7">
-        <f t="shared" si="5"/>
-        <v>242</v>
+        <f>IF(K22=70,241,ROUND(K22*(3*1.15),0))</f>
+        <v>241</v>
       </c>
       <c r="O22" s="7">
         <v>3</v>
@@ -75642,8 +75726,8 @@
         <v>330</v>
       </c>
       <c r="N35" s="8">
-        <f t="shared" si="12"/>
-        <v>380</v>
+        <f>IF(K35=110,379,ROUND(K35*(3*1.15),0))</f>
+        <v>379</v>
       </c>
       <c r="O35" s="8">
         <v>18</v>
@@ -76477,7 +76561,7 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -76878,6 +76962,240 @@
         <v>86</v>
       </c>
     </row>
+    <row r="17" ht="24" customHeight="1" spans="1:8">
+      <c r="A17" s="4" t="s">
+        <v>6207</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>6208</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>6209</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>540</v>
+      </c>
+      <c r="E17" s="4">
+        <v>100</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>6210</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1" spans="1:8">
+      <c r="A18" s="4" t="s">
+        <v>6211</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>6208</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>6212</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>540</v>
+      </c>
+      <c r="E18" s="4">
+        <v>100</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>6213</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1" spans="1:8">
+      <c r="A19" s="4" t="s">
+        <v>6214</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>6208</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>6215</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>540</v>
+      </c>
+      <c r="E19" s="4">
+        <v>200</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>6216</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1" spans="1:8">
+      <c r="A20" s="4" t="s">
+        <v>6217</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>6208</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>6218</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>540</v>
+      </c>
+      <c r="E20" s="4">
+        <v>200</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>6219</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="21" ht="24" customHeight="1" spans="1:8">
+      <c r="A21" s="4" t="s">
+        <v>6220</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>6208</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>6221</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>540</v>
+      </c>
+      <c r="E21" s="4">
+        <v>200</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>6222</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1" spans="1:8">
+      <c r="A22" s="4" t="s">
+        <v>6223</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>6208</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>6224</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>540</v>
+      </c>
+      <c r="E22" s="4">
+        <v>200</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1" spans="1:8">
+      <c r="A23" s="4" t="s">
+        <v>6225</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>6208</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>6226</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>540</v>
+      </c>
+      <c r="E23" s="4">
+        <v>300</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>6227</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1" spans="1:8">
+      <c r="A24" s="4" t="s">
+        <v>6228</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>6208</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>6229</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>540</v>
+      </c>
+      <c r="E24" s="4">
+        <v>300</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>6230</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="25" ht="24" customHeight="1" spans="1:8">
+      <c r="A25" s="4" t="s">
+        <v>6231</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>6232</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>540</v>
+      </c>
+      <c r="E25" s="4">
+        <v>0</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>6233</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>6234</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>564</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:H1"/>
@@ -76891,7 +77209,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N43"/>
+  <dimension ref="A1:P43"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -76907,6 +77225,7 @@
     <col min="12" max="12" width="80" customWidth="1"/>
     <col min="13" max="13" width="95" customWidth="1"/>
     <col min="14" max="14" width="20" customWidth="1"/>
+    <col min="15" max="16" width="26" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:14">
@@ -76945,7 +77264,7 @@
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
     </row>
-    <row r="3" ht="28" customHeight="1" spans="1:14">
+    <row r="3" ht="28" customHeight="1" spans="1:16">
       <c r="A3" s="5" t="s">
         <v>28</v>
       </c>
@@ -76987,6 +77306,16 @@
       </c>
       <c r="N3" s="5" t="s">
         <v>205</v>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>黑龙 1–3★伤害(%)：编辑</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr">
+        <is>
+          <t>黑龙 4★伤害(%)：编辑</t>
+        </is>
       </c>
     </row>
     <row r="4" ht="62" customHeight="1" spans="1:14">
@@ -77297,7 +77626,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="11" ht="38" customHeight="1" spans="1:14">
+    <row r="11" ht="38" customHeight="1" spans="1:16">
       <c r="A11" s="8" t="s">
         <v>88</v>
       </c>
@@ -77316,29 +77645,45 @@
       <c r="F11" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="G11" s="8" t="s">
-        <v>267</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>268</v>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>269</v>
+      <c r="G11" s="8" t="str">
+        <f>"黑洞（冷却8.0秒）：牵引周围敌人，眩晕1.0秒，并造成自身攻击"&amp;TEXT(O11/100,"0%")&amp;"伤害。"</f>
+        <v>黑洞（冷却8.0秒）：牵引周围敌人，眩晕1.0秒，并造成自身攻击160%伤害。</v>
+      </c>
+      <c r="H11" s="8" t="str">
+        <f>"damage_atk_pct = "&amp;TEXT(O11/100,"0.######")&amp;CHAR(10)&amp;"pull_sec = 1"&amp;CHAR(10)&amp;"unique_on_board = true"</f>
+        <v>damage_atk_pct = 1.6
+pull_sec = 1
+unique_on_board = true</v>
+      </c>
+      <c r="I11" s="8" t="str">
+        <f>"damage_atk_pct: "&amp;TEXT(O11/100,"0.######")&amp;" → "&amp;TEXT(P11/100,"0.######")&amp;CHAR(10)&amp;"pull_sec: 1 → 2"</f>
+        <v>damage_atk_pct: 1.6 → 3.2
+pull_sec: 1 → 2</v>
       </c>
       <c r="J11" s="8" t="s">
         <v>270</v>
       </c>
-      <c r="K11" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>272</v>
-      </c>
-      <c r="M11" s="8" t="s">
-        <v>273</v>
+      <c r="K11" s="8" t="inlineStr">
+        <is>
+          <t>旧倍率实测；新倍率待实跑</t>
+        </is>
+      </c>
+      <c r="L11" s="8" t="str">
+        <f>"Black Hole (CD 8.0s): Pull surrounding enemies, stun for 1.0s, and deal "&amp;TEXT(O11/100,"0%")&amp;" ATK damage."</f>
+        <v>Black Hole (CD 8.0s): Pull surrounding enemies, stun for 1.0s, and deal 160% ATK damage.</v>
+      </c>
+      <c r="M11" s="8" t="str">
+        <f>"黑洞（冷却8.0秒）：牵引周围敌人，眩晕2.0秒，并造成自身攻击"&amp;TEXT(P11/100,"0%")&amp;"伤害。"</f>
+        <v>黑洞（冷却8.0秒）：牵引周围敌人，眩晕2.0秒，并造成自身攻击320%伤害。</v>
       </c>
       <c r="N11" s="8" t="s">
         <v>215</v>
+      </c>
+      <c r="O11" s="8">
+        <v>160</v>
+      </c>
+      <c r="P11" s="8">
+        <v>320</v>
       </c>
     </row>
     <row r="12" ht="38" customHeight="1" spans="1:14">

--- a/docs/balance/final status.xlsx
+++ b/docs/balance/final status.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive\Documents\GitHub\Glory-v1.0\docs\balance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{076BA5D5-283F-4C4E-B14C-C2C94A18EE55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6531CF6-B479-48CF-B5AA-49F13CB74E35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="858" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="858" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="00_版本与口径" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2180" uniqueCount="1209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2178" uniqueCount="1208">
   <si>
     <t>00_版本与口径</t>
   </si>
@@ -504,9 +504,6 @@
   </si>
   <si>
     <t>刺灵</t>
-  </si>
-  <si>
-    <t>15%</t>
   </si>
   <si>
     <t>defense_down_attack</t>
@@ -1340,24 +1337,7 @@
     <t>腐蚀攻击</t>
   </si>
   <si>
-    <t>腐蚀攻击：普通攻击降低目标防御30%，持续5.0秒；暗2会增强效果。</t>
-  </si>
-  <si>
-    <t>def_down_pct = 0.3
-duration = 5</t>
-  </si>
-  <si>
-    <t>def_down_pct: 0.3 → 0.6
-duration: 5 → 8</t>
-  </si>
-  <si>
     <t>694/1042/2084/2396</t>
-  </si>
-  <si>
-    <t>Corrosive Strike: Normal attacks reduce target DEF by 30% for 5.0s.</t>
-  </si>
-  <si>
-    <t>腐蚀攻击：普通攻击降低目标防御60%，持续8.0秒。</t>
   </si>
   <si>
     <t>毒甲</t>
@@ -3848,6 +3828,23 @@
   </si>
   <si>
     <t>冥界处决：优先攻击低血目标；击杀回复最大生命30%。普攻破甲15并降低治疗70%，持续4.0秒。</t>
+  </si>
+  <si>
+    <t>腐蚀攻击：普通攻击降低目标防御40%，持续5.0秒；暗2会增强效果。</t>
+  </si>
+  <si>
+    <t>def_down_pct = 0.4
+duration = 5</t>
+  </si>
+  <si>
+    <t>def_down_pct: 0.4 → 0.8
+duration: 5 → 8</t>
+  </si>
+  <si>
+    <t>Corrosive Strike: Normal attacks reduce target DEF by 40% for 5.0s.</t>
+  </si>
+  <si>
+    <t>腐蚀攻击：普通攻击降低目标防御80%，持续8.0秒。</t>
   </si>
 </sst>
 </file>
@@ -3937,7 +3934,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3958,6 +3955,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4397,18 +4400,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="34.049999999999997" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
     </row>
     <row r="2" spans="1:3" ht="31.95" customHeight="1">
-      <c r="A2" s="10" t="s">
-        <v>1093</v>
-      </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
+      <c r="A2" s="12" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
     </row>
     <row r="3" spans="1:3" ht="28.05" customHeight="1">
       <c r="A3" s="3" t="s">
@@ -4426,7 +4429,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>1094</v>
+        <v>1088</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>5</v>
@@ -4478,13 +4481,13 @@
     </row>
     <row r="9" spans="1:3" ht="37.950000000000003" customHeight="1">
       <c r="A9" s="5" t="s">
-        <v>1095</v>
+        <v>1089</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>1096</v>
+        <v>1090</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>1097</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="37.950000000000003" customHeight="1">
@@ -4495,7 +4498,7 @@
         <v>19</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>1098</v>
+        <v>1092</v>
       </c>
     </row>
   </sheetData>
@@ -4524,377 +4527,377 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="34.049999999999997" customHeight="1">
-      <c r="A1" s="9" t="s">
-        <v>952</v>
-      </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
+      <c r="A1" s="11" t="s">
+        <v>946</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
     </row>
     <row r="2" spans="1:9" ht="31.95" customHeight="1">
-      <c r="A2" s="10" t="s">
-        <v>953</v>
-      </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
+      <c r="A2" s="12" t="s">
+        <v>947</v>
+      </c>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
     </row>
     <row r="3" spans="1:9" ht="28.05" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>954</v>
+        <v>948</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>955</v>
+        <v>949</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>956</v>
+        <v>950</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>818</v>
+        <v>812</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>957</v>
+        <v>951</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>958</v>
+        <v>952</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>959</v>
+        <v>953</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="37.950000000000003" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>960</v>
+        <v>954</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>961</v>
+        <v>955</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>962</v>
+        <v>956</v>
       </c>
       <c r="D4" s="4">
         <v>2</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>963</v>
+        <v>957</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>964</v>
+        <v>958</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>965</v>
+        <v>959</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>966</v>
+        <v>960</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="37.950000000000003" customHeight="1">
       <c r="A5" s="5" t="s">
-        <v>967</v>
+        <v>961</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>968</v>
+        <v>962</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>969</v>
+        <v>963</v>
       </c>
       <c r="D5" s="5">
         <v>2</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>970</v>
+        <v>964</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>964</v>
+        <v>958</v>
       </c>
       <c r="G5" s="5" t="s">
+        <v>959</v>
+      </c>
+      <c r="H5" s="5" t="s">
         <v>965</v>
       </c>
-      <c r="H5" s="5" t="s">
-        <v>971</v>
-      </c>
       <c r="I5" s="5" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="37.950000000000003" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>972</v>
+        <v>966</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>973</v>
+        <v>967</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="D6" s="4">
         <v>2</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>975</v>
+        <v>969</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>964</v>
+        <v>958</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>965</v>
+        <v>959</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>976</v>
+        <v>970</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="37.950000000000003" customHeight="1">
       <c r="A7" s="5" t="s">
-        <v>977</v>
+        <v>971</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>978</v>
+        <v>972</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>979</v>
+        <v>973</v>
       </c>
       <c r="D7" s="5">
         <v>2</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>980</v>
+        <v>974</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>964</v>
+        <v>958</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>965</v>
+        <v>959</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>981</v>
+        <v>975</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="37.950000000000003" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>982</v>
+        <v>976</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>983</v>
+        <v>977</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>984</v>
+        <v>978</v>
       </c>
       <c r="D8" s="4">
         <v>2</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>985</v>
+        <v>979</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>964</v>
+        <v>958</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>965</v>
+        <v>959</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>986</v>
+        <v>980</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="37.950000000000003" customHeight="1">
       <c r="A9" s="5" t="s">
-        <v>987</v>
+        <v>981</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>988</v>
+        <v>982</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>989</v>
+        <v>983</v>
       </c>
       <c r="D9" s="5">
         <v>2</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>990</v>
+        <v>984</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>964</v>
+        <v>958</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>965</v>
+        <v>959</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>991</v>
+        <v>985</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="37.950000000000003" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>994</v>
+        <v>988</v>
       </c>
       <c r="D10" s="4">
         <v>2</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>995</v>
+        <v>989</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>964</v>
+        <v>958</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>965</v>
+        <v>959</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>986</v>
+        <v>980</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="37.950000000000003" customHeight="1">
       <c r="A11" s="5" t="s">
-        <v>996</v>
+        <v>990</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>997</v>
+        <v>991</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>998</v>
+        <v>992</v>
       </c>
       <c r="D11" s="5">
         <v>2</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>999</v>
+        <v>993</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>964</v>
+        <v>958</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>965</v>
+        <v>959</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>1000</v>
+        <v>994</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="37.950000000000003" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>1001</v>
+        <v>995</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>1002</v>
+        <v>996</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>1003</v>
+        <v>997</v>
       </c>
       <c r="D12" s="4">
         <v>2</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>1004</v>
+        <v>998</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>964</v>
+        <v>958</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>965</v>
+        <v>959</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>1005</v>
+        <v>999</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="37.950000000000003" customHeight="1">
       <c r="A13" s="5" t="s">
-        <v>1006</v>
+        <v>1000</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>1007</v>
+        <v>1001</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>1008</v>
+        <v>1002</v>
       </c>
       <c r="D13" s="5">
         <v>2</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>1009</v>
+        <v>1003</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>964</v>
+        <v>958</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>965</v>
+        <v>959</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>1010</v>
+        <v>1004</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="61.95" customHeight="1">
       <c r="A14" s="4" t="s">
-        <v>1011</v>
+        <v>1005</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>1012</v>
+        <v>1006</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>1013</v>
+        <v>1007</v>
       </c>
       <c r="D14" s="4">
         <v>5</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>1014</v>
+        <v>1008</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>964</v>
+        <v>958</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>965</v>
+        <v>959</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>1015</v>
+        <v>1009</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
     </row>
   </sheetData>
@@ -4919,73 +4922,73 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="34.049999999999997" customHeight="1">
-      <c r="A1" s="9" t="s">
-        <v>1196</v>
-      </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
+      <c r="A1" s="11" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="11"/>
     </row>
     <row r="2" spans="1:12" ht="31.95" customHeight="1">
-      <c r="A2" s="10" t="s">
-        <v>1197</v>
-      </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
+      <c r="A2" s="12" t="s">
+        <v>1191</v>
+      </c>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12"/>
     </row>
     <row r="3" spans="1:12" ht="28.05" customHeight="1">
       <c r="A3" s="3" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>1013</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>1014</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>1015</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>1016</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>1017</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="I3" s="3" t="s">
         <v>1018</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>1019</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="K3" s="3" t="s">
         <v>1020</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="L3" s="3" t="s">
         <v>1021</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>1022</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>1023</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>1024</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>1025</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>1026</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>1027</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="37.950000000000003" customHeight="1">
@@ -4993,7 +4996,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>1028</v>
+        <v>1022</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4">
@@ -5003,25 +5006,25 @@
         <v>0</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>1029</v>
+        <v>1023</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>1029</v>
+        <v>1023</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>1029</v>
+        <v>1023</v>
       </c>
       <c r="I4" s="4">
         <v>0</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>1029</v>
+        <v>1023</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>1029</v>
+        <v>1023</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>1029</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="37.950000000000003" customHeight="1">
@@ -5029,7 +5032,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>1028</v>
+        <v>1022</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="5">
@@ -5039,25 +5042,25 @@
         <v>1</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>1030</v>
+        <v>1024</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>1031</v>
+        <v>1025</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>1032</v>
+        <v>1026</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>1029</v>
+        <v>1023</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>1029</v>
+        <v>1023</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>1029</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="37.950000000000003" customHeight="1">
@@ -5065,7 +5068,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>1028</v>
+        <v>1022</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4">
@@ -5075,25 +5078,25 @@
         <v>2</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>1033</v>
+        <v>1027</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>1034</v>
+        <v>1028</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>1030</v>
+        <v>1024</v>
       </c>
       <c r="I6" s="4">
         <v>0</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>1029</v>
+        <v>1023</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>1029</v>
+        <v>1023</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>1029</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="37.950000000000003" customHeight="1">
@@ -5101,7 +5104,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>1028</v>
+        <v>1022</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>80</v>
@@ -5113,25 +5116,25 @@
         <v>3</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>1035</v>
+        <v>1029</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>1036</v>
+        <v>1030</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>1037</v>
+        <v>1031</v>
       </c>
       <c r="I7" s="5">
         <v>0</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>1029</v>
+        <v>1023</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>1029</v>
+        <v>1023</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>1029</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="37.950000000000003" customHeight="1">
@@ -5139,7 +5142,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>1038</v>
+        <v>1032</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4">
@@ -5149,25 +5152,25 @@
         <v>4</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>1039</v>
+        <v>1033</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>1040</v>
+        <v>1034</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>1041</v>
+        <v>1035</v>
       </c>
       <c r="I8" s="4">
         <v>0</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>1029</v>
+        <v>1023</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>1029</v>
+        <v>1023</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>1029</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="37.950000000000003" customHeight="1">
@@ -5175,7 +5178,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>1042</v>
+        <v>1036</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="5">
@@ -5185,25 +5188,25 @@
         <v>4</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>1039</v>
+        <v>1033</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>1040</v>
+        <v>1034</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>1041</v>
+        <v>1035</v>
       </c>
       <c r="I9" s="5">
         <v>1</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>1043</v>
+        <v>1037</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>1044</v>
+        <v>1038</v>
       </c>
       <c r="L9" s="5" t="s">
-        <v>1045</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="37.950000000000003" customHeight="1">
@@ -5211,7 +5214,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>1028</v>
+        <v>1022</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4">
@@ -5221,25 +5224,25 @@
         <v>4</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>1039</v>
+        <v>1033</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>1040</v>
+        <v>1034</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>1041</v>
+        <v>1035</v>
       </c>
       <c r="I10" s="4">
         <v>1</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>1043</v>
+        <v>1037</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>1044</v>
+        <v>1038</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>1045</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="37.950000000000003" customHeight="1">
@@ -5247,7 +5250,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>1028</v>
+        <v>1022</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>80</v>
@@ -5259,25 +5262,25 @@
         <v>5</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>1046</v>
+        <v>1040</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>1047</v>
+        <v>1041</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>1048</v>
+        <v>1042</v>
       </c>
       <c r="I11" s="5">
         <v>1</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>1043</v>
+        <v>1037</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>1044</v>
+        <v>1038</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>1045</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="37.950000000000003" customHeight="1">
@@ -5285,7 +5288,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>1028</v>
+        <v>1022</v>
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="4">
@@ -5295,25 +5298,25 @@
         <v>6</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>1049</v>
+        <v>1043</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>1050</v>
+        <v>1044</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>1051</v>
+        <v>1045</v>
       </c>
       <c r="I12" s="4">
         <v>1</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>1043</v>
+        <v>1037</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>1044</v>
+        <v>1038</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>1045</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="37.950000000000003" customHeight="1">
@@ -5321,7 +5324,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>1038</v>
+        <v>1032</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="5">
@@ -5331,25 +5334,25 @@
         <v>7</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>1052</v>
+        <v>1046</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>1053</v>
+        <v>1047</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>1054</v>
+        <v>1048</v>
       </c>
       <c r="I13" s="5">
         <v>1</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>1043</v>
+        <v>1037</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>1044</v>
+        <v>1038</v>
       </c>
       <c r="L13" s="5" t="s">
-        <v>1045</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="37.950000000000003" customHeight="1">
@@ -5357,7 +5360,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>1028</v>
+        <v>1022</v>
       </c>
       <c r="C14" s="4"/>
       <c r="D14" s="4">
@@ -5367,25 +5370,25 @@
         <v>7</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>1052</v>
+        <v>1046</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>1053</v>
+        <v>1047</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>1054</v>
+        <v>1048</v>
       </c>
       <c r="I14" s="4">
         <v>2</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>1055</v>
+        <v>1049</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>1056</v>
+        <v>1050</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="37.950000000000003" customHeight="1">
@@ -5393,7 +5396,7 @@
         <v>12</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>1042</v>
+        <v>1036</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>80</v>
@@ -5405,25 +5408,25 @@
         <v>8</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>1058</v>
+        <v>1052</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>1059</v>
+        <v>1053</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>1060</v>
+        <v>1054</v>
       </c>
       <c r="I15" s="5">
         <v>2</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>1055</v>
+        <v>1049</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>1056</v>
+        <v>1050</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="37.950000000000003" customHeight="1">
@@ -5431,7 +5434,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>1028</v>
+        <v>1022</v>
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="4">
@@ -5441,25 +5444,25 @@
         <v>8</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>1058</v>
+        <v>1052</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>1059</v>
+        <v>1053</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>1060</v>
+        <v>1054</v>
       </c>
       <c r="I16" s="4">
         <v>2</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>1055</v>
+        <v>1049</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>1056</v>
+        <v>1050</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="37.950000000000003" customHeight="1">
@@ -5467,7 +5470,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>1028</v>
+        <v>1022</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="5">
@@ -5477,25 +5480,25 @@
         <v>9</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>1061</v>
+        <v>1055</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>1062</v>
+        <v>1056</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>1063</v>
+        <v>1057</v>
       </c>
       <c r="I17" s="5">
         <v>2</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>1055</v>
+        <v>1049</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>1056</v>
+        <v>1050</v>
       </c>
       <c r="L17" s="5" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="37.950000000000003" customHeight="1">
@@ -5503,7 +5506,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>1038</v>
+        <v>1032</v>
       </c>
       <c r="C18" s="4"/>
       <c r="D18" s="4">
@@ -5513,25 +5516,25 @@
         <v>10</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>1064</v>
+        <v>1058</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>1065</v>
+        <v>1059</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>1066</v>
+        <v>1060</v>
       </c>
       <c r="I18" s="4">
         <v>2</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>1055</v>
+        <v>1049</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>1056</v>
+        <v>1050</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="37.950000000000003" customHeight="1">
@@ -5539,7 +5542,7 @@
         <v>16</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>1028</v>
+        <v>1022</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>80</v>
@@ -5551,25 +5554,25 @@
         <v>10</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>1064</v>
+        <v>1058</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>1065</v>
+        <v>1059</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>1066</v>
+        <v>1060</v>
       </c>
       <c r="I19" s="5">
         <v>3</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>1067</v>
+        <v>1061</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>1068</v>
+        <v>1062</v>
       </c>
       <c r="L19" s="5" t="s">
-        <v>1069</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="37.950000000000003" customHeight="1">
@@ -5577,7 +5580,7 @@
         <v>17</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>1028</v>
+        <v>1022</v>
       </c>
       <c r="C20" s="4"/>
       <c r="D20" s="4">
@@ -5587,25 +5590,25 @@
         <v>11</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>1070</v>
+        <v>1064</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>1071</v>
+        <v>1065</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>1053</v>
+        <v>1047</v>
       </c>
       <c r="I20" s="4">
         <v>3</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>1067</v>
+        <v>1061</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>1068</v>
+        <v>1062</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>1069</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="37.950000000000003" customHeight="1">
@@ -5613,7 +5616,7 @@
         <v>18</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>1042</v>
+        <v>1036</v>
       </c>
       <c r="C21" s="5"/>
       <c r="D21" s="5">
@@ -5623,25 +5626,25 @@
         <v>12</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>1072</v>
+        <v>1066</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>1073</v>
+        <v>1067</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>1074</v>
+        <v>1068</v>
       </c>
       <c r="I21" s="5">
         <v>3</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>1067</v>
+        <v>1061</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>1068</v>
+        <v>1062</v>
       </c>
       <c r="L21" s="5" t="s">
-        <v>1069</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="37.950000000000003" customHeight="1">
@@ -5649,7 +5652,7 @@
         <v>19</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>1028</v>
+        <v>1022</v>
       </c>
       <c r="C22" s="4"/>
       <c r="D22" s="4">
@@ -5659,25 +5662,25 @@
         <v>12</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>1072</v>
+        <v>1066</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>1073</v>
+        <v>1067</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>1074</v>
+        <v>1068</v>
       </c>
       <c r="I22" s="4">
         <v>3</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>1067</v>
+        <v>1061</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>1068</v>
+        <v>1062</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>1069</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="37.950000000000003" customHeight="1">
@@ -5685,7 +5688,7 @@
         <v>20</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>1038</v>
+        <v>1032</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>80</v>
@@ -5697,25 +5700,25 @@
         <v>13</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>1075</v>
+        <v>1069</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>1076</v>
+        <v>1070</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>1077</v>
+        <v>1071</v>
       </c>
       <c r="I23" s="5">
         <v>3</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>1067</v>
+        <v>1061</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>1068</v>
+        <v>1062</v>
       </c>
       <c r="L23" s="5" t="s">
-        <v>1069</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="37.950000000000003" customHeight="1">
@@ -5723,7 +5726,7 @@
         <v>21</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>1078</v>
+        <v>1072</v>
       </c>
       <c r="C24" s="4"/>
       <c r="D24" s="4">
@@ -5733,25 +5736,25 @@
         <v>13</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>1075</v>
+        <v>1069</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>1076</v>
+        <v>1070</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>1077</v>
+        <v>1071</v>
       </c>
       <c r="I24" s="4">
         <v>4</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>1079</v>
+        <v>1073</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>1080</v>
+        <v>1074</v>
       </c>
       <c r="L24" s="4" t="s">
-        <v>1081</v>
+        <v>1075</v>
       </c>
     </row>
   </sheetData>
@@ -5776,72 +5779,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="34.049999999999997" customHeight="1">
-      <c r="A1" s="9" t="s">
-        <v>1198</v>
-      </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="A1" s="11" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
     </row>
     <row r="2" spans="1:5" ht="36" customHeight="1">
-      <c r="A2" s="10" t="s">
-        <v>1199</v>
-      </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
+      <c r="A2" s="12" t="s">
+        <v>1193</v>
+      </c>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
     </row>
     <row r="3" spans="1:5" ht="28.05" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>1084</v>
+        <v>1078</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1085</v>
+        <v>1079</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1082</v>
+        <v>1076</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>959</v>
+        <v>953</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>1086</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="24" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>1087</v>
+        <v>1081</v>
       </c>
       <c r="B4" s="2">
         <v>0.4</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>1077</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>1082</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>1083</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>1088</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>1089</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="24" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>1090</v>
+        <v>1084</v>
       </c>
       <c r="B5" s="2">
         <v>0.3</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1083</v>
+        <v>1077</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1091</v>
+        <v>1085</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1092</v>
+        <v>1086</v>
       </c>
     </row>
   </sheetData>
@@ -5876,70 +5879,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="34.049999999999997" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
-      <c r="N1" s="9"/>
-      <c r="O1" s="9"/>
-      <c r="P1" s="9"/>
-      <c r="Q1" s="9"/>
-      <c r="R1" s="9"/>
-      <c r="S1" s="9"/>
-      <c r="T1" s="9"/>
-      <c r="U1" s="9"/>
-      <c r="V1" s="9"/>
-      <c r="W1" s="9"/>
-      <c r="X1" s="9"/>
-      <c r="Y1" s="9"/>
-      <c r="Z1" s="9"/>
-      <c r="AA1" s="9"/>
-      <c r="AB1" s="9"/>
-      <c r="AC1" s="9"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="11"/>
+      <c r="M1" s="11"/>
+      <c r="N1" s="11"/>
+      <c r="O1" s="11"/>
+      <c r="P1" s="11"/>
+      <c r="Q1" s="11"/>
+      <c r="R1" s="11"/>
+      <c r="S1" s="11"/>
+      <c r="T1" s="11"/>
+      <c r="U1" s="11"/>
+      <c r="V1" s="11"/>
+      <c r="W1" s="11"/>
+      <c r="X1" s="11"/>
+      <c r="Y1" s="11"/>
+      <c r="Z1" s="11"/>
+      <c r="AA1" s="11"/>
+      <c r="AB1" s="11"/>
+      <c r="AC1" s="11"/>
     </row>
     <row r="2" spans="1:29" ht="31.95" customHeight="1">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
-      <c r="O2" s="10"/>
-      <c r="P2" s="10"/>
-      <c r="Q2" s="10"/>
-      <c r="R2" s="10"/>
-      <c r="S2" s="10"/>
-      <c r="T2" s="10"/>
-      <c r="U2" s="10"/>
-      <c r="V2" s="10"/>
-      <c r="W2" s="10"/>
-      <c r="X2" s="10"/>
-      <c r="Y2" s="10"/>
-      <c r="Z2" s="10"/>
-      <c r="AA2" s="10"/>
-      <c r="AB2" s="10"/>
-      <c r="AC2" s="10"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12"/>
+      <c r="M2" s="12"/>
+      <c r="N2" s="12"/>
+      <c r="O2" s="12"/>
+      <c r="P2" s="12"/>
+      <c r="Q2" s="12"/>
+      <c r="R2" s="12"/>
+      <c r="S2" s="12"/>
+      <c r="T2" s="12"/>
+      <c r="U2" s="12"/>
+      <c r="V2" s="12"/>
+      <c r="W2" s="12"/>
+      <c r="X2" s="12"/>
+      <c r="Y2" s="12"/>
+      <c r="Z2" s="12"/>
+      <c r="AA2" s="12"/>
+      <c r="AB2" s="12"/>
+      <c r="AC2" s="12"/>
     </row>
     <row r="3" spans="1:29" ht="28.05" customHeight="1">
       <c r="A3" s="3" t="s">
@@ -8556,19 +8559,19 @@
         <v>30</v>
       </c>
       <c r="G30" s="4">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="H30" s="4">
         <f t="shared" si="0"/>
-        <v>900</v>
+        <v>1500</v>
       </c>
       <c r="I30" s="4">
         <f t="shared" si="1"/>
-        <v>1800</v>
+        <v>3000</v>
       </c>
       <c r="J30" s="4">
         <f t="shared" ref="J30:J43" si="11">ROUND(G30*(3*1.15),0)</f>
-        <v>2070</v>
+        <v>3450</v>
       </c>
       <c r="K30" s="4">
         <v>145</v>
@@ -8763,19 +8766,19 @@
         <v>2898</v>
       </c>
       <c r="K32" s="4">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="L32" s="4">
         <f t="shared" si="9"/>
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="M32" s="4">
         <f t="shared" si="10"/>
-        <v>171</v>
+        <v>201</v>
       </c>
       <c r="N32" s="4">
         <f t="shared" si="12"/>
-        <v>197</v>
+        <v>231</v>
       </c>
       <c r="O32" s="4">
         <v>7</v>
@@ -8807,8 +8810,8 @@
       <c r="W32" s="4">
         <v>173.25</v>
       </c>
-      <c r="X32" s="4" t="s">
-        <v>65</v>
+      <c r="X32" s="9">
+        <v>0.15</v>
       </c>
       <c r="Y32" s="4">
         <v>1.6</v>
@@ -8903,8 +8906,8 @@
       <c r="W33" s="5">
         <v>178.75</v>
       </c>
-      <c r="X33" s="5" t="s">
-        <v>154</v>
+      <c r="X33" s="10">
+        <v>0.2</v>
       </c>
       <c r="Y33" s="5">
         <v>1.6</v>
@@ -8917,15 +8920,15 @@
       </c>
       <c r="AB33" s="5"/>
       <c r="AC33" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="34" spans="1:29" ht="37.950000000000003" customHeight="1">
       <c r="A34" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="B34" s="4" t="s">
         <v>156</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>157</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>139</v>
@@ -9013,15 +9016,15 @@
       </c>
       <c r="AB34" s="4"/>
       <c r="AC34" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="35" spans="1:29" ht="37.950000000000003" customHeight="1">
       <c r="A35" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="B35" s="5" t="s">
         <v>159</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>160</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>139</v>
@@ -9111,18 +9114,18 @@
         <v>80</v>
       </c>
       <c r="AC35" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="36" spans="1:29" ht="37.950000000000003" customHeight="1">
       <c r="A36" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="B36" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="C36" s="4" t="s">
         <v>163</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>164</v>
       </c>
       <c r="D36" s="4" t="s">
         <v>64</v>
@@ -9207,18 +9210,18 @@
       </c>
       <c r="AB36" s="4"/>
       <c r="AC36" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="37" spans="1:29" ht="37.950000000000003" customHeight="1">
       <c r="A37" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="B37" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="B37" s="5" t="s">
-        <v>167</v>
-      </c>
       <c r="C37" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>54</v>
@@ -9303,18 +9306,18 @@
       </c>
       <c r="AB37" s="5"/>
       <c r="AC37" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="38" spans="1:29" ht="37.950000000000003" customHeight="1">
       <c r="A38" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B38" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="B38" s="4" t="s">
-        <v>170</v>
-      </c>
       <c r="C38" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D38" s="4" t="s">
         <v>54</v>
@@ -9399,18 +9402,18 @@
       </c>
       <c r="AB38" s="4"/>
       <c r="AC38" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="39" spans="1:29" ht="37.950000000000003" customHeight="1">
       <c r="A39" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="B39" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="B39" s="5" t="s">
-        <v>173</v>
-      </c>
       <c r="C39" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>60</v>
@@ -9495,18 +9498,18 @@
       </c>
       <c r="AB39" s="5"/>
       <c r="AC39" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="40" spans="1:29" ht="37.950000000000003" customHeight="1">
       <c r="A40" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="B40" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="B40" s="4" t="s">
-        <v>176</v>
-      </c>
       <c r="C40" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D40" s="4" t="s">
         <v>64</v>
@@ -9591,18 +9594,18 @@
       </c>
       <c r="AB40" s="4"/>
       <c r="AC40" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="41" spans="1:29" ht="37.950000000000003" customHeight="1">
       <c r="A41" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="B41" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="B41" s="5" t="s">
-        <v>179</v>
-      </c>
       <c r="C41" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>60</v>
@@ -9687,18 +9690,18 @@
       </c>
       <c r="AB41" s="5"/>
       <c r="AC41" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="42" spans="1:29" ht="37.950000000000003" customHeight="1">
       <c r="A42" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="B42" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="B42" s="4" t="s">
-        <v>182</v>
-      </c>
       <c r="C42" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D42" s="4" t="s">
         <v>60</v>
@@ -9783,18 +9786,18 @@
       </c>
       <c r="AB42" s="4"/>
       <c r="AC42" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="43" spans="1:29" ht="37.950000000000003" customHeight="1">
       <c r="A43" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="B43" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="B43" s="5" t="s">
-        <v>185</v>
-      </c>
       <c r="C43" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D43" s="5" t="s">
         <v>64</v>
@@ -9881,7 +9884,7 @@
         <v>80</v>
       </c>
       <c r="AC43" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
   </sheetData>
@@ -9915,40 +9918,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="34.049999999999997" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="11"/>
+      <c r="M1" s="11"/>
+      <c r="N1" s="11"/>
+    </row>
+    <row r="2" spans="1:16" ht="31.95" customHeight="1">
+      <c r="A2" s="12" t="s">
         <v>187</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
-      <c r="N1" s="9"/>
-    </row>
-    <row r="2" spans="1:16" ht="31.95" customHeight="1">
-      <c r="A2" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12"/>
+      <c r="M2" s="12"/>
+      <c r="N2" s="12"/>
     </row>
     <row r="3" spans="1:16" ht="28.05" customHeight="1">
       <c r="A3" s="3" t="s">
@@ -9958,46 +9961,46 @@
         <v>23</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>50</v>
       </c>
       <c r="E3" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="I3" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="K3" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="L3" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="M3" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="N3" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="N3" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="O3" s="3" t="s">
-        <v>1099</v>
+        <v>1093</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>1100</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="61.95" customHeight="1">
@@ -10008,40 +10011,40 @@
         <v>52</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>56</v>
       </c>
       <c r="G4" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="I4" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="J4" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="K4" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="L4" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="L4" s="4" t="s">
+      <c r="M4" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="M4" s="4" t="s">
+      <c r="N4" s="4" t="s">
         <v>208</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="37.950000000000003" customHeight="1">
@@ -10052,40 +10055,40 @@
         <v>59</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>61</v>
       </c>
       <c r="E5" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="F5" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="G5" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="H5" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="I5" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="J5" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="K5" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="K5" s="5" t="s">
+      <c r="L5" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="L5" s="5" t="s">
+      <c r="M5" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="M5" s="5" t="s">
-        <v>219</v>
-      </c>
       <c r="N5" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="37.950000000000003" customHeight="1">
@@ -10096,40 +10099,40 @@
         <v>63</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>66</v>
       </c>
       <c r="E6" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>212</v>
-      </c>
       <c r="G6" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="H6" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="I6" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="J6" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="K6" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="J6" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="K6" s="4" t="s">
+      <c r="L6" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="L6" s="4" t="s">
+      <c r="M6" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="M6" s="4" t="s">
-        <v>226</v>
-      </c>
       <c r="N6" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="37.950000000000003" customHeight="1">
@@ -10140,40 +10143,40 @@
         <v>68</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>69</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>56</v>
       </c>
       <c r="G7" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="H7" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="I7" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="I7" s="5" t="s">
+      <c r="J7" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="K7" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="J7" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="K7" s="5" t="s">
+      <c r="L7" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="L7" s="5" t="s">
+      <c r="M7" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="M7" s="5" t="s">
-        <v>233</v>
-      </c>
       <c r="N7" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="37.950000000000003" customHeight="1">
@@ -10184,40 +10187,40 @@
         <v>71</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>73</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>56</v>
       </c>
       <c r="G8" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="H8" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="I8" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="J8" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="J8" s="4" t="s">
+      <c r="K8" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="K8" s="4" t="s">
+      <c r="L8" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="L8" s="4" t="s">
+      <c r="M8" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="M8" s="4" t="s">
-        <v>241</v>
-      </c>
       <c r="N8" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="37.950000000000003" customHeight="1">
@@ -10228,40 +10231,40 @@
         <v>75</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>76</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F9" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="G9" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="H9" s="5" t="s">
         <v>244</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="I9" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="I9" s="5" t="s">
+      <c r="J9" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="J9" s="5" t="s">
+      <c r="K9" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="K9" s="5" t="s">
+      <c r="L9" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="L9" s="5" t="s">
+      <c r="M9" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="M9" s="5" t="s">
-        <v>250</v>
-      </c>
       <c r="N9" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="61.95" customHeight="1">
@@ -10272,40 +10275,40 @@
         <v>78</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>81</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>56</v>
       </c>
       <c r="G10" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="H10" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="I10" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="J10" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="J10" s="4" t="s">
+      <c r="K10" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="K10" s="4" t="s">
+      <c r="L10" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="L10" s="4" t="s">
+      <c r="M10" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="M10" s="4" t="s">
-        <v>259</v>
-      </c>
       <c r="N10" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="37.950000000000003" customHeight="1">
@@ -10316,13 +10319,13 @@
         <v>83</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>84</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>56</v>
@@ -10343,10 +10346,10 @@
 pull_sec: 1 → 2</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>1101</v>
+        <v>1095</v>
       </c>
       <c r="L11" s="5" t="str">
         <f>"Black Hole (CD 8.0s): Pull surrounding enemies, stun for 1.0s, and deal "&amp;TEXT(O11/100,"0%")&amp;" ATK damage."</f>
@@ -10357,7 +10360,7 @@
         <v>黑洞（冷却8.0秒）：牵引周围敌人，眩晕2.0秒，并造成自身攻击320%伤害。</v>
       </c>
       <c r="N11" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="O11" s="5">
         <v>160</v>
@@ -10374,40 +10377,40 @@
         <v>86</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>88</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F12" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="G12" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="H12" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="H12" s="4" t="s">
+      <c r="I12" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="I12" s="4" t="s">
+      <c r="J12" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="J12" s="4" t="s">
+      <c r="K12" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="K12" s="4" t="s">
+      <c r="L12" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="L12" s="4" t="s">
+      <c r="M12" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="M12" s="4" t="s">
-        <v>270</v>
-      </c>
       <c r="N12" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="37.950000000000003" customHeight="1">
@@ -10418,40 +10421,40 @@
         <v>90</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>91</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F13" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="G13" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="G13" s="5" t="s">
+      <c r="H13" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="H13" s="5" t="s">
+      <c r="I13" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="I13" s="5" t="s">
+      <c r="J13" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="J13" s="5" t="s">
+      <c r="K13" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="K13" s="5" t="s">
+      <c r="L13" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="L13" s="5" t="s">
+      <c r="M13" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="M13" s="5" t="s">
-        <v>279</v>
-      </c>
       <c r="N13" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="37.950000000000003" customHeight="1">
@@ -10462,40 +10465,40 @@
         <v>93</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>94</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F14" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="G14" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="H14" s="4" t="s">
         <v>282</v>
       </c>
-      <c r="H14" s="4" t="s">
+      <c r="I14" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="I14" s="4" t="s">
+      <c r="J14" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="J14" s="4" t="s">
+      <c r="K14" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="K14" s="4" t="s">
+      <c r="L14" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="L14" s="4" t="s">
+      <c r="M14" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="M14" s="4" t="s">
-        <v>288</v>
-      </c>
       <c r="N14" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="37.950000000000003" customHeight="1">
@@ -10506,40 +10509,40 @@
         <v>96</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>97</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F15" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="G15" s="5" t="s">
         <v>290</v>
       </c>
-      <c r="G15" s="5" t="s">
+      <c r="H15" s="5" t="s">
         <v>291</v>
       </c>
-      <c r="H15" s="5" t="s">
+      <c r="I15" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="I15" s="5" t="s">
+      <c r="J15" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="J15" s="5" t="s">
+      <c r="K15" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="K15" s="5" t="s">
+      <c r="L15" s="5" t="s">
         <v>295</v>
       </c>
-      <c r="L15" s="5" t="s">
+      <c r="M15" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="M15" s="5" t="s">
-        <v>297</v>
-      </c>
       <c r="N15" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="37.950000000000003" customHeight="1">
@@ -10550,40 +10553,40 @@
         <v>99</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>100</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>56</v>
       </c>
       <c r="G16" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="H16" s="4" t="s">
         <v>299</v>
       </c>
-      <c r="H16" s="4" t="s">
+      <c r="I16" s="4" t="s">
         <v>300</v>
       </c>
-      <c r="I16" s="4" t="s">
+      <c r="J16" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="K16" s="4" t="s">
         <v>301</v>
       </c>
-      <c r="J16" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="K16" s="4" t="s">
+      <c r="L16" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="L16" s="4" t="s">
+      <c r="M16" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="M16" s="4" t="s">
-        <v>304</v>
-      </c>
       <c r="N16" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="17" spans="1:16" ht="37.950000000000003" customHeight="1">
@@ -10594,40 +10597,40 @@
         <v>102</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>103</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>56</v>
       </c>
       <c r="G17" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="H17" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="H17" s="5" t="s">
+      <c r="I17" s="5" t="s">
         <v>308</v>
       </c>
-      <c r="I17" s="5" t="s">
+      <c r="J17" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="K17" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="J17" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="K17" s="5" t="s">
+      <c r="L17" s="5" t="s">
         <v>310</v>
       </c>
-      <c r="L17" s="5" t="s">
+      <c r="M17" s="5" t="s">
         <v>311</v>
       </c>
-      <c r="M17" s="5" t="s">
-        <v>312</v>
-      </c>
       <c r="N17" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="18" spans="1:16" ht="37.950000000000003" customHeight="1">
@@ -10638,40 +10641,40 @@
         <v>105</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>106</v>
       </c>
       <c r="E18" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="F18" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="F18" s="4" t="s">
-        <v>212</v>
-      </c>
       <c r="G18" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="H18" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="H18" s="4" t="s">
+      <c r="I18" s="4" t="s">
         <v>315</v>
       </c>
-      <c r="I18" s="4" t="s">
+      <c r="J18" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="K18" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="J18" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="K18" s="4" t="s">
+      <c r="L18" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="L18" s="4" t="s">
+      <c r="M18" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="M18" s="4" t="s">
-        <v>319</v>
-      </c>
       <c r="N18" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="19" spans="1:16" ht="61.95" customHeight="1">
@@ -10682,40 +10685,40 @@
         <v>108</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>109</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F19" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="G19" s="5" t="s">
         <v>321</v>
       </c>
-      <c r="G19" s="5" t="s">
+      <c r="H19" s="5" t="s">
         <v>322</v>
       </c>
-      <c r="H19" s="5" t="s">
+      <c r="I19" s="5" t="s">
         <v>323</v>
       </c>
-      <c r="I19" s="5" t="s">
+      <c r="J19" s="5" t="s">
         <v>324</v>
       </c>
-      <c r="J19" s="5" t="s">
+      <c r="K19" s="5" t="s">
         <v>325</v>
       </c>
-      <c r="K19" s="5" t="s">
+      <c r="L19" s="5" t="s">
         <v>326</v>
       </c>
-      <c r="L19" s="5" t="s">
+      <c r="M19" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="M19" s="5" t="s">
-        <v>328</v>
-      </c>
       <c r="N19" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="20" spans="1:16" ht="37.950000000000003" customHeight="1">
@@ -10726,38 +10729,38 @@
         <v>111</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>113</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>56</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H20" s="4"/>
       <c r="I20" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="K20" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="J20" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="K20" s="4" t="s">
+      <c r="L20" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="L20" s="4" t="s">
-        <v>334</v>
-      </c>
       <c r="M20" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="N20" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="21" spans="1:16" ht="37.950000000000003" customHeight="1">
@@ -10768,40 +10771,40 @@
         <v>115</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>116</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>56</v>
       </c>
       <c r="G21" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="H21" s="5" t="s">
         <v>337</v>
       </c>
-      <c r="H21" s="5" t="s">
+      <c r="I21" s="5" t="s">
         <v>338</v>
       </c>
-      <c r="I21" s="5" t="s">
+      <c r="J21" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="K21" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="J21" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="K21" s="5" t="s">
+      <c r="L21" s="5" t="s">
         <v>340</v>
       </c>
-      <c r="L21" s="5" t="s">
+      <c r="M21" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="M21" s="5" t="s">
-        <v>342</v>
-      </c>
       <c r="N21" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="22" spans="1:16" ht="37.950000000000003" customHeight="1">
@@ -10812,40 +10815,40 @@
         <v>118</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>119</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>56</v>
       </c>
       <c r="G22" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="H22" s="4" t="s">
         <v>345</v>
       </c>
-      <c r="H22" s="4" t="s">
+      <c r="I22" s="4" t="s">
         <v>346</v>
       </c>
-      <c r="I22" s="4" t="s">
+      <c r="J22" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="K22" s="4" t="s">
         <v>347</v>
       </c>
-      <c r="J22" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="K22" s="4" t="s">
+      <c r="L22" s="4" t="s">
         <v>348</v>
       </c>
-      <c r="L22" s="4" t="s">
+      <c r="M22" s="4" t="s">
         <v>349</v>
       </c>
-      <c r="M22" s="4" t="s">
-        <v>350</v>
-      </c>
       <c r="N22" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="23" spans="1:16" ht="37.950000000000003" customHeight="1">
@@ -10856,13 +10859,13 @@
         <v>121</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>122</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>56</v>
@@ -10882,10 +10885,10 @@
 heal_pct: 0.1 → 0.2</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="L23" s="5" t="str">
         <f>"War Song: Every 5 attacks, heal nearby allies for "&amp;TEXT(O23/100,"0%")&amp;" of their max HP."</f>
@@ -10896,7 +10899,7 @@
         <v>战歌：每第4次普通攻击治疗周围友军最大生命20%。</v>
       </c>
       <c r="N23" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="O23" s="5">
         <v>10</v>
@@ -10913,40 +10916,40 @@
         <v>124</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>126</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>56</v>
       </c>
       <c r="G24" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="H24" s="4" t="s">
         <v>355</v>
       </c>
-      <c r="H24" s="4" t="s">
+      <c r="I24" s="4" t="s">
         <v>356</v>
       </c>
-      <c r="I24" s="4" t="s">
+      <c r="J24" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="K24" s="4" t="s">
         <v>357</v>
       </c>
-      <c r="J24" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="K24" s="4" t="s">
+      <c r="L24" s="4" t="s">
         <v>358</v>
       </c>
-      <c r="L24" s="4" t="s">
+      <c r="M24" s="4" t="s">
         <v>359</v>
       </c>
-      <c r="M24" s="4" t="s">
-        <v>360</v>
-      </c>
       <c r="N24" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="25" spans="1:16" ht="37.950000000000003" customHeight="1">
@@ -10957,40 +10960,40 @@
         <v>128</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>129</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F25" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="G25" s="5" t="s">
         <v>362</v>
       </c>
-      <c r="G25" s="5" t="s">
+      <c r="H25" s="5" t="s">
         <v>363</v>
       </c>
-      <c r="H25" s="5" t="s">
+      <c r="I25" s="5" t="s">
         <v>364</v>
       </c>
-      <c r="I25" s="5" t="s">
+      <c r="J25" s="5" t="s">
         <v>365</v>
       </c>
-      <c r="J25" s="5" t="s">
+      <c r="K25" s="5" t="s">
         <v>366</v>
       </c>
-      <c r="K25" s="5" t="s">
+      <c r="L25" s="5" t="s">
         <v>367</v>
       </c>
-      <c r="L25" s="5" t="s">
+      <c r="M25" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="M25" s="5" t="s">
-        <v>369</v>
-      </c>
       <c r="N25" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="26" spans="1:16" ht="37.950000000000003" customHeight="1">
@@ -11001,40 +11004,40 @@
         <v>131</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>132</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F26" s="4" t="s">
         <v>56</v>
       </c>
       <c r="G26" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="H26" s="4" t="s">
         <v>371</v>
       </c>
-      <c r="H26" s="4" t="s">
+      <c r="I26" s="4" t="s">
         <v>372</v>
       </c>
-      <c r="I26" s="4" t="s">
+      <c r="J26" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="K26" s="4" t="s">
         <v>373</v>
       </c>
-      <c r="J26" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="K26" s="4" t="s">
+      <c r="L26" s="4" t="s">
         <v>374</v>
       </c>
-      <c r="L26" s="4" t="s">
+      <c r="M26" s="4" t="s">
         <v>375</v>
       </c>
-      <c r="M26" s="4" t="s">
-        <v>376</v>
-      </c>
       <c r="N26" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="27" spans="1:16" ht="61.95" customHeight="1">
@@ -11045,40 +11048,40 @@
         <v>134</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>136</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F27" s="5" t="s">
         <v>56</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>1102</v>
+        <v>1096</v>
       </c>
       <c r="H27" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="I27" s="5" t="s">
         <v>379</v>
       </c>
-      <c r="I27" s="5" t="s">
+      <c r="J27" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="K27" s="5" t="s">
         <v>380</v>
       </c>
-      <c r="J27" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="K27" s="5" t="s">
-        <v>381</v>
-      </c>
       <c r="L27" s="5" t="s">
-        <v>1103</v>
+        <v>1097</v>
       </c>
       <c r="M27" s="5" t="s">
-        <v>1104</v>
+        <v>1098</v>
       </c>
       <c r="N27" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="28" spans="1:16" ht="37.950000000000003" customHeight="1">
@@ -11089,40 +11092,40 @@
         <v>138</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>140</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>56</v>
       </c>
       <c r="G28" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="H28" s="4" t="s">
         <v>383</v>
       </c>
-      <c r="H28" s="4" t="s">
+      <c r="I28" s="4" t="s">
         <v>384</v>
       </c>
-      <c r="I28" s="4" t="s">
+      <c r="J28" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="K28" s="4" t="s">
         <v>385</v>
       </c>
-      <c r="J28" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="K28" s="4" t="s">
+      <c r="L28" s="4" t="s">
         <v>386</v>
       </c>
-      <c r="L28" s="4" t="s">
+      <c r="M28" s="4" t="s">
         <v>387</v>
       </c>
-      <c r="M28" s="4" t="s">
-        <v>388</v>
-      </c>
       <c r="N28" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="29" spans="1:16" ht="37.950000000000003" customHeight="1">
@@ -11133,40 +11136,40 @@
         <v>142</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>143</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F29" s="5" t="s">
         <v>56</v>
       </c>
       <c r="G29" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="H29" s="5" t="s">
         <v>389</v>
       </c>
-      <c r="H29" s="5" t="s">
+      <c r="I29" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="J29" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="K29" s="5" t="s">
         <v>390</v>
       </c>
-      <c r="I29" s="5" t="s">
-        <v>332</v>
-      </c>
-      <c r="J29" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="K29" s="5" t="s">
+      <c r="L29" s="5" t="s">
         <v>391</v>
       </c>
-      <c r="L29" s="5" t="s">
-        <v>392</v>
-      </c>
       <c r="M29" s="5" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="N29" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="30" spans="1:16" ht="37.950000000000003" customHeight="1">
@@ -11177,13 +11180,13 @@
         <v>145</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>146</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F30" s="4" t="s">
         <v>56</v>
@@ -11201,10 +11204,10 @@
         <v>damage_atk_pct: 2.5 → 3.521127</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="L30" s="4" t="str">
         <f>"Death Poison Burst: On death, deal "&amp;TEXT(O30/40,"0%")&amp;" ATK true damage to surrounding enemies and apply poison (up to 2 separate damage stacks)."</f>
@@ -11215,7 +11218,7 @@
         <v>死亡毒爆：死亡时对周围敌人造成自身攻击250%真实伤害，并施加中毒（最多2层，分别扣血）。</v>
       </c>
       <c r="N30" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="O30" s="5">
         <v>100</v>
@@ -11232,40 +11235,40 @@
         <v>148</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>140</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F31" s="5" t="s">
         <v>56</v>
       </c>
       <c r="G31" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="H31" s="5" t="s">
         <v>383</v>
       </c>
-      <c r="H31" s="5" t="s">
-        <v>384</v>
-      </c>
       <c r="I31" s="5" t="s">
+        <v>395</v>
+      </c>
+      <c r="J31" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="K31" s="5" t="s">
         <v>396</v>
       </c>
-      <c r="J31" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="K31" s="5" t="s">
-        <v>397</v>
-      </c>
       <c r="L31" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="M31" s="5" t="s">
         <v>387</v>
       </c>
-      <c r="M31" s="5" t="s">
-        <v>388</v>
-      </c>
       <c r="N31" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="32" spans="1:16" ht="37.950000000000003" customHeight="1">
@@ -11276,40 +11279,40 @@
         <v>150</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>151</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>56</v>
       </c>
       <c r="G32" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="H32" s="4" t="s">
         <v>400</v>
       </c>
-      <c r="H32" s="4" t="s">
+      <c r="I32" s="4" t="s">
         <v>401</v>
       </c>
-      <c r="I32" s="4" t="s">
+      <c r="J32" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="K32" s="4" t="s">
         <v>402</v>
       </c>
-      <c r="J32" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="K32" s="4" t="s">
+      <c r="L32" s="4" t="s">
         <v>403</v>
       </c>
-      <c r="L32" s="4" t="s">
+      <c r="M32" s="4" t="s">
         <v>404</v>
       </c>
-      <c r="M32" s="4" t="s">
-        <v>405</v>
-      </c>
       <c r="N32" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="37.950000000000003" customHeight="1">
@@ -11320,480 +11323,480 @@
         <v>153</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F33" s="5" t="s">
         <v>56</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>407</v>
+        <v>1203</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>408</v>
+        <v>1204</v>
       </c>
       <c r="I33" s="5" t="s">
-        <v>409</v>
+        <v>1205</v>
       </c>
       <c r="J33" s="5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="K33" s="5" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="L33" s="5" t="s">
-        <v>411</v>
+        <v>1206</v>
       </c>
       <c r="M33" s="5" t="s">
-        <v>412</v>
+        <v>1207</v>
       </c>
       <c r="N33" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="34" spans="1:14" ht="61.95" customHeight="1">
       <c r="A34" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="B34" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="C34" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="D34" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="C34" s="4" t="s">
-        <v>413</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>158</v>
-      </c>
       <c r="E34" s="4" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="F34" s="4" t="s">
         <v>56</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="K34" s="4" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="L34" s="4" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="M34" s="4" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="N34" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="35" spans="1:14" ht="61.95" customHeight="1">
       <c r="A35" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="B35" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="C35" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="D35" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="C35" s="5" t="s">
-        <v>421</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>161</v>
-      </c>
       <c r="E35" s="5" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="F35" s="5" t="s">
         <v>56</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="J35" s="5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="K35" s="5" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="L35" s="5" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="M35" s="5" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="N35" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="36" spans="1:14" ht="37.950000000000003" customHeight="1">
       <c r="A36" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="B36" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="B36" s="4" t="s">
-        <v>163</v>
-      </c>
       <c r="C36" s="4" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="F36" s="4" t="s">
         <v>56</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="K36" s="4" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="L36" s="4" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="M36" s="4" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="N36" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="37" spans="1:14" ht="61.95" customHeight="1">
       <c r="A37" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="B37" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="C37" s="5" t="s">
+        <v>431</v>
+      </c>
+      <c r="D37" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="C37" s="5" t="s">
+      <c r="E37" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>433</v>
+      </c>
+      <c r="H37" s="5" t="s">
+        <v>434</v>
+      </c>
+      <c r="I37" s="5" t="s">
+        <v>435</v>
+      </c>
+      <c r="J37" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="K37" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="L37" s="5" t="s">
         <v>437</v>
       </c>
-      <c r="D37" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="E37" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="F37" s="5" t="s">
+      <c r="M37" s="5" t="s">
         <v>438</v>
       </c>
-      <c r="G37" s="5" t="s">
-        <v>439</v>
-      </c>
-      <c r="H37" s="5" t="s">
-        <v>440</v>
-      </c>
-      <c r="I37" s="5" t="s">
-        <v>441</v>
-      </c>
-      <c r="J37" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="K37" s="5" t="s">
-        <v>442</v>
-      </c>
-      <c r="L37" s="5" t="s">
-        <v>443</v>
-      </c>
-      <c r="M37" s="5" t="s">
-        <v>444</v>
-      </c>
       <c r="N37" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="38" spans="1:14" ht="61.95" customHeight="1">
       <c r="A38" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B38" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="C38" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="D38" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="C38" s="4" t="s">
-        <v>445</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>171</v>
-      </c>
       <c r="E38" s="4" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="F38" s="4" t="s">
         <v>56</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="K38" s="4" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="L38" s="4" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="M38" s="4" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="N38" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="37.950000000000003" customHeight="1">
       <c r="A39" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="B39" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="C39" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="D39" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="C39" s="5" t="s">
-        <v>453</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>174</v>
-      </c>
       <c r="E39" s="5" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="F39" s="5" t="s">
         <v>56</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="I39" s="5" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="J39" s="5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="K39" s="5" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="L39" s="5" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="M39" s="5" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="N39" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="37.950000000000003" customHeight="1">
       <c r="A40" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="B40" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="C40" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="D40" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="C40" s="4" t="s">
-        <v>460</v>
-      </c>
-      <c r="D40" s="4" t="s">
-        <v>177</v>
-      </c>
       <c r="E40" s="4" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="F40" s="4" t="s">
         <v>56</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="K40" s="4" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="L40" s="4" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="M40" s="4" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="N40" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="41" spans="1:14" ht="61.95" customHeight="1">
       <c r="A41" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="B41" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="B41" s="5" t="s">
+      <c r="C41" s="5" t="s">
+        <v>461</v>
+      </c>
+      <c r="D41" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="C41" s="5" t="s">
+      <c r="E41" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="G41" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="H41" s="5" t="s">
+        <v>464</v>
+      </c>
+      <c r="I41" s="5" t="s">
+        <v>465</v>
+      </c>
+      <c r="J41" s="5" t="s">
+        <v>466</v>
+      </c>
+      <c r="K41" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="D41" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="E41" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="F41" s="5" t="s">
+      <c r="L41" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="G41" s="5" t="s">
+      <c r="M41" s="5" t="s">
         <v>469</v>
       </c>
-      <c r="H41" s="5" t="s">
-        <v>470</v>
-      </c>
-      <c r="I41" s="5" t="s">
-        <v>471</v>
-      </c>
-      <c r="J41" s="5" t="s">
-        <v>472</v>
-      </c>
-      <c r="K41" s="5" t="s">
-        <v>473</v>
-      </c>
-      <c r="L41" s="5" t="s">
-        <v>474</v>
-      </c>
-      <c r="M41" s="5" t="s">
-        <v>475</v>
-      </c>
       <c r="N41" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="37.950000000000003" customHeight="1">
       <c r="A42" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="B42" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="B42" s="4" t="s">
+      <c r="C42" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="D42" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="C42" s="4" t="s">
-        <v>476</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>183</v>
-      </c>
       <c r="E42" s="4" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="F42" s="4" t="s">
         <v>56</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="K42" s="4" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="L42" s="4" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="M42" s="4" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="N42" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="43" spans="1:14" ht="61.95" customHeight="1">
       <c r="A43" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="B43" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="B43" s="5" t="s">
+      <c r="C43" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="D43" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="C43" s="5" t="s">
+      <c r="E43" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>479</v>
+      </c>
+      <c r="H43" s="5" t="s">
+        <v>480</v>
+      </c>
+      <c r="I43" s="5" t="s">
+        <v>481</v>
+      </c>
+      <c r="J43" s="5" t="s">
+        <v>482</v>
+      </c>
+      <c r="K43" s="5" t="s">
         <v>483</v>
       </c>
-      <c r="D43" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="F43" s="5" t="s">
+      <c r="L43" s="5" t="s">
         <v>484</v>
       </c>
-      <c r="G43" s="5" t="s">
+      <c r="M43" s="5" t="s">
         <v>485</v>
       </c>
-      <c r="H43" s="5" t="s">
-        <v>486</v>
-      </c>
-      <c r="I43" s="5" t="s">
-        <v>487</v>
-      </c>
-      <c r="J43" s="5" t="s">
-        <v>488</v>
-      </c>
-      <c r="K43" s="5" t="s">
-        <v>489</v>
-      </c>
-      <c r="L43" s="5" t="s">
-        <v>490</v>
-      </c>
-      <c r="M43" s="5" t="s">
-        <v>491</v>
-      </c>
       <c r="N43" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
   </sheetData>
@@ -11823,223 +11826,223 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="34.049999999999997" customHeight="1">
-      <c r="A1" s="9" t="s">
-        <v>1105</v>
-      </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
+      <c r="A1" s="11" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
     </row>
     <row r="2" spans="1:10" ht="31.95" customHeight="1">
-      <c r="A2" s="10" t="s">
-        <v>1106</v>
-      </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
+      <c r="A2" s="12" t="s">
+        <v>1100</v>
+      </c>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
     </row>
     <row r="3" spans="1:10" ht="28.05" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>494</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>495</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>496</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>497</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>498</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>499</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>500</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="37.950000000000003" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>79</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>80</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="37.950000000000003" customHeight="1">
       <c r="A5" s="5" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>55</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="H5" s="5" t="s">
         <v>80</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="37.950000000000003" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>79</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>80</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="37.950000000000003" customHeight="1">
       <c r="A7" s="5" t="s">
+        <v>516</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>517</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>518</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>519</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>520</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>521</v>
+      </c>
+      <c r="G7" s="5" t="s">
         <v>522</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="H7" s="5" t="s">
         <v>523</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="I7" s="5" t="s">
+        <v>501</v>
+      </c>
+      <c r="J7" s="5" t="s">
         <v>524</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>525</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>526</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>527</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>528</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>529</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>507</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>530</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="37.950000000000003" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>55</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
     </row>
   </sheetData>
@@ -12065,403 +12068,403 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="34.049999999999997" customHeight="1">
-      <c r="A1" s="9" t="s">
-        <v>538</v>
-      </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
+      <c r="A1" s="11" t="s">
+        <v>532</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
     </row>
     <row r="2" spans="1:6" ht="31.95" customHeight="1">
-      <c r="A2" s="10" t="s">
-        <v>539</v>
-      </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
+      <c r="A2" s="12" t="s">
+        <v>533</v>
+      </c>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
     </row>
     <row r="3" spans="1:6" ht="28.05" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="37.950000000000003" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="B4" s="4">
         <v>1</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="37.950000000000003" customHeight="1">
       <c r="A5" s="5" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="B5" s="5">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="37.950000000000003" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="B6" s="4">
         <v>7</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="37.950000000000003" customHeight="1">
       <c r="A7" s="5" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="B7" s="5">
         <v>1</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="37.950000000000003" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="B8" s="4">
         <v>2</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>561</v>
+        <v>555</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="37.950000000000003" customHeight="1">
       <c r="A9" s="5" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="B9" s="5">
         <v>5</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>563</v>
+        <v>557</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>564</v>
+        <v>558</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="37.950000000000003" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="B10" s="4">
         <v>7</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>565</v>
+        <v>559</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>566</v>
+        <v>560</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>567</v>
+        <v>561</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="37.950000000000003" customHeight="1">
       <c r="A11" s="5" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="B11" s="5">
         <v>1</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>569</v>
+        <v>563</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="37.950000000000003" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="B12" s="4">
         <v>2</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>572</v>
+        <v>566</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>573</v>
+        <v>567</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>574</v>
+        <v>568</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="37.950000000000003" customHeight="1">
       <c r="A13" s="5" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="B13" s="5">
         <v>4</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>576</v>
+        <v>570</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>574</v>
+        <v>568</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="37.950000000000003" customHeight="1">
       <c r="A14" s="4" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="B14" s="4">
         <v>7</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>577</v>
+        <v>571</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>579</v>
+        <v>573</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="37.950000000000003" customHeight="1">
       <c r="A15" s="5" t="s">
-        <v>580</v>
+        <v>574</v>
       </c>
       <c r="B15" s="5">
         <v>1</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>583</v>
+        <v>577</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="37.950000000000003" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>580</v>
+        <v>574</v>
       </c>
       <c r="B16" s="4">
         <v>2</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>586</v>
+        <v>580</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="37.950000000000003" customHeight="1">
       <c r="A17" s="5" t="s">
-        <v>580</v>
+        <v>574</v>
       </c>
       <c r="B17" s="5">
         <v>7</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>588</v>
+        <v>582</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>589</v>
+        <v>583</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="37.950000000000003" customHeight="1">
       <c r="A18" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B18" s="4">
         <v>1</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="37.950000000000003" customHeight="1">
       <c r="A19" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B19" s="5">
         <v>2</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="37.950000000000003" customHeight="1">
       <c r="A20" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B20" s="4">
         <v>4</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>598</v>
+        <v>592</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="37.950000000000003" customHeight="1">
       <c r="A21" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B21" s="5">
         <v>7</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>599</v>
+        <v>593</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>601</v>
+        <v>595</v>
       </c>
     </row>
   </sheetData>
@@ -12497,52 +12500,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="34.049999999999997" customHeight="1">
-      <c r="A1" s="9" t="s">
-        <v>602</v>
-      </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
-      <c r="N1" s="9"/>
-      <c r="O1" s="9"/>
-      <c r="P1" s="9"/>
-      <c r="Q1" s="9"/>
-      <c r="R1" s="9"/>
-      <c r="S1" s="9"/>
-      <c r="T1" s="9"/>
+      <c r="A1" s="11" t="s">
+        <v>596</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="11"/>
+      <c r="M1" s="11"/>
+      <c r="N1" s="11"/>
+      <c r="O1" s="11"/>
+      <c r="P1" s="11"/>
+      <c r="Q1" s="11"/>
+      <c r="R1" s="11"/>
+      <c r="S1" s="11"/>
+      <c r="T1" s="11"/>
     </row>
     <row r="2" spans="1:20" ht="31.95" customHeight="1">
-      <c r="A2" s="10" t="s">
-        <v>603</v>
-      </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
-      <c r="O2" s="10"/>
-      <c r="P2" s="10"/>
-      <c r="Q2" s="10"/>
-      <c r="R2" s="10"/>
-      <c r="S2" s="10"/>
-      <c r="T2" s="10"/>
+      <c r="A2" s="12" t="s">
+        <v>597</v>
+      </c>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12"/>
+      <c r="M2" s="12"/>
+      <c r="N2" s="12"/>
+      <c r="O2" s="12"/>
+      <c r="P2" s="12"/>
+      <c r="Q2" s="12"/>
+      <c r="R2" s="12"/>
+      <c r="S2" s="12"/>
+      <c r="T2" s="12"/>
     </row>
     <row r="3" spans="1:20" ht="28.05" customHeight="1">
       <c r="A3" s="3" t="s">
@@ -12552,19 +12555,19 @@
         <v>23</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>605</v>
+        <v>599</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>40</v>
@@ -12576,45 +12579,45 @@
         <v>44</v>
       </c>
       <c r="K3" s="3" t="s">
+        <v>602</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>603</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>604</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="Q3" s="3" t="s">
         <v>608</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="R3" s="3" t="s">
         <v>609</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="S3" s="3" t="s">
         <v>610</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="T3" s="3" t="s">
         <v>611</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>612</v>
-      </c>
-      <c r="P3" s="3" t="s">
-        <v>613</v>
-      </c>
-      <c r="Q3" s="3" t="s">
-        <v>614</v>
-      </c>
-      <c r="R3" s="3" t="s">
-        <v>615</v>
-      </c>
-      <c r="S3" s="3" t="s">
-        <v>616</v>
-      </c>
-      <c r="T3" s="3" t="s">
-        <v>617</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="37.950000000000003" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>618</v>
+        <v>612</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>619</v>
+        <v>613</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>60</v>
@@ -12647,36 +12650,36 @@
         <v>680</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>621</v>
+        <v>615</v>
       </c>
       <c r="O4" s="4" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="P4" s="4" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="R4" s="4" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="S4" s="4" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="37.950000000000003" customHeight="1">
       <c r="A5" s="5" t="s">
-        <v>627</v>
+        <v>621</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>628</v>
+        <v>622</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>60</v>
@@ -12709,36 +12712,36 @@
         <v>624</v>
       </c>
       <c r="N5" s="5" t="s">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="O5" s="5" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="P5" s="5" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="Q5" s="5" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="R5" s="5" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="S5" s="5" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="T5" s="5" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="6" spans="1:20" ht="37.950000000000003" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>631</v>
+        <v>625</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>60</v>
@@ -12771,36 +12774,36 @@
         <v>551</v>
       </c>
       <c r="N6" s="4" t="s">
-        <v>632</v>
+        <v>626</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="P6" s="4" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="S6" s="4" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="37.950000000000003" customHeight="1">
       <c r="A7" s="5" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>60</v>
@@ -12833,36 +12836,36 @@
         <v>1144</v>
       </c>
       <c r="N7" s="5" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="O7" s="5" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="P7" s="5" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="Q7" s="5" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="R7" s="5" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="S7" s="5" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="T7" s="5" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="37.950000000000003" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>636</v>
+        <v>630</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>637</v>
+        <v>631</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>60</v>
@@ -12895,36 +12898,36 @@
         <v>686</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>638</v>
+        <v>632</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="R8" s="4" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="S8" s="4" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="37.950000000000003" customHeight="1">
       <c r="A9" s="5" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>60</v>
@@ -12957,36 +12960,36 @@
         <v>756</v>
       </c>
       <c r="N9" s="5" t="s">
-        <v>641</v>
+        <v>635</v>
       </c>
       <c r="O9" s="5" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="P9" s="5" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="Q9" s="5" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="R9" s="5" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="S9" s="5" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="T9" s="5" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="37.950000000000003" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>642</v>
+        <v>636</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>643</v>
+        <v>637</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>644</v>
+        <v>638</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>64</v>
@@ -13019,36 +13022,36 @@
         <v>974</v>
       </c>
       <c r="N10" s="4" t="s">
-        <v>645</v>
+        <v>639</v>
       </c>
       <c r="O10" s="4" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="P10" s="4" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="R10" s="4" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="S10" s="4" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="T10" s="4" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="37.950000000000003" customHeight="1">
       <c r="A11" s="5" t="s">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>644</v>
+        <v>638</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>64</v>
@@ -13081,36 +13084,36 @@
         <v>851</v>
       </c>
       <c r="N11" s="5" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="O11" s="5" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="P11" s="5" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="Q11" s="5" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="R11" s="5" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="S11" s="5" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="T11" s="5" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="37.950000000000003" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>650</v>
+        <v>644</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>644</v>
+        <v>638</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>64</v>
@@ -13143,36 +13146,36 @@
         <v>734</v>
       </c>
       <c r="N12" s="4" t="s">
-        <v>651</v>
+        <v>645</v>
       </c>
       <c r="O12" s="4" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="P12" s="4" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="Q12" s="4" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="S12" s="4" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="T12" s="4" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="13" spans="1:20" ht="37.950000000000003" customHeight="1">
       <c r="A13" s="5" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>653</v>
+        <v>647</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>644</v>
+        <v>638</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>64</v>
@@ -13205,36 +13208,36 @@
         <v>1062</v>
       </c>
       <c r="N13" s="5" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="O13" s="5" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="P13" s="5" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="Q13" s="5" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="R13" s="5" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="S13" s="5" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="T13" s="5" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="14" spans="1:20" ht="37.950000000000003" customHeight="1">
       <c r="A14" s="4" t="s">
-        <v>655</v>
+        <v>649</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>656</v>
+        <v>650</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>644</v>
+        <v>638</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>64</v>
@@ -13267,36 +13270,36 @@
         <v>1299</v>
       </c>
       <c r="N14" s="4" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
       <c r="O14" s="4" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="P14" s="4" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="Q14" s="4" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="S14" s="4" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="T14" s="4" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="15" spans="1:20" ht="37.950000000000003" customHeight="1">
       <c r="A15" s="5" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>659</v>
+        <v>653</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>644</v>
+        <v>638</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>64</v>
@@ -13329,36 +13332,36 @@
         <v>1680</v>
       </c>
       <c r="N15" s="5" t="s">
-        <v>660</v>
+        <v>654</v>
       </c>
       <c r="O15" s="5" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="P15" s="5" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="Q15" s="5" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="S15" s="5" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="T15" s="5" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="16" spans="1:20" ht="37.950000000000003" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>661</v>
+        <v>655</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>662</v>
+        <v>656</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>663</v>
+        <v>657</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>54</v>
@@ -13391,36 +13394,36 @@
         <v>499</v>
       </c>
       <c r="N16" s="4" t="s">
-        <v>664</v>
+        <v>658</v>
       </c>
       <c r="O16" s="4" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="P16" s="4" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="Q16" s="4" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="R16" s="4" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="S16" s="4" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="T16" s="4" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="17" spans="1:20" ht="37.950000000000003" customHeight="1">
       <c r="A17" s="5" t="s">
-        <v>665</v>
+        <v>659</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>663</v>
+        <v>657</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>54</v>
@@ -13453,36 +13456,36 @@
         <v>588</v>
       </c>
       <c r="N17" s="5" t="s">
-        <v>667</v>
+        <v>661</v>
       </c>
       <c r="O17" s="5" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="P17" s="5" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="Q17" s="5" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="R17" s="5" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="S17" s="5" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="T17" s="5" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="18" spans="1:20" ht="37.950000000000003" customHeight="1">
       <c r="A18" s="4" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>663</v>
+        <v>657</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>54</v>
@@ -13515,36 +13518,36 @@
         <v>704</v>
       </c>
       <c r="N18" s="4" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
       <c r="O18" s="4" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="P18" s="4" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="Q18" s="4" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="R18" s="4" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="S18" s="4" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="T18" s="4" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="19" spans="1:20" ht="37.950000000000003" customHeight="1">
       <c r="A19" s="5" t="s">
-        <v>671</v>
+        <v>665</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>672</v>
+        <v>666</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>663</v>
+        <v>657</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>54</v>
@@ -13580,22 +13583,22 @@
         <v>143</v>
       </c>
       <c r="O19" s="5" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="P19" s="5" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="Q19" s="5" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="R19" s="5" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="S19" s="5" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="T19" s="5" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
   </sheetData>
@@ -13629,70 +13632,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="34.049999999999997" customHeight="1">
-      <c r="A1" s="9" t="s">
-        <v>673</v>
-      </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
-      <c r="N1" s="9"/>
-      <c r="O1" s="9"/>
-      <c r="P1" s="9"/>
-      <c r="Q1" s="9"/>
-      <c r="R1" s="9"/>
-      <c r="S1" s="9"/>
-      <c r="T1" s="9"/>
-      <c r="U1" s="9"/>
-      <c r="V1" s="9"/>
-      <c r="W1" s="9"/>
-      <c r="X1" s="9"/>
-      <c r="Y1" s="9"/>
-      <c r="Z1" s="9"/>
-      <c r="AA1" s="9"/>
-      <c r="AB1" s="9"/>
-      <c r="AC1" s="9"/>
+      <c r="A1" s="11" t="s">
+        <v>667</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="11"/>
+      <c r="M1" s="11"/>
+      <c r="N1" s="11"/>
+      <c r="O1" s="11"/>
+      <c r="P1" s="11"/>
+      <c r="Q1" s="11"/>
+      <c r="R1" s="11"/>
+      <c r="S1" s="11"/>
+      <c r="T1" s="11"/>
+      <c r="U1" s="11"/>
+      <c r="V1" s="11"/>
+      <c r="W1" s="11"/>
+      <c r="X1" s="11"/>
+      <c r="Y1" s="11"/>
+      <c r="Z1" s="11"/>
+      <c r="AA1" s="11"/>
+      <c r="AB1" s="11"/>
+      <c r="AC1" s="11"/>
     </row>
     <row r="2" spans="1:29" ht="31.95" customHeight="1">
-      <c r="A2" s="10" t="s">
-        <v>1107</v>
-      </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
-      <c r="O2" s="10"/>
-      <c r="P2" s="10"/>
-      <c r="Q2" s="10"/>
-      <c r="R2" s="10"/>
-      <c r="S2" s="10"/>
-      <c r="T2" s="10"/>
-      <c r="U2" s="10"/>
-      <c r="V2" s="10"/>
-      <c r="W2" s="10"/>
-      <c r="X2" s="10"/>
-      <c r="Y2" s="10"/>
-      <c r="Z2" s="10"/>
-      <c r="AA2" s="10"/>
-      <c r="AB2" s="10"/>
-      <c r="AC2" s="10"/>
+      <c r="A2" s="12" t="s">
+        <v>1101</v>
+      </c>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12"/>
+      <c r="M2" s="12"/>
+      <c r="N2" s="12"/>
+      <c r="O2" s="12"/>
+      <c r="P2" s="12"/>
+      <c r="Q2" s="12"/>
+      <c r="R2" s="12"/>
+      <c r="S2" s="12"/>
+      <c r="T2" s="12"/>
+      <c r="U2" s="12"/>
+      <c r="V2" s="12"/>
+      <c r="W2" s="12"/>
+      <c r="X2" s="12"/>
+      <c r="Y2" s="12"/>
+      <c r="Z2" s="12"/>
+      <c r="AA2" s="12"/>
+      <c r="AB2" s="12"/>
+      <c r="AC2" s="12"/>
     </row>
     <row r="3" spans="1:29" ht="28.05" customHeight="1">
       <c r="A3" s="3" t="s">
@@ -13705,49 +13708,49 @@
         <v>25</v>
       </c>
       <c r="D3" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>669</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>670</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>671</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>672</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>673</v>
+      </c>
+      <c r="J3" s="3" t="s">
         <v>674</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="K3" s="3" t="s">
         <v>675</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="L3" s="3" t="s">
         <v>676</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="M3" s="3" t="s">
         <v>677</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="N3" s="3" t="s">
         <v>678</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="O3" s="3" t="s">
         <v>679</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="P3" s="3" t="s">
         <v>680</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="Q3" s="3" t="s">
         <v>681</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="R3" s="3" t="s">
         <v>682</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>683</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>684</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>685</v>
-      </c>
-      <c r="P3" s="3" t="s">
-        <v>686</v>
-      </c>
-      <c r="Q3" s="3" t="s">
-        <v>687</v>
-      </c>
-      <c r="R3" s="3" t="s">
-        <v>688</v>
       </c>
       <c r="S3" s="3" t="s">
         <v>40</v>
@@ -13756,39 +13759,39 @@
         <v>42</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="V3" s="3" t="s">
-        <v>609</v>
+        <v>603</v>
       </c>
       <c r="W3" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="X3" s="3" t="s">
         <v>50</v>
       </c>
       <c r="Y3" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Z3" s="3" t="s">
-        <v>690</v>
+        <v>684</v>
       </c>
       <c r="AA3" s="3" t="s">
-        <v>691</v>
+        <v>685</v>
       </c>
       <c r="AB3" s="3" t="s">
-        <v>692</v>
+        <v>686</v>
       </c>
       <c r="AC3" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="4" spans="1:29" ht="37.950000000000003" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>694</v>
+        <v>688</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>60</v>
@@ -13863,33 +13866,33 @@
         <v>1794</v>
       </c>
       <c r="W4" s="4" t="s">
-        <v>695</v>
+        <v>689</v>
       </c>
       <c r="X4" s="4" t="s">
-        <v>696</v>
+        <v>690</v>
       </c>
       <c r="Y4" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Z4" s="4" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
       <c r="AA4" s="4">
         <v>10</v>
       </c>
       <c r="AB4" s="4" t="s">
-        <v>1108</v>
+        <v>1102</v>
       </c>
       <c r="AC4" s="4" t="s">
-        <v>1109</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="5" spans="1:29" ht="37.950000000000003" customHeight="1">
       <c r="A5" s="5" t="s">
-        <v>698</v>
+        <v>692</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>60</v>
@@ -13964,33 +13967,33 @@
         <v>736</v>
       </c>
       <c r="W5" s="5" t="s">
-        <v>700</v>
+        <v>694</v>
       </c>
       <c r="X5" s="5" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
       <c r="Y5" s="5" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="Z5" s="5" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
       <c r="AA5" s="5">
         <v>0</v>
       </c>
       <c r="AB5" s="5" t="s">
-        <v>1110</v>
+        <v>1104</v>
       </c>
       <c r="AC5" s="5" t="s">
-        <v>1111</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="6" spans="1:29" ht="37.950000000000003" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>703</v>
+        <v>697</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>704</v>
+        <v>698</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>54</v>
@@ -14065,33 +14068,33 @@
         <v>1160</v>
       </c>
       <c r="W6" s="4" t="s">
-        <v>705</v>
+        <v>699</v>
       </c>
       <c r="X6" s="4" t="s">
-        <v>706</v>
+        <v>700</v>
       </c>
       <c r="Y6" s="4" t="s">
-        <v>707</v>
+        <v>701</v>
       </c>
       <c r="Z6" s="4" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
       <c r="AA6" s="4">
         <v>59</v>
       </c>
       <c r="AB6" s="4" t="s">
-        <v>1112</v>
+        <v>1106</v>
       </c>
       <c r="AC6" s="4" t="s">
-        <v>1113</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="7" spans="1:29" ht="37.950000000000003" customHeight="1">
       <c r="A7" s="5" t="s">
-        <v>708</v>
+        <v>702</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>709</v>
+        <v>703</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>54</v>
@@ -14166,33 +14169,33 @@
         <v>600</v>
       </c>
       <c r="W7" s="5" t="s">
-        <v>710</v>
+        <v>704</v>
       </c>
       <c r="X7" s="5" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="Y7" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Z7" s="5" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
       <c r="AA7" s="5">
         <v>8</v>
       </c>
       <c r="AB7" s="5" t="s">
-        <v>1114</v>
+        <v>1108</v>
       </c>
       <c r="AC7" s="5" t="s">
-        <v>1115</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="8" spans="1:29" ht="37.950000000000003" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>64</v>
@@ -14267,33 +14270,33 @@
         <v>1183</v>
       </c>
       <c r="W8" s="4" t="s">
-        <v>714</v>
+        <v>708</v>
       </c>
       <c r="X8" s="4" t="s">
-        <v>715</v>
+        <v>709</v>
       </c>
       <c r="Y8" s="4" t="s">
-        <v>716</v>
+        <v>710</v>
       </c>
       <c r="Z8" s="4" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
       <c r="AA8" s="4">
         <v>0</v>
       </c>
       <c r="AB8" s="4" t="s">
-        <v>1116</v>
+        <v>1110</v>
       </c>
       <c r="AC8" s="4" t="s">
-        <v>1117</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="9" spans="1:29" ht="37.950000000000003" customHeight="1">
       <c r="A9" s="5" t="s">
-        <v>717</v>
+        <v>711</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>54</v>
@@ -14368,33 +14371,33 @@
         <v>828</v>
       </c>
       <c r="W9" s="5" t="s">
-        <v>719</v>
+        <v>713</v>
       </c>
       <c r="X9" s="5" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
       <c r="Y9" s="5" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
       <c r="Z9" s="5" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
       <c r="AA9" s="5">
         <v>0</v>
       </c>
       <c r="AB9" s="5" t="s">
-        <v>1118</v>
+        <v>1112</v>
       </c>
       <c r="AC9" s="5" t="s">
-        <v>1119</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="10" spans="1:29" ht="37.950000000000003" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>723</v>
+        <v>717</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>54</v>
@@ -14469,33 +14472,33 @@
         <v>1071</v>
       </c>
       <c r="W10" s="4" t="s">
-        <v>724</v>
+        <v>718</v>
       </c>
       <c r="X10" s="4" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="Y10" s="4" t="s">
-        <v>726</v>
+        <v>720</v>
       </c>
       <c r="Z10" s="4" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
       <c r="AA10" s="4">
         <v>0</v>
       </c>
       <c r="AB10" s="4" t="s">
-        <v>1120</v>
+        <v>1114</v>
       </c>
       <c r="AC10" s="4" t="s">
-        <v>1121</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="11" spans="1:29" ht="37.950000000000003" customHeight="1">
       <c r="A11" s="5" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>64</v>
@@ -14570,33 +14573,33 @@
         <v>864</v>
       </c>
       <c r="W11" s="5" t="s">
-        <v>729</v>
+        <v>723</v>
       </c>
       <c r="X11" s="5" t="s">
-        <v>730</v>
+        <v>724</v>
       </c>
       <c r="Y11" s="5" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="Z11" s="5" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
       <c r="AA11" s="5">
         <v>0</v>
       </c>
       <c r="AB11" s="5" t="s">
-        <v>1122</v>
+        <v>1116</v>
       </c>
       <c r="AC11" s="5" t="s">
-        <v>1123</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="12" spans="1:29" ht="37.950000000000003" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>733</v>
+        <v>727</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>60</v>
@@ -14671,543 +14674,543 @@
         <v>1090</v>
       </c>
       <c r="W12" s="4" t="s">
-        <v>734</v>
+        <v>728</v>
       </c>
       <c r="X12" s="4" t="s">
-        <v>735</v>
+        <v>729</v>
       </c>
       <c r="Y12" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Z12" s="4" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
       <c r="AA12" s="4">
         <v>6</v>
       </c>
       <c r="AB12" s="4" t="s">
-        <v>1124</v>
+        <v>1118</v>
       </c>
       <c r="AC12" s="4" t="s">
-        <v>1125</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="15" spans="1:29" ht="22.05" customHeight="1">
       <c r="B15" s="3" t="s">
-        <v>1126</v>
+        <v>1120</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>1127</v>
+        <v>1121</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>1128</v>
+        <v>1122</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>1129</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="16" spans="1:29" ht="22.05" customHeight="1">
       <c r="B16" s="4" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>1130</v>
+        <v>1124</v>
       </c>
       <c r="D16" s="8">
         <v>6</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>1131</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="17" spans="2:5" ht="22.05" customHeight="1">
       <c r="B17" s="5" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>1132</v>
+        <v>1126</v>
       </c>
       <c r="D17" s="8">
         <v>240</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>1133</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="18" spans="2:5" ht="22.05" customHeight="1">
       <c r="B18" s="4" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>1134</v>
+        <v>1128</v>
       </c>
       <c r="D18" s="8">
         <v>250</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>1135</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="19" spans="2:5" ht="22.05" customHeight="1">
       <c r="B19" s="5" t="s">
-        <v>698</v>
+        <v>692</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>1136</v>
+        <v>1130</v>
       </c>
       <c r="D19" s="8">
         <v>8</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>1137</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="20" spans="2:5" ht="22.05" customHeight="1">
       <c r="B20" s="4" t="s">
-        <v>698</v>
+        <v>692</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>1132</v>
+        <v>1126</v>
       </c>
       <c r="D20" s="8">
         <v>300</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>1133</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="21" spans="2:5" ht="22.05" customHeight="1">
       <c r="B21" s="5" t="s">
-        <v>698</v>
+        <v>692</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>1138</v>
+        <v>1132</v>
       </c>
       <c r="D21" s="8">
         <v>25</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>1139</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="22" spans="2:5" ht="22.05" customHeight="1">
       <c r="B22" s="4" t="s">
-        <v>698</v>
+        <v>692</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>1140</v>
+        <v>1134</v>
       </c>
       <c r="D22" s="8">
         <v>200</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>1141</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="23" spans="2:5" ht="22.05" customHeight="1">
       <c r="B23" s="5" t="s">
-        <v>698</v>
+        <v>692</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>1142</v>
+        <v>1136</v>
       </c>
       <c r="D23" s="8">
         <v>180</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>1143</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="24" spans="2:5" ht="22.05" customHeight="1">
       <c r="B24" s="4" t="s">
-        <v>703</v>
+        <v>697</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>1144</v>
+        <v>1138</v>
       </c>
       <c r="D24" s="8">
         <v>25</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>1145</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="25" spans="2:5" ht="22.05" customHeight="1">
       <c r="B25" s="5" t="s">
-        <v>703</v>
+        <v>697</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>1146</v>
+        <v>1140</v>
       </c>
       <c r="D25" s="8">
         <v>30</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>1147</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="26" spans="2:5" ht="22.05" customHeight="1">
       <c r="B26" s="4" t="s">
-        <v>703</v>
+        <v>697</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>1148</v>
+        <v>1142</v>
       </c>
       <c r="D26" s="8">
         <v>100</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>1149</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="27" spans="2:5" ht="22.05" customHeight="1">
       <c r="B27" s="5" t="s">
-        <v>703</v>
+        <v>697</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>1150</v>
+        <v>1144</v>
       </c>
       <c r="D27" s="8">
         <v>0</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>1151</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="28" spans="2:5" ht="22.05" customHeight="1">
       <c r="B28" s="4" t="s">
-        <v>708</v>
+        <v>702</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>1130</v>
+        <v>1124</v>
       </c>
       <c r="D28" s="8">
         <v>8</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>1131</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="29" spans="2:5" ht="22.05" customHeight="1">
       <c r="B29" s="5" t="s">
-        <v>708</v>
+        <v>702</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>1152</v>
+        <v>1146</v>
       </c>
       <c r="D29" s="8">
         <v>20</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>1153</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="30" spans="2:5" ht="22.05" customHeight="1">
       <c r="B30" s="4" t="s">
-        <v>708</v>
+        <v>702</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>1154</v>
+        <v>1148</v>
       </c>
       <c r="D30" s="8">
         <v>15</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>1155</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="31" spans="2:5" ht="22.05" customHeight="1">
       <c r="B31" s="5" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>1156</v>
+        <v>1150</v>
       </c>
       <c r="D31" s="8">
         <v>5</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>1157</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="32" spans="2:5" ht="22.05" customHeight="1">
       <c r="B32" s="4" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>1158</v>
+        <v>1152</v>
       </c>
       <c r="D32" s="8">
         <v>0.03</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>1159</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="33" spans="2:5" ht="22.05" customHeight="1">
       <c r="B33" s="5" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>1160</v>
+        <v>1154</v>
       </c>
       <c r="D33" s="8">
         <v>50</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>1161</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="34" spans="2:5" ht="22.05" customHeight="1">
       <c r="B34" s="4" t="s">
-        <v>717</v>
+        <v>711</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>1162</v>
+        <v>1156</v>
       </c>
       <c r="D34" s="8">
         <v>50</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>1163</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="35" spans="2:5" ht="22.05" customHeight="1">
       <c r="B35" s="5" t="s">
-        <v>717</v>
+        <v>711</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>1164</v>
+        <v>1158</v>
       </c>
       <c r="D35" s="8">
         <v>100</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>1165</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="36" spans="2:5" ht="22.05" customHeight="1">
       <c r="B36" s="4" t="s">
-        <v>717</v>
+        <v>711</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>1166</v>
+        <v>1160</v>
       </c>
       <c r="D36" s="8">
         <v>0.5</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>1167</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="37" spans="2:5" ht="22.05" customHeight="1">
       <c r="B37" s="5" t="s">
-        <v>717</v>
+        <v>711</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>1168</v>
+        <v>1162</v>
       </c>
       <c r="D37" s="8">
         <v>20</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>1169</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="38" spans="2:5" ht="22.05" customHeight="1">
       <c r="B38" s="4" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>1170</v>
+        <v>1164</v>
       </c>
       <c r="D38" s="8">
         <v>20</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>1171</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="39" spans="2:5" ht="22.05" customHeight="1">
       <c r="B39" s="5" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>1172</v>
+        <v>1166</v>
       </c>
       <c r="D39" s="8">
         <v>20</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>1173</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="40" spans="2:5" ht="22.05" customHeight="1">
       <c r="B40" s="4" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>1174</v>
+        <v>1168</v>
       </c>
       <c r="D40" s="8">
         <v>0.2</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>1175</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="41" spans="2:5" ht="22.05" customHeight="1">
       <c r="B41" s="5" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>1176</v>
+        <v>1170</v>
       </c>
       <c r="D41" s="8">
         <v>5</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>1177</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="42" spans="2:5" ht="22.05" customHeight="1">
       <c r="B42" s="4" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>1178</v>
+        <v>1172</v>
       </c>
       <c r="D42" s="8">
         <v>60</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>1179</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="43" spans="2:5" ht="22.05" customHeight="1">
       <c r="B43" s="5" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>1180</v>
+        <v>1174</v>
       </c>
       <c r="D43" s="8">
         <v>1</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>1181</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="44" spans="2:5" ht="22.05" customHeight="1">
       <c r="B44" s="4" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>1182</v>
+        <v>1176</v>
       </c>
       <c r="D44" s="8">
         <v>50</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>1183</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="45" spans="2:5" ht="22.05" customHeight="1">
       <c r="B45" s="5" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>1184</v>
+        <v>1178</v>
       </c>
       <c r="D45" s="8">
         <v>180</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>1185</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="46" spans="2:5" ht="22.05" customHeight="1">
       <c r="B46" s="4" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>1186</v>
+        <v>1180</v>
       </c>
       <c r="D46" s="8">
         <v>45</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>1187</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="47" spans="2:5" ht="22.05" customHeight="1">
       <c r="B47" s="5" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>1188</v>
+        <v>1182</v>
       </c>
       <c r="D47" s="8">
         <v>90</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>1189</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="48" spans="2:5" ht="22.05" customHeight="1">
       <c r="B48" s="4" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>1130</v>
+        <v>1124</v>
       </c>
       <c r="D48" s="8">
         <v>8</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>1131</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="49" spans="2:5" ht="22.05" customHeight="1">
       <c r="B49" s="5" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>1190</v>
+        <v>1184</v>
       </c>
       <c r="D49" s="8">
         <v>2</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>1191</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="50" spans="2:5" ht="22.05" customHeight="1">
       <c r="B50" s="4" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>1192</v>
+        <v>1186</v>
       </c>
       <c r="D50" s="8">
         <v>10</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>1155</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="51" spans="2:5" ht="22.05" customHeight="1">
       <c r="B51" s="5" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>1193</v>
+        <v>1187</v>
       </c>
       <c r="D51" s="8">
         <v>250</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>1194</v>
+        <v>1188</v>
       </c>
     </row>
   </sheetData>
@@ -15239,60 +15242,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="34.049999999999997" customHeight="1">
-      <c r="A1" s="9" t="s">
-        <v>736</v>
-      </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
-      <c r="N1" s="9"/>
-      <c r="O1" s="9"/>
-      <c r="P1" s="9"/>
-      <c r="Q1" s="9"/>
-      <c r="R1" s="9"/>
-      <c r="S1" s="9"/>
-      <c r="T1" s="9"/>
-      <c r="U1" s="9"/>
-      <c r="V1" s="9"/>
-      <c r="W1" s="9"/>
-      <c r="X1" s="9"/>
+      <c r="A1" s="11" t="s">
+        <v>730</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="11"/>
+      <c r="M1" s="11"/>
+      <c r="N1" s="11"/>
+      <c r="O1" s="11"/>
+      <c r="P1" s="11"/>
+      <c r="Q1" s="11"/>
+      <c r="R1" s="11"/>
+      <c r="S1" s="11"/>
+      <c r="T1" s="11"/>
+      <c r="U1" s="11"/>
+      <c r="V1" s="11"/>
+      <c r="W1" s="11"/>
+      <c r="X1" s="11"/>
     </row>
     <row r="2" spans="1:24" ht="31.95" customHeight="1">
-      <c r="A2" s="10" t="s">
-        <v>737</v>
-      </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
-      <c r="O2" s="10"/>
-      <c r="P2" s="10"/>
-      <c r="Q2" s="10"/>
-      <c r="R2" s="10"/>
-      <c r="S2" s="10"/>
-      <c r="T2" s="10"/>
-      <c r="U2" s="10"/>
-      <c r="V2" s="10"/>
-      <c r="W2" s="10"/>
-      <c r="X2" s="10"/>
+      <c r="A2" s="12" t="s">
+        <v>731</v>
+      </c>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12"/>
+      <c r="M2" s="12"/>
+      <c r="N2" s="12"/>
+      <c r="O2" s="12"/>
+      <c r="P2" s="12"/>
+      <c r="Q2" s="12"/>
+      <c r="R2" s="12"/>
+      <c r="S2" s="12"/>
+      <c r="T2" s="12"/>
+      <c r="U2" s="12"/>
+      <c r="V2" s="12"/>
+      <c r="W2" s="12"/>
+      <c r="X2" s="12"/>
     </row>
     <row r="3" spans="1:24" ht="28.05" customHeight="1">
       <c r="A3" s="3" t="s">
@@ -15302,22 +15305,22 @@
         <v>23</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>738</v>
+        <v>732</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>740</v>
+        <v>734</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>605</v>
+        <v>599</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>40</v>
@@ -15335,45 +15338,45 @@
         <v>46</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>609</v>
+        <v>603</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="R3" s="3" t="s">
         <v>50</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="T3" s="3" t="s">
-        <v>690</v>
+        <v>684</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>691</v>
+        <v>685</v>
       </c>
       <c r="V3" s="3" t="s">
-        <v>741</v>
+        <v>735</v>
       </c>
       <c r="W3" s="3" t="s">
-        <v>692</v>
+        <v>686</v>
       </c>
       <c r="X3" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="4" spans="1:24" ht="37.950000000000003" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>742</v>
+        <v>736</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>743</v>
+        <v>737</v>
       </c>
       <c r="C4" s="4">
         <v>3</v>
@@ -15420,36 +15423,36 @@
         <v>577</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>744</v>
+        <v>738</v>
       </c>
       <c r="R4" s="4" t="s">
-        <v>745</v>
+        <v>739</v>
       </c>
       <c r="S4" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
       <c r="U4" s="4">
         <v>10</v>
       </c>
       <c r="V4" s="4" t="s">
-        <v>746</v>
+        <v>740</v>
       </c>
       <c r="W4" s="4" t="s">
-        <v>747</v>
+        <v>741</v>
       </c>
       <c r="X4" s="4" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
     </row>
     <row r="5" spans="1:24" ht="37.950000000000003" customHeight="1">
       <c r="A5" s="5" t="s">
-        <v>749</v>
+        <v>743</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="C5" s="5">
         <v>6</v>
@@ -15496,34 +15499,34 @@
         <v>1356</v>
       </c>
       <c r="Q5" s="5" t="s">
-        <v>751</v>
+        <v>745</v>
       </c>
       <c r="R5" s="5" t="s">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="S5" s="5" t="s">
-        <v>753</v>
+        <v>747</v>
       </c>
       <c r="T5" s="5" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
       <c r="U5" s="5">
         <v>10</v>
       </c>
       <c r="V5" s="5"/>
       <c r="W5" s="5" t="s">
-        <v>754</v>
+        <v>748</v>
       </c>
       <c r="X5" s="5" t="s">
-        <v>755</v>
+        <v>749</v>
       </c>
     </row>
     <row r="6" spans="1:24" ht="37.950000000000003" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>756</v>
+        <v>750</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>757</v>
+        <v>751</v>
       </c>
       <c r="C6" s="4">
         <v>9</v>
@@ -15570,34 +15573,34 @@
         <v>1798</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>758</v>
+        <v>752</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>759</v>
+        <v>753</v>
       </c>
       <c r="S6" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
       <c r="U6" s="4">
         <v>0</v>
       </c>
       <c r="V6" s="4"/>
       <c r="W6" s="4" t="s">
-        <v>760</v>
+        <v>754</v>
       </c>
       <c r="X6" s="4" t="s">
-        <v>761</v>
+        <v>755</v>
       </c>
     </row>
     <row r="7" spans="1:24" ht="37.950000000000003" customHeight="1">
       <c r="A7" s="5" t="s">
-        <v>762</v>
+        <v>756</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>763</v>
+        <v>757</v>
       </c>
       <c r="C7" s="5">
         <v>12</v>
@@ -15644,36 +15647,36 @@
         <v>2484</v>
       </c>
       <c r="Q7" s="5" t="s">
-        <v>764</v>
+        <v>758</v>
       </c>
       <c r="R7" s="5" t="s">
-        <v>765</v>
+        <v>759</v>
       </c>
       <c r="S7" s="5" t="s">
-        <v>766</v>
+        <v>760</v>
       </c>
       <c r="T7" s="5" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
       <c r="U7" s="5">
         <v>9</v>
       </c>
       <c r="V7" s="5" t="s">
-        <v>767</v>
+        <v>761</v>
       </c>
       <c r="W7" s="5" t="s">
-        <v>1201</v>
+        <v>1195</v>
       </c>
       <c r="X7" s="5" t="s">
-        <v>1200</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="8" spans="1:24" ht="37.950000000000003" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>768</v>
+        <v>762</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>769</v>
+        <v>763</v>
       </c>
       <c r="C8" s="4">
         <v>15</v>
@@ -15720,34 +15723,34 @@
         <v>1584</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>770</v>
+        <v>764</v>
       </c>
       <c r="R8" s="4" t="s">
-        <v>771</v>
+        <v>765</v>
       </c>
       <c r="S8" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
       <c r="U8" s="4">
         <v>6</v>
       </c>
       <c r="V8" s="4"/>
       <c r="W8" s="4" t="s">
-        <v>772</v>
+        <v>766</v>
       </c>
       <c r="X8" s="4" t="s">
-        <v>773</v>
+        <v>767</v>
       </c>
     </row>
     <row r="9" spans="1:24" ht="37.950000000000003" customHeight="1">
       <c r="A9" s="5" t="s">
-        <v>774</v>
+        <v>768</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>775</v>
+        <v>769</v>
       </c>
       <c r="C9" s="5">
         <v>18</v>
@@ -15794,34 +15797,34 @@
         <v>2915</v>
       </c>
       <c r="Q9" s="5" t="s">
-        <v>776</v>
+        <v>770</v>
       </c>
       <c r="R9" s="5" t="s">
-        <v>777</v>
+        <v>771</v>
       </c>
       <c r="S9" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="T9" s="5" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
       <c r="U9" s="5">
         <v>6</v>
       </c>
       <c r="V9" s="5"/>
       <c r="W9" s="5" t="s">
-        <v>1202</v>
+        <v>1196</v>
       </c>
       <c r="X9" s="5" t="s">
-        <v>778</v>
+        <v>772</v>
       </c>
     </row>
     <row r="10" spans="1:24" ht="37.950000000000003" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>779</v>
+        <v>773</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>780</v>
+        <v>774</v>
       </c>
       <c r="C10" s="4">
         <v>21</v>
@@ -15868,34 +15871,34 @@
         <v>3140</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>781</v>
+        <v>775</v>
       </c>
       <c r="R10" s="4" t="s">
-        <v>782</v>
+        <v>776</v>
       </c>
       <c r="S10" s="4" t="s">
-        <v>783</v>
+        <v>777</v>
       </c>
       <c r="T10" s="4" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
       <c r="U10" s="4">
         <v>30</v>
       </c>
       <c r="V10" s="4"/>
       <c r="W10" s="4" t="s">
-        <v>1203</v>
+        <v>1197</v>
       </c>
       <c r="X10" s="4" t="s">
-        <v>784</v>
+        <v>778</v>
       </c>
     </row>
     <row r="11" spans="1:24" ht="37.950000000000003" customHeight="1">
       <c r="A11" s="5" t="s">
-        <v>785</v>
+        <v>779</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>786</v>
+        <v>780</v>
       </c>
       <c r="C11" s="5">
         <v>24</v>
@@ -15942,36 +15945,36 @@
         <v>2318</v>
       </c>
       <c r="Q11" s="5" t="s">
-        <v>787</v>
+        <v>781</v>
       </c>
       <c r="R11" s="5" t="s">
-        <v>788</v>
+        <v>782</v>
       </c>
       <c r="S11" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="T11" s="5" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
       <c r="U11" s="5">
         <v>10</v>
       </c>
       <c r="V11" s="5" t="s">
-        <v>789</v>
+        <v>783</v>
       </c>
       <c r="W11" s="5" t="s">
-        <v>1204</v>
+        <v>1198</v>
       </c>
       <c r="X11" s="5" t="s">
-        <v>1205</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="12" spans="1:24" ht="37.950000000000003" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>790</v>
+        <v>784</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>791</v>
+        <v>785</v>
       </c>
       <c r="C12" s="4">
         <v>27</v>
@@ -16018,34 +16021,34 @@
         <v>4437</v>
       </c>
       <c r="Q12" s="4" t="s">
-        <v>792</v>
+        <v>786</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>793</v>
+        <v>787</v>
       </c>
       <c r="S12" s="4" t="s">
-        <v>794</v>
+        <v>788</v>
       </c>
       <c r="T12" s="4" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
       <c r="U12" s="4">
         <v>0</v>
       </c>
       <c r="V12" s="4"/>
       <c r="W12" s="4" t="s">
-        <v>1206</v>
+        <v>1200</v>
       </c>
       <c r="X12" s="4" t="s">
-        <v>795</v>
+        <v>789</v>
       </c>
     </row>
     <row r="13" spans="1:24" ht="37.950000000000003" customHeight="1">
       <c r="A13" s="5" t="s">
-        <v>796</v>
+        <v>790</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>797</v>
+        <v>791</v>
       </c>
       <c r="C13" s="5">
         <v>30</v>
@@ -16092,34 +16095,34 @@
         <v>4153</v>
       </c>
       <c r="Q13" s="5" t="s">
-        <v>798</v>
+        <v>792</v>
       </c>
       <c r="R13" s="5" t="s">
-        <v>799</v>
+        <v>793</v>
       </c>
       <c r="S13" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="T13" s="5" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
       <c r="U13" s="5">
         <v>8</v>
       </c>
       <c r="V13" s="5"/>
       <c r="W13" s="5" t="s">
-        <v>800</v>
+        <v>794</v>
       </c>
       <c r="X13" s="5" t="s">
-        <v>801</v>
+        <v>795</v>
       </c>
     </row>
     <row r="14" spans="1:24" ht="37.950000000000003" customHeight="1">
       <c r="A14" s="4" t="s">
-        <v>802</v>
+        <v>796</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>803</v>
+        <v>797</v>
       </c>
       <c r="C14" s="4">
         <v>33</v>
@@ -16166,36 +16169,36 @@
         <v>3795</v>
       </c>
       <c r="Q14" s="4" t="s">
-        <v>804</v>
+        <v>798</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>805</v>
+        <v>799</v>
       </c>
       <c r="S14" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="T14" s="4" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
       <c r="U14" s="4">
         <v>8</v>
       </c>
       <c r="V14" s="4" t="s">
-        <v>806</v>
+        <v>800</v>
       </c>
       <c r="W14" s="4" t="s">
-        <v>807</v>
+        <v>801</v>
       </c>
       <c r="X14" s="4" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
     </row>
     <row r="15" spans="1:24" ht="37.950000000000003" customHeight="1">
       <c r="A15" s="5" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="C15" s="5">
         <v>36</v>
@@ -16225,14 +16228,14 @@
         <v>181.5</v>
       </c>
       <c r="L15" s="7">
-        <v>0.05</v>
+        <v>0.25</v>
       </c>
       <c r="M15" s="5">
         <v>1.5</v>
       </c>
       <c r="N15" s="5">
         <f t="shared" si="0"/>
-        <v>482.8</v>
+        <v>529.9</v>
       </c>
       <c r="O15" s="5">
         <v>1240</v>
@@ -16242,26 +16245,26 @@
         <v>4181</v>
       </c>
       <c r="Q15" s="5" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="S15" s="5" t="s">
-        <v>813</v>
+        <v>807</v>
       </c>
       <c r="T15" s="5" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
       <c r="U15" s="5">
         <v>0</v>
       </c>
       <c r="V15" s="5"/>
       <c r="W15" s="5" t="s">
-        <v>1207</v>
+        <v>1201</v>
       </c>
       <c r="X15" s="5" t="s">
-        <v>1208</v>
+        <v>1202</v>
       </c>
     </row>
   </sheetData>
@@ -16289,28 +16292,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="34.049999999999997" customHeight="1">
-      <c r="A1" s="9" t="s">
-        <v>814</v>
-      </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
+      <c r="A1" s="11" t="s">
+        <v>808</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
     </row>
     <row r="2" spans="1:8" ht="31.95" customHeight="1">
-      <c r="A2" s="10" t="s">
-        <v>815</v>
-      </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
+      <c r="A2" s="12" t="s">
+        <v>809</v>
+      </c>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
     </row>
     <row r="3" spans="1:8" ht="28.05" customHeight="1">
       <c r="A3" s="3" t="s">
@@ -16320,672 +16323,672 @@
         <v>23</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>816</v>
+        <v>810</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>817</v>
+        <v>811</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>818</v>
+        <v>812</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>819</v>
+        <v>813</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>820</v>
+        <v>814</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="37.950000000000003" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>821</v>
+        <v>815</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>822</v>
+        <v>816</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>823</v>
+        <v>817</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>824</v>
+        <v>818</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>825</v>
+        <v>819</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>826</v>
+        <v>820</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="37.950000000000003" customHeight="1">
       <c r="A5" s="5" t="s">
-        <v>827</v>
+        <v>821</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>828</v>
+        <v>822</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="D5" s="5" t="s">
+        <v>817</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>823</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>829</v>
-      </c>
       <c r="F5" s="5" t="s">
-        <v>830</v>
+        <v>824</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>831</v>
+        <v>825</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="37.950000000000003" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>832</v>
+        <v>826</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>833</v>
+        <v>827</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>834</v>
+        <v>828</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>835</v>
+        <v>829</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>836</v>
+        <v>830</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="37.950000000000003" customHeight="1">
       <c r="A7" s="5" t="s">
-        <v>837</v>
+        <v>831</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>838</v>
+        <v>832</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>839</v>
+        <v>833</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>840</v>
+        <v>834</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>56</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>836</v>
+        <v>830</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="37.950000000000003" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>841</v>
+        <v>835</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>842</v>
+        <v>836</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>843</v>
+        <v>837</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>844</v>
+        <v>838</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>56</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>836</v>
+        <v>830</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="37.950000000000003" customHeight="1">
       <c r="A9" s="5" t="s">
-        <v>845</v>
+        <v>839</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>846</v>
+        <v>840</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>823</v>
+        <v>817</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>847</v>
+        <v>841</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>56</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>848</v>
+        <v>842</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="37.950000000000003" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>849</v>
+        <v>843</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>850</v>
+        <v>844</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>851</v>
+        <v>845</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>852</v>
+        <v>846</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>853</v>
+        <v>847</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>854</v>
+        <v>848</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>836</v>
+        <v>830</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="37.950000000000003" customHeight="1">
       <c r="A11" s="5" t="s">
-        <v>855</v>
+        <v>849</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>856</v>
+        <v>850</v>
       </c>
       <c r="C11" s="5" t="s">
+        <v>845</v>
+      </c>
+      <c r="D11" s="5" t="s">
         <v>851</v>
       </c>
-      <c r="D11" s="5" t="s">
-        <v>857</v>
-      </c>
       <c r="E11" s="5" t="s">
-        <v>1195</v>
+        <v>1189</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>56</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>836</v>
+        <v>830</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="37.950000000000003" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>858</v>
+        <v>852</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>859</v>
+        <v>853</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>851</v>
+        <v>845</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>860</v>
+        <v>854</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>861</v>
+        <v>855</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>56</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>836</v>
+        <v>830</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="37.950000000000003" customHeight="1">
       <c r="A13" s="5" t="s">
-        <v>862</v>
+        <v>856</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>863</v>
+        <v>857</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>851</v>
+        <v>845</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>864</v>
+        <v>858</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>865</v>
+        <v>859</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>56</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>866</v>
+        <v>860</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="37.950000000000003" customHeight="1">
       <c r="A14" s="4" t="s">
-        <v>867</v>
+        <v>861</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>868</v>
+        <v>862</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>851</v>
+        <v>845</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>852</v>
+        <v>846</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>869</v>
+        <v>863</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>56</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>836</v>
+        <v>830</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="37.950000000000003" customHeight="1">
       <c r="A15" s="5" t="s">
-        <v>870</v>
+        <v>864</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>871</v>
+        <v>865</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>823</v>
+        <v>817</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>872</v>
+        <v>866</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>873</v>
+        <v>867</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>874</v>
+        <v>868</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="37.950000000000003" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>875</v>
+        <v>869</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>876</v>
+        <v>870</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>877</v>
+        <v>871</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>878</v>
+        <v>872</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>879</v>
+        <v>873</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>836</v>
+        <v>830</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="37.950000000000003" customHeight="1">
       <c r="A17" s="5" t="s">
-        <v>880</v>
+        <v>874</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>881</v>
+        <v>875</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>823</v>
+        <v>817</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>882</v>
+        <v>876</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>56</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>883</v>
+        <v>877</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="37.950000000000003" customHeight="1">
       <c r="A18" s="4" t="s">
-        <v>884</v>
+        <v>878</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>885</v>
+        <v>879</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>886</v>
+        <v>880</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>887</v>
+        <v>881</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>56</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>836</v>
+        <v>830</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="37.950000000000003" customHeight="1">
       <c r="A19" s="5" t="s">
-        <v>888</v>
+        <v>882</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>889</v>
+        <v>883</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>890</v>
+        <v>884</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>891</v>
+        <v>885</v>
       </c>
       <c r="F19" s="5" t="s">
         <v>56</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>836</v>
+        <v>830</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="37.950000000000003" customHeight="1">
       <c r="A20" s="4" t="s">
-        <v>892</v>
+        <v>886</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>893</v>
+        <v>887</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>894</v>
+        <v>888</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>895</v>
+        <v>889</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>896</v>
+        <v>890</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>56</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>836</v>
+        <v>830</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="37.950000000000003" customHeight="1">
       <c r="A21" s="5" t="s">
-        <v>897</v>
+        <v>891</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>898</v>
+        <v>892</v>
       </c>
       <c r="C21" s="5" t="s">
+        <v>888</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>893</v>
+      </c>
+      <c r="E21" s="5" t="s">
         <v>894</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>899</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>900</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>56</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>836</v>
+        <v>830</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="37.950000000000003" customHeight="1">
       <c r="A22" s="4" t="s">
-        <v>901</v>
+        <v>895</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>902</v>
+        <v>896</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>894</v>
+        <v>888</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>903</v>
+        <v>897</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>904</v>
+        <v>898</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>56</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>836</v>
+        <v>830</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="37.950000000000003" customHeight="1">
       <c r="A23" s="5" t="s">
-        <v>905</v>
+        <v>899</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>906</v>
+        <v>900</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>894</v>
+        <v>888</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>907</v>
+        <v>901</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>908</v>
+        <v>902</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>909</v>
+        <v>903</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>836</v>
+        <v>830</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="37.950000000000003" customHeight="1">
       <c r="A24" s="4" t="s">
-        <v>910</v>
+        <v>904</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>911</v>
+        <v>905</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>894</v>
+        <v>888</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>912</v>
+        <v>906</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>56</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>836</v>
+        <v>830</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="37.950000000000003" customHeight="1">
       <c r="A25" s="5" t="s">
-        <v>913</v>
+        <v>907</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>914</v>
+        <v>908</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>25</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>915</v>
+        <v>909</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>916</v>
+        <v>910</v>
       </c>
       <c r="F25" s="5" t="s">
         <v>56</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>836</v>
+        <v>830</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="37.950000000000003" customHeight="1">
       <c r="A26" s="4" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>918</v>
+        <v>912</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>25</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>915</v>
+        <v>909</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>919</v>
+        <v>913</v>
       </c>
       <c r="F26" s="4" t="s">
         <v>56</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>836</v>
+        <v>830</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="37.950000000000003" customHeight="1">
       <c r="A27" s="5" t="s">
-        <v>920</v>
+        <v>914</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>25</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>915</v>
+        <v>909</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>922</v>
+        <v>916</v>
       </c>
       <c r="F27" s="5" t="s">
         <v>56</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>836</v>
+        <v>830</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="37.950000000000003" customHeight="1">
       <c r="A28" s="4" t="s">
-        <v>923</v>
+        <v>917</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>924</v>
+        <v>918</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>25</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>915</v>
+        <v>909</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>925</v>
+        <v>919</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>56</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>836</v>
+        <v>830</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="37.950000000000003" customHeight="1">
@@ -16997,12 +17000,12 @@
       <c r="F29" s="5"/>
       <c r="G29" s="5"/>
       <c r="H29" s="5" t="s">
-        <v>926</v>
+        <v>920</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="37.950000000000003" customHeight="1">
       <c r="A30" s="4" t="s">
-        <v>927</v>
+        <v>921</v>
       </c>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
@@ -17011,127 +17014,127 @@
       <c r="F30" s="4"/>
       <c r="G30" s="4"/>
       <c r="H30" s="4" t="s">
-        <v>926</v>
+        <v>920</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="37.950000000000003" customHeight="1">
       <c r="A31" s="5" t="s">
-        <v>928</v>
+        <v>922</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>929</v>
+        <v>923</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>930</v>
+        <v>924</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>931</v>
+        <v>925</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>932</v>
+        <v>926</v>
       </c>
       <c r="F31" s="5"/>
       <c r="G31" s="5" t="s">
-        <v>933</v>
+        <v>927</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>926</v>
+        <v>920</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="37.950000000000003" customHeight="1">
       <c r="A32" s="4" t="s">
-        <v>934</v>
+        <v>928</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>935</v>
+        <v>929</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
       <c r="D32" s="4" t="s">
+        <v>925</v>
+      </c>
+      <c r="E32" s="4" t="s">
         <v>931</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>937</v>
       </c>
       <c r="F32" s="4"/>
       <c r="G32" s="4" t="s">
-        <v>938</v>
+        <v>932</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>926</v>
+        <v>920</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="37.950000000000003" customHeight="1">
       <c r="A33" s="5" t="s">
-        <v>939</v>
+        <v>933</v>
       </c>
       <c r="B33" s="5" t="s">
+        <v>929</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>934</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>925</v>
+      </c>
+      <c r="E33" s="5" t="s">
         <v>935</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>940</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>931</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>941</v>
       </c>
       <c r="F33" s="5"/>
       <c r="G33" s="5" t="s">
-        <v>942</v>
+        <v>936</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>926</v>
+        <v>920</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="37.950000000000003" customHeight="1">
       <c r="A34" s="4" t="s">
-        <v>943</v>
+        <v>937</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>935</v>
+        <v>929</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>944</v>
+        <v>938</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>931</v>
+        <v>925</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>945</v>
+        <v>939</v>
       </c>
       <c r="F34" s="4"/>
       <c r="G34" s="4" t="s">
-        <v>946</v>
+        <v>940</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>926</v>
+        <v>920</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="37.950000000000003" customHeight="1">
       <c r="A35" s="5" t="s">
-        <v>947</v>
+        <v>941</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>948</v>
+        <v>942</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>949</v>
+        <v>943</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>931</v>
+        <v>925</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>950</v>
+        <v>944</v>
       </c>
       <c r="F35" s="5"/>
       <c r="G35" s="5" t="s">
-        <v>951</v>
+        <v>945</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>926</v>
+        <v>920</v>
       </c>
     </row>
   </sheetData>
